--- a/technicals/exports/2026-10-16.xlsx
+++ b/technicals/exports/2026-10-16.xlsx
@@ -158,7 +158,7 @@
         <ns0:v>-2.3044347702507295</ns0:v>
       </ns0:c>
       <ns0:c r="K2">
-        <ns0:v>1.162452351462825</ns0:v>
+        <ns0:v>1.162443934055627</ns0:v>
       </ns0:c>
       <ns0:c r="L2">
         <ns0:v>62.251705736388324</ns0:v>
@@ -237,7 +237,7 @@
         <ns0:v>-0.31055691317948275</ns0:v>
       </ns0:c>
       <ns0:c r="K3">
-        <ns0:v>1.1156304284975012</ns0:v>
+        <ns0:v>1.1333305798576776</ns0:v>
       </ns0:c>
       <ns0:c r="L3">
         <ns0:v>71.29250623553872</ns0:v>
@@ -280,59 +280,59 @@
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
         <ns0:is>
-          <ns0:t>ALRM</ns0:t>
+          <ns0:t>AFG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Alarm.com Holdings Inc</ns0:t>
+          <ns0:t>American Financial Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미와 해외에서 건물 연결 플랫폼과 주거용 경보·스마트 보안·개인 안전 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>미국에서 재산·상해보험을 제공하는 보험 지주회사로, 재산 및 운송보험 상품 등을 취급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
-        <ns0:v>57.369998931884766</ns0:v>
+        <ns0:v>149.1300048828125</ns0:v>
       </ns0:c>
       <ns0:c r="H4">
-        <ns0:v>-0.46842550420318485</ns0:v>
+        <ns0:v>2.3330880772344242</ns0:v>
       </ns0:c>
       <ns0:c r="I4">
-        <ns0:v>58.5</ns0:v>
+        <ns0:v>148.7100067138672</ns0:v>
       </ns0:c>
       <ns0:c r="J4">
-        <ns0:v>-1.931625757461941</ns0:v>
+        <ns0:v>0.28242764439747603</ns0:v>
       </ns0:c>
       <ns0:c r="K4">
-        <ns0:v>0.9733438452643751</ns0:v>
+        <ns0:v>1.0793372929040326</ns0:v>
       </ns0:c>
       <ns0:c r="L4">
-        <ns0:v>64.16002590729695</ns0:v>
+        <ns0:v>72.23582790396111</ns0:v>
       </ns0:c>
       <ns0:c r="M4">
-        <ns0:v>54.99700012207031</ns0:v>
+        <ns0:v>140.94650115966797</ns0:v>
       </ns0:c>
       <ns0:c r="N4">
-        <ns0:v>55.69099990844727</ns0:v>
+        <ns0:v>142.53739959716796</ns0:v>
       </ns0:c>
       <ns0:c r="O4">
-        <ns0:v>49.495450038909915</ns0:v>
+        <ns0:v>135.53219959259033</ns0:v>
       </ns0:c>
       <ns0:c r="P4" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q4" t="inlineStr">
@@ -347,7 +347,7 @@
       </ns0:c>
       <ns0:c r="T4" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ALRM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AFG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -359,59 +359,59 @@
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>AOUT</ns0:t>
+          <ns0:t>ALRM</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5" t="inlineStr">
         <ns0:is>
-          <ns0:t>American Outdoor Brands Inc</ns0:t>
+          <ns0:t>Alarm.com Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Leisure</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 사격 스포츠 액세서리, 칼 등 야외활동 제품과 용품을 제공하는 기업.</ns0:t>
+          <ns0:t>북미와 해외에서 건물 연결 플랫폼과 주거용 경보·스마트 보안·개인 안전 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
-        <ns0:v>18.059999465942383</ns0:v>
+        <ns0:v>57.369998931884766</ns0:v>
       </ns0:c>
       <ns0:c r="H5">
-        <ns0:v>1.6891848715895774</ns0:v>
+        <ns0:v>-0.46842550420318485</ns0:v>
       </ns0:c>
       <ns0:c r="I5">
-        <ns0:v>17.829999923706055</ns0:v>
+        <ns0:v>58.5</ns0:v>
       </ns0:c>
       <ns0:c r="J5">
-        <ns0:v>1.2899581784659997</ns0:v>
+        <ns0:v>-1.931625757461941</ns0:v>
       </ns0:c>
       <ns0:c r="K5">
-        <ns0:v>2.150208869572556</ns0:v>
+        <ns0:v>0.9734048144644171</ns0:v>
       </ns0:c>
       <ns0:c r="L5">
-        <ns0:v>71.81724408467235</ns0:v>
+        <ns0:v>64.16002590729695</ns0:v>
       </ns0:c>
       <ns0:c r="M5">
-        <ns0:v>16.775500106811524</ns0:v>
+        <ns0:v>54.99700012207031</ns0:v>
       </ns0:c>
       <ns0:c r="N5">
-        <ns0:v>14.337000026702881</ns0:v>
+        <ns0:v>55.69099990844727</ns0:v>
       </ns0:c>
       <ns0:c r="O5">
-        <ns0:v>11.073200047016144</ns0:v>
+        <ns0:v>49.495450038909915</ns0:v>
       </ns0:c>
       <ns0:c r="P5" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q5" t="inlineStr">
@@ -426,7 +426,7 @@
       </ns0:c>
       <ns0:c r="T5" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AOUT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ALRM/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -438,55 +438,55 @@
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>APA</ns0:t>
+          <ns0:t>AMN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6" t="inlineStr">
         <ns0:is>
-          <ns0:t>APA Corp</ns0:t>
+          <ns0:t>AMN Healthcare Services Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Medical Care Facilities</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·이집트·북해에서 천연가스, 원유 및 천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
+          <ns0:t>미국 병원과 의료시설에 기술 기반 의료인력 솔루션 및 인력 공급 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
-        <ns0:v>49.150001525878906</ns0:v>
+        <ns0:v>40.4900016784668</ns0:v>
       </ns0:c>
       <ns0:c r="H6">
-        <ns0:v>4.065217027845991</ns0:v>
+        <ns0:v>1.225004196167001</ns0:v>
       </ns0:c>
       <ns0:c r="I6">
-        <ns0:v>48.599998474121094</ns0:v>
+        <ns0:v>40.15999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J6">
-        <ns0:v>1.1316935576668463</ns0:v>
+        <ns0:v>0.821717709931602</ns0:v>
       </ns0:c>
       <ns0:c r="K6">
-        <ns0:v>1.1156014425837384</ns0:v>
+        <ns0:v>2.228164121339666</ns0:v>
       </ns0:c>
       <ns0:c r="L6">
-        <ns0:v>69.73438077327219</ns0:v>
+        <ns0:v>75.60233724087706</ns0:v>
       </ns0:c>
       <ns0:c r="M6">
-        <ns0:v>44.55100021362305</ns0:v>
+        <ns0:v>36.12050018310547</ns0:v>
       </ns0:c>
       <ns0:c r="N6">
-        <ns0:v>43.61280006408691</ns0:v>
+        <ns0:v>35.010400009155276</ns0:v>
       </ns0:c>
       <ns0:c r="O6">
-        <ns0:v>36.4315500831604</ns0:v>
+        <ns0:v>26.97614996433258</ns0:v>
       </ns0:c>
       <ns0:c r="P6" t="inlineStr">
         <ns0:is>
@@ -505,7 +505,7 @@
       </ns0:c>
       <ns0:c r="T6" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/APA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AMN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -517,59 +517,59 @@
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>APLE</ns0:t>
+          <ns0:t>AOUT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apple Hospitality REIT Inc</ns0:t>
+          <ns0:t>American Outdoor Brands Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Real Estate</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E7" t="inlineStr">
         <ns0:is>
-          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
+          <ns0:t>Leisure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 내 고급 객실 중심 호텔 포트폴리오를 보유한 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>미국과 해외에서 사격 스포츠 액세서리, 칼 등 야외활동 제품과 용품을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
-        <ns0:v>17.049999237060547</ns0:v>
+        <ns0:v>18.059999465942383</ns0:v>
       </ns0:c>
       <ns0:c r="H7">
-        <ns0:v>1.1269194533263027</ns0:v>
+        <ns0:v>1.6891848715895774</ns0:v>
       </ns0:c>
       <ns0:c r="I7">
-        <ns0:v>17.280000686645508</ns0:v>
+        <ns0:v>17.829999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="J7">
-        <ns0:v>-1.3310268544301174</ns0:v>
+        <ns0:v>1.2899581784659997</ns0:v>
       </ns0:c>
       <ns0:c r="K7">
-        <ns0:v>0.8779936886913957</ns0:v>
+        <ns0:v>2.1503017004936917</ns0:v>
       </ns0:c>
       <ns0:c r="L7">
-        <ns0:v>67.46825087874123</ns0:v>
+        <ns0:v>71.81724408467235</ns0:v>
       </ns0:c>
       <ns0:c r="M7">
-        <ns0:v>16.282000017166137</ns0:v>
+        <ns0:v>16.775500106811524</ns0:v>
       </ns0:c>
       <ns0:c r="N7">
-        <ns0:v>16.060199966430662</ns0:v>
+        <ns0:v>14.337000026702881</ns0:v>
       </ns0:c>
       <ns0:c r="O7">
-        <ns0:v>14.355899996757508</ns0:v>
+        <ns0:v>11.073200047016144</ns0:v>
       </ns0:c>
       <ns0:c r="P7" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q7" t="inlineStr">
@@ -584,7 +584,7 @@
       </ns0:c>
       <ns0:c r="T7" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/APLE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AOUT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -596,59 +596,59 @@
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
         <ns0:is>
-          <ns0:t>AUDC</ns0:t>
+          <ns0:t>APA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Audiocodes</ns0:t>
+          <ns0:t>APA Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Equipment</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
+          <ns0:t>미국·이집트·북해에서 천연가스, 원유 및 천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
-        <ns0:v>11.199999809265137</ns0:v>
+        <ns0:v>49.150001525878906</ns0:v>
       </ns0:c>
       <ns0:c r="H8">
-        <ns0:v>-0.7971669875286636</ns0:v>
+        <ns0:v>4.065217027845991</ns0:v>
       </ns0:c>
       <ns0:c r="I8">
-        <ns0:v>11.5600004196167</ns0:v>
+        <ns0:v>48.599998474121094</ns0:v>
       </ns0:c>
       <ns0:c r="J8">
-        <ns0:v>-3.1141920180267513</ns0:v>
+        <ns0:v>1.1316935576668463</ns0:v>
       </ns0:c>
       <ns0:c r="K8">
-        <ns0:v>0.7669403784362727</ns0:v>
+        <ns0:v>1.1159649990871399</ns0:v>
       </ns0:c>
       <ns0:c r="L8">
-        <ns0:v>61.50096685772864</ns0:v>
+        <ns0:v>69.73438077327219</ns0:v>
       </ns0:c>
       <ns0:c r="M8">
-        <ns0:v>10.908000040054322</ns0:v>
+        <ns0:v>44.55100021362305</ns0:v>
       </ns0:c>
       <ns0:c r="N8">
-        <ns0:v>10.31019998550415</ns0:v>
+        <ns0:v>43.61280006408691</ns0:v>
       </ns0:c>
       <ns0:c r="O8">
-        <ns0:v>9.19255000591278</ns0:v>
+        <ns0:v>36.4315500831604</ns0:v>
       </ns0:c>
       <ns0:c r="P8" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q8" t="inlineStr">
@@ -663,7 +663,7 @@
       </ns0:c>
       <ns0:c r="T8" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AUDC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/APA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -675,59 +675,59 @@
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>AVTR</ns0:t>
+          <ns0:t>APLE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Avantor Inc</ns0:t>
+          <ns0:t>Apple Hospitality REIT Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Real Estate</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
+          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>바이오제약·의료·교육·정부·첨단기술·응용소재 산업에 핵심 제품과 서비스를 제공.</ns0:t>
+          <ns0:t>미국 내 고급 객실 중심 호텔 포트폴리오를 보유한 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
-        <ns0:v>16.420000076293945</ns0:v>
+        <ns0:v>17.049999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="H9">
-        <ns0:v>2.0509628376416122</ns0:v>
+        <ns0:v>1.1269194533263027</ns0:v>
       </ns0:c>
       <ns0:c r="I9">
-        <ns0:v>16.375</ns0:v>
+        <ns0:v>17.280000686645508</ns0:v>
       </ns0:c>
       <ns0:c r="J9">
-        <ns0:v>0.2748096262225719</ns0:v>
+        <ns0:v>-1.3310268544301174</ns0:v>
       </ns0:c>
       <ns0:c r="K9">
-        <ns0:v>3.5161867379902048</ns0:v>
+        <ns0:v>0.8779800699613617</ns0:v>
       </ns0:c>
       <ns0:c r="L9">
-        <ns0:v>68.39164203130747</ns0:v>
+        <ns0:v>67.46825087874123</ns0:v>
       </ns0:c>
       <ns0:c r="M9">
-        <ns0:v>15.414000082015992</ns0:v>
+        <ns0:v>16.282000017166137</ns0:v>
       </ns0:c>
       <ns0:c r="N9">
-        <ns0:v>14.872800025939942</ns0:v>
+        <ns0:v>16.060199966430662</ns0:v>
       </ns0:c>
       <ns0:c r="O9">
-        <ns0:v>10.95655002117157</ns0:v>
+        <ns0:v>14.355899996757508</ns0:v>
       </ns0:c>
       <ns0:c r="P9" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q9" t="inlineStr">
@@ -742,7 +742,7 @@
       </ns0:c>
       <ns0:c r="T9" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AVTR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/APLE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -754,55 +754,55 @@
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
-          <ns0:t>BDX</ns0:t>
+          <ns0:t>AUDC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Becton Dickinson &amp; Co</ns0:t>
+          <ns0:t>Audiocodes</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
+          <ns0:t>Communication Equipment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 의료기관·연구기관 등에 의료용품, 의료기기, 실험실 장비 및 진단 제품을 개발·제조·판매.</ns0:t>
+          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
-        <ns0:v>191.75</ns0:v>
+        <ns0:v>11.199999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="H10">
-        <ns0:v>-1.037363007751857</ns0:v>
+        <ns0:v>-0.7971669875286636</ns0:v>
       </ns0:c>
       <ns0:c r="I10">
-        <ns0:v>194.33999633789062</ns0:v>
+        <ns0:v>11.5600004196167</ns0:v>
       </ns0:c>
       <ns0:c r="J10">
-        <ns0:v>-1.3327139995348736</ns0:v>
+        <ns0:v>-3.1141920180267513</ns0:v>
       </ns0:c>
       <ns0:c r="K10">
-        <ns0:v>0.7778691841977021</ns0:v>
+        <ns0:v>0.7671863223451941</ns0:v>
       </ns0:c>
       <ns0:c r="L10">
-        <ns0:v>63.73162342773647</ns0:v>
+        <ns0:v>61.50096685772864</ns0:v>
       </ns0:c>
       <ns0:c r="M10">
-        <ns0:v>183.36150054931642</ns0:v>
+        <ns0:v>10.908000040054322</ns0:v>
       </ns0:c>
       <ns0:c r="N10">
-        <ns0:v>183.8764013671875</ns0:v>
+        <ns0:v>10.31019998550415</ns0:v>
       </ns0:c>
       <ns0:c r="O10">
-        <ns0:v>164.09863754272462</ns0:v>
+        <ns0:v>9.19255000591278</ns0:v>
       </ns0:c>
       <ns0:c r="P10" t="inlineStr">
         <ns0:is>
@@ -821,7 +821,7 @@
       </ns0:c>
       <ns0:c r="T10" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BDX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AUDC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -833,59 +833,59 @@
       </ns0:c>
       <ns0:c r="B11" t="inlineStr">
         <ns0:is>
-          <ns0:t>BOX</ns0:t>
+          <ns0:t>AVTR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Box Inc</ns0:t>
+          <ns0:t>Avantor Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 규모의 조직이 장소와 기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
+          <ns0:t>바이오제약·의료·교육·정부·첨단기술·응용소재 산업에 핵심 제품과 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
-        <ns0:v>39.560001373291016</ns0:v>
+        <ns0:v>16.420000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H11">
-        <ns0:v>0.20263888546681041</ns0:v>
+        <ns0:v>2.0509628376416122</ns0:v>
       </ns0:c>
       <ns0:c r="I11">
-        <ns0:v>39.63999938964844</ns0:v>
+        <ns0:v>16.375</ns0:v>
       </ns0:c>
       <ns0:c r="J11">
-        <ns0:v>-0.20181134608774354</ns0:v>
+        <ns0:v>0.2748096262225719</ns0:v>
       </ns0:c>
       <ns0:c r="K11">
-        <ns0:v>1.212603491451097</ns0:v>
+        <ns0:v>3.5162017101838465</ns0:v>
       </ns0:c>
       <ns0:c r="L11">
-        <ns0:v>78.25560752066835</ns0:v>
+        <ns0:v>68.39164203130747</ns0:v>
       </ns0:c>
       <ns0:c r="M11">
-        <ns0:v>34.998999977111815</ns0:v>
+        <ns0:v>15.414000082015992</ns0:v>
       </ns0:c>
       <ns0:c r="N11">
-        <ns0:v>34.35159996032715</ns0:v>
+        <ns0:v>14.872800025939942</ns0:v>
       </ns0:c>
       <ns0:c r="O11">
-        <ns0:v>28.05569996833801</ns0:v>
+        <ns0:v>10.95655002117157</ns0:v>
       </ns0:c>
       <ns0:c r="P11" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q11" t="inlineStr">
@@ -900,7 +900,7 @@
       </ns0:c>
       <ns0:c r="T11" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BOX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AVTR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -912,59 +912,59 @@
       </ns0:c>
       <ns0:c r="B12" t="inlineStr">
         <ns0:is>
-          <ns0:t>BP</ns0:t>
+          <ns0:t>BDX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C12" t="inlineStr">
         <ns0:is>
-          <ns0:t>BP plc ADR</ns0:t>
+          <ns0:t>Becton Dickinson &amp; Co</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 석유·가스 사업을 운영하며 가스·저탄소 에너지, 석유 생산 및 고객·제품 부문을 영위.</ns0:t>
+          <ns0:t>전 세계 의료기관·연구기관 등에 의료용품, 의료기기, 실험실 장비 및 진단 제품을 개발·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
-        <ns0:v>50.209999084472656</ns0:v>
+        <ns0:v>191.75</ns0:v>
       </ns0:c>
       <ns0:c r="H12">
-        <ns0:v>3.6540060031870603</ns0:v>
+        <ns0:v>-1.037363007751857</ns0:v>
       </ns0:c>
       <ns0:c r="I12">
-        <ns0:v>49.2400016784668</ns0:v>
+        <ns0:v>194.33999633789062</ns0:v>
       </ns0:c>
       <ns0:c r="J12">
-        <ns0:v>1.9699378004490509</ns0:v>
+        <ns0:v>-1.3327139995348736</ns0:v>
       </ns0:c>
       <ns0:c r="K12">
-        <ns0:v>1.2102319932109897</ns0:v>
+        <ns0:v>0.7778906591999736</ns0:v>
       </ns0:c>
       <ns0:c r="L12">
-        <ns0:v>73.61850984610606</ns0:v>
+        <ns0:v>63.73162342773647</ns0:v>
       </ns0:c>
       <ns0:c r="M12">
-        <ns0:v>45.50049991607666</ns0:v>
+        <ns0:v>183.36150054931642</ns0:v>
       </ns0:c>
       <ns0:c r="N12">
-        <ns0:v>44.58240013122558</ns0:v>
+        <ns0:v>183.8764013671875</ns0:v>
       </ns0:c>
       <ns0:c r="O12">
-        <ns0:v>42.2493500328064</ns0:v>
+        <ns0:v>164.09863754272462</ns0:v>
       </ns0:c>
       <ns0:c r="P12" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q12" t="inlineStr">
@@ -979,7 +979,7 @@
       </ns0:c>
       <ns0:c r="T12" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BDX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -991,59 +991,59 @@
       </ns0:c>
       <ns0:c r="B13" t="inlineStr">
         <ns0:is>
-          <ns0:t>BSVN</ns0:t>
+          <ns0:t>BOX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Bank7 Corp</ns0:t>
+          <ns0:t>Box Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·기업 고객에게 예금 등 은행·금융 서비스를 제공하는 Bank7의 은행지주회사.</ns0:t>
+          <ns0:t>다양한 규모의 조직이 장소와 기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
-        <ns0:v>58.13999938964844</ns0:v>
+        <ns0:v>39.560001373291016</ns0:v>
       </ns0:c>
       <ns0:c r="H13">
-        <ns0:v>4.775630980400547</ns0:v>
+        <ns0:v>0.20263888546681041</ns0:v>
       </ns0:c>
       <ns0:c r="I13">
-        <ns0:v>57.68000030517578</ns0:v>
+        <ns0:v>39.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="J13">
-        <ns0:v>0.7975018759342367</ns0:v>
+        <ns0:v>-0.20181134608774354</ns0:v>
       </ns0:c>
       <ns0:c r="K13">
-        <ns0:v>1.0967174925878864</ns0:v>
+        <ns0:v>1.2126622015072908</ns0:v>
       </ns0:c>
       <ns0:c r="L13">
-        <ns0:v>69.79664834262604</ns0:v>
+        <ns0:v>78.25560752066835</ns0:v>
       </ns0:c>
       <ns0:c r="M13">
-        <ns0:v>55.348999977111816</ns0:v>
+        <ns0:v>34.998999977111815</ns0:v>
       </ns0:c>
       <ns0:c r="N13">
-        <ns0:v>53.85160011291504</ns0:v>
+        <ns0:v>34.35159996032715</ns0:v>
       </ns0:c>
       <ns0:c r="O13">
-        <ns0:v>46.772350006103515</ns0:v>
+        <ns0:v>28.05569996833801</ns0:v>
       </ns0:c>
       <ns0:c r="P13" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q13" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </ns0:c>
       <ns0:c r="T13" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BSVN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BOX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1070,59 +1070,59 @@
       </ns0:c>
       <ns0:c r="B14" t="inlineStr">
         <ns0:is>
-          <ns0:t>BZUN</ns0:t>
+          <ns0:t>BP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Baozun Inc ADR</ns0:t>
+          <ns0:t>BP plc ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Internet Retail</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국에서 통합 전자상거래 솔루션과 브랜드 관리 사업을 운영하는 기업.</ns0:t>
+          <ns0:t>전 세계에서 석유·가스 사업을 운영하며 가스·저탄소 에너지, 석유 생산 및 고객·제품 부문을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
-        <ns0:v>3.7200000286102295</ns0:v>
+        <ns0:v>50.209999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="H14">
-        <ns0:v>1.3623964925574494</ns0:v>
+        <ns0:v>3.6540060031870603</ns0:v>
       </ns0:c>
       <ns0:c r="I14">
-        <ns0:v>3.815999984741211</ns0:v>
+        <ns0:v>49.2400016784668</ns0:v>
       </ns0:c>
       <ns0:c r="J14">
-        <ns0:v>-2.515722130892295</ns0:v>
+        <ns0:v>1.9699378004490509</ns0:v>
       </ns0:c>
       <ns0:c r="K14">
-        <ns0:v>2.8233873104437137</ns0:v>
+        <ns0:v>1.2152540574944308</ns0:v>
       </ns0:c>
       <ns0:c r="L14">
-        <ns0:v>70.15213504021058</ns0:v>
+        <ns0:v>73.61850984610606</ns0:v>
       </ns0:c>
       <ns0:c r="M14">
-        <ns0:v>3.2357499837875365</ns0:v>
+        <ns0:v>45.50049991607666</ns0:v>
       </ns0:c>
       <ns0:c r="N14">
-        <ns0:v>2.989199981689453</ns0:v>
+        <ns0:v>44.58240013122558</ns0:v>
       </ns0:c>
       <ns0:c r="O14">
-        <ns0:v>2.7500250005722044</ns0:v>
+        <ns0:v>42.2493500328064</ns0:v>
       </ns0:c>
       <ns0:c r="P14" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q14" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </ns0:c>
       <ns0:c r="T14" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BZUN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1149,59 +1149,59 @@
       </ns0:c>
       <ns0:c r="B15" t="inlineStr">
         <ns0:is>
-          <ns0:t>CAKE</ns0:t>
+          <ns0:t>BSVN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Cheesecake Factory Inc</ns0:t>
+          <ns0:t>Bank7 Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Restaurants</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다에서 식당을 운영·라이선스하고, 치즈케이크 등 제과 제품을 생산·공급하는 기업.</ns0:t>
+          <ns0:t>개인·기업 고객에게 예금 등 은행·금융 서비스를 제공하는 Bank7의 은행지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
-        <ns0:v>114.91999816894531</ns0:v>
+        <ns0:v>58.13999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="H15">
-        <ns0:v>-1.432368317523125</ns0:v>
+        <ns0:v>4.775630980400547</ns0:v>
       </ns0:c>
       <ns0:c r="I15">
-        <ns0:v>118.45999908447266</ns0:v>
+        <ns0:v>57.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J15">
-        <ns0:v>-2.988351294011915</ns0:v>
+        <ns0:v>0.7975018759342367</ns0:v>
       </ns0:c>
       <ns0:c r="K15">
-        <ns0:v>0.9846638792583805</ns0:v>
+        <ns0:v>1.0969927996611606</ns0:v>
       </ns0:c>
       <ns0:c r="L15">
-        <ns0:v>65.32314158140974</ns0:v>
+        <ns0:v>69.79664834262604</ns0:v>
       </ns0:c>
       <ns0:c r="M15">
-        <ns0:v>107.85750007629395</ns0:v>
+        <ns0:v>55.348999977111816</ns0:v>
       </ns0:c>
       <ns0:c r="N15">
-        <ns0:v>107.69759994506836</ns0:v>
+        <ns0:v>53.85160011291504</ns0:v>
       </ns0:c>
       <ns0:c r="O15">
-        <ns0:v>76.91014989852906</ns0:v>
+        <ns0:v>46.772350006103515</ns0:v>
       </ns0:c>
       <ns0:c r="P15" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q15" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </ns0:c>
       <ns0:c r="T15" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CAKE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BSVN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1228,12 +1228,12 @@
       </ns0:c>
       <ns0:c r="B16" t="inlineStr">
         <ns0:is>
-          <ns0:t>CBRL</ns0:t>
+          <ns0:t>BZUN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Cracker Barrel Old Country Store Inc</ns0:t>
+          <ns0:t>Baozun Inc ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D16" t="inlineStr">
@@ -1243,44 +1243,44 @@
       </ns0:c>
       <ns0:c r="E16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Restaurants</ns0:t>
+          <ns0:t>Internet Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 선물 가게를 갖춘 Cracker Barrel 음식점을 개발·운영.</ns0:t>
+          <ns0:t>중국에서 통합 전자상거래 솔루션과 브랜드 관리 사업을 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
-        <ns0:v>68.97000122070312</ns0:v>
+        <ns0:v>3.7200000286102295</ns0:v>
       </ns0:c>
       <ns0:c r="H16">
-        <ns0:v>2.314192959272332</ns0:v>
+        <ns0:v>1.3623964925574494</ns0:v>
       </ns0:c>
       <ns0:c r="I16">
-        <ns0:v>67.58000183105469</ns0:v>
+        <ns0:v>3.815999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J16">
-        <ns0:v>2.0568205859528454</ns0:v>
+        <ns0:v>-2.515722130892295</ns0:v>
       </ns0:c>
       <ns0:c r="K16">
-        <ns0:v>1.6371324599708879</ns0:v>
+        <ns0:v>2.8246808908561007</ns0:v>
       </ns0:c>
       <ns0:c r="L16">
-        <ns0:v>79.77470260847306</ns0:v>
+        <ns0:v>70.15213504021058</ns0:v>
       </ns0:c>
       <ns0:c r="M16">
-        <ns0:v>55.43800029754639</ns0:v>
+        <ns0:v>3.2357499837875365</ns0:v>
       </ns0:c>
       <ns0:c r="N16">
-        <ns0:v>54.57860023498535</ns0:v>
+        <ns0:v>2.989199981689453</ns0:v>
       </ns0:c>
       <ns0:c r="O16">
-        <ns0:v>40.757800045013425</ns0:v>
+        <ns0:v>2.7500250005722044</ns0:v>
       </ns0:c>
       <ns0:c r="P16" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q16" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </ns0:c>
       <ns0:c r="T16" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CBRL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BZUN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1307,55 +1307,55 @@
       </ns0:c>
       <ns0:c r="B17" t="inlineStr">
         <ns0:is>
-          <ns0:t>CHT</ns0:t>
+          <ns0:t>CAKE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Chunghwa Telecom ADR</ns0:t>
+          <ns0:t>Cheesecake Factory Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Telecom Services</ns0:t>
+          <ns0:t>Restaurants</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>대만과 해외에서 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>미국·캐나다에서 식당을 운영·라이선스하고, 치즈케이크 등 제과 제품을 생산·공급하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
-        <ns0:v>47.63999938964844</ns0:v>
+        <ns0:v>114.91999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H17">
-        <ns0:v>-0.04196487164855878</ns0:v>
+        <ns0:v>-1.432368317523125</ns0:v>
       </ns0:c>
       <ns0:c r="I17">
-        <ns0:v>47.75</ns0:v>
+        <ns0:v>118.45999908447266</ns0:v>
       </ns0:c>
       <ns0:c r="J17">
-        <ns0:v>-0.23036777036976597</ns0:v>
+        <ns0:v>-2.988351294011915</ns0:v>
       </ns0:c>
       <ns0:c r="K17">
-        <ns0:v>0.8127601325212768</ns0:v>
+        <ns0:v>0.9847306849115209</ns0:v>
       </ns0:c>
       <ns0:c r="L17">
-        <ns0:v>75.91187197355978</ns0:v>
+        <ns0:v>65.32314158140974</ns0:v>
       </ns0:c>
       <ns0:c r="M17">
-        <ns0:v>46.175500106811526</ns0:v>
+        <ns0:v>107.85750007629395</ns0:v>
       </ns0:c>
       <ns0:c r="N17">
-        <ns0:v>44.62540000915527</ns0:v>
+        <ns0:v>107.69759994506836</ns0:v>
       </ns0:c>
       <ns0:c r="O17">
-        <ns0:v>43.48070001602173</ns0:v>
+        <ns0:v>76.91014989852906</ns0:v>
       </ns0:c>
       <ns0:c r="P17" t="inlineStr">
         <ns0:is>
@@ -1374,7 +1374,7 @@
       </ns0:c>
       <ns0:c r="T17" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CHT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CAKE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1386,59 +1386,59 @@
       </ns0:c>
       <ns0:c r="B18" t="inlineStr">
         <ns0:is>
-          <ns0:t>CLDT</ns0:t>
+          <ns0:t>CBRL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Chatham Lodging Trust</ns0:t>
+          <ns0:t>Cracker Barrel Old Country Store Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Real Estate</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E18" t="inlineStr">
         <ns0:is>
-          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
+          <ns0:t>Restaurants</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>고급 장기체류 호텔과 프리미엄 브랜드의 선택형 서비스 호텔에 주로 투자하는 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>미국에서 선물 가게를 갖춘 Cracker Barrel 음식점을 개발·운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
-        <ns0:v>14.050000190734863</ns0:v>
+        <ns0:v>68.97000122070312</ns0:v>
       </ns0:c>
       <ns0:c r="H18">
-        <ns0:v>-0.6364932843187066</ns0:v>
+        <ns0:v>2.314192959272332</ns0:v>
       </ns0:c>
       <ns0:c r="I18">
-        <ns0:v>14.199999809265137</ns0:v>
+        <ns0:v>67.58000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="J18">
-        <ns0:v>-1.0563353559512212</ns0:v>
+        <ns0:v>2.0568205859528454</ns0:v>
       </ns0:c>
       <ns0:c r="K18">
-        <ns0:v>1.1422842289533712</ns0:v>
+        <ns0:v>1.6372977138453635</ns0:v>
       </ns0:c>
       <ns0:c r="L18">
-        <ns0:v>64.20028470629879</ns0:v>
+        <ns0:v>79.77470260847306</ns0:v>
       </ns0:c>
       <ns0:c r="M18">
-        <ns0:v>13.571999979019164</ns0:v>
+        <ns0:v>55.43800029754639</ns0:v>
       </ns0:c>
       <ns0:c r="N18">
-        <ns0:v>13.26439998626709</ns0:v>
+        <ns0:v>54.57860023498535</ns0:v>
       </ns0:c>
       <ns0:c r="O18">
-        <ns0:v>10.542399990558625</ns0:v>
+        <ns0:v>40.757800045013425</ns0:v>
       </ns0:c>
       <ns0:c r="P18" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q18" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </ns0:c>
       <ns0:c r="T18" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CLDT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CBRL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1465,55 +1465,55 @@
       </ns0:c>
       <ns0:c r="B19" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNC</ns0:t>
+          <ns0:t>CHT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Centene Corp</ns0:t>
+          <ns0:t>Chunghwa Telecom ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare Plans</ns0:t>
+          <ns0:t>Telecom Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 보험 보장이 부족한 가정과 기업에 프로그램·서비스를 제공하는 관리형 의료 기업.</ns0:t>
+          <ns0:t>대만과 해외에서 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
-        <ns0:v>69.16000366210938</ns0:v>
+        <ns0:v>47.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="H19">
-        <ns0:v>-1.9146198173598084</ns0:v>
+        <ns0:v>-0.04196487164855878</ns0:v>
       </ns0:c>
       <ns0:c r="I19">
-        <ns0:v>71.01000213623047</ns0:v>
+        <ns0:v>47.75</ns0:v>
       </ns0:c>
       <ns0:c r="J19">
-        <ns0:v>-2.605264636623905</ns0:v>
+        <ns0:v>-0.23036777036976597</ns0:v>
       </ns0:c>
       <ns0:c r="K19">
-        <ns0:v>0.6939522876925045</ns0:v>
+        <ns0:v>0.8125855535937468</ns0:v>
       </ns0:c>
       <ns0:c r="L19">
-        <ns0:v>62.451797461583624</ns0:v>
+        <ns0:v>75.91187197355978</ns0:v>
       </ns0:c>
       <ns0:c r="M19">
-        <ns0:v>64.72300033569336</ns0:v>
+        <ns0:v>46.175500106811526</ns0:v>
       </ns0:c>
       <ns0:c r="N19">
-        <ns0:v>65.3934001159668</ns0:v>
+        <ns0:v>44.62540000915527</ns0:v>
       </ns0:c>
       <ns0:c r="O19">
-        <ns0:v>54.14669998168945</ns0:v>
+        <ns0:v>43.48070001602173</ns0:v>
       </ns0:c>
       <ns0:c r="P19" t="inlineStr">
         <ns0:is>
@@ -1532,7 +1532,7 @@
       </ns0:c>
       <ns0:c r="T19" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CNC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CHT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1544,55 +1544,55 @@
       </ns0:c>
       <ns0:c r="B20" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNK</ns0:t>
+          <ns0:t>CLDT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Cinemark Holdings Inc</ns0:t>
+          <ns0:t>Chatham Lodging Trust</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Real Estate</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Entertainment</ns0:t>
+          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 라틴아메리카에서 영화관을 운영하는 영화 상영 기업.</ns0:t>
+          <ns0:t>고급 장기체류 호텔과 프리미엄 브랜드의 선택형 서비스 호텔에 주로 투자하는 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
-        <ns0:v>38.47999954223633</ns0:v>
+        <ns0:v>14.050000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H20">
-        <ns0:v>-0.10384453544127759</ns0:v>
+        <ns0:v>-0.6364932843187066</ns0:v>
       </ns0:c>
       <ns0:c r="I20">
-        <ns0:v>39.09000015258789</ns0:v>
+        <ns0:v>14.199999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="J20">
-        <ns0:v>-1.5605029623188105</ns0:v>
+        <ns0:v>-1.0563353559512212</ns0:v>
       </ns0:c>
       <ns0:c r="K20">
-        <ns0:v>1.216671244367572</ns0:v>
+        <ns0:v>1.1422913019645289</ns0:v>
       </ns0:c>
       <ns0:c r="L20">
-        <ns0:v>62.879803006802064</ns0:v>
+        <ns0:v>64.20028470629879</ns0:v>
       </ns0:c>
       <ns0:c r="M20">
-        <ns0:v>36.98350009918213</ns0:v>
+        <ns0:v>13.571999979019164</ns0:v>
       </ns0:c>
       <ns0:c r="N20">
-        <ns0:v>36.476800231933595</ns0:v>
+        <ns0:v>13.26439998626709</ns0:v>
       </ns0:c>
       <ns0:c r="O20">
-        <ns0:v>30.490500078201293</ns0:v>
+        <ns0:v>10.542399990558625</ns0:v>
       </ns0:c>
       <ns0:c r="P20" t="inlineStr">
         <ns0:is>
@@ -1611,7 +1611,7 @@
       </ns0:c>
       <ns0:c r="T20" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CNK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CLDT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1623,59 +1623,59 @@
       </ns0:c>
       <ns0:c r="B21" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNQ</ns0:t>
+          <ns0:t>CNC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Canadian Natural Resources Ltd</ns0:t>
+          <ns0:t>Centene Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Healthcare Plans</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>미국에서 보험 보장이 부족한 가정과 기업에 프로그램·서비스를 제공하는 관리형 의료 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
-        <ns0:v>53.79999923706055</ns0:v>
+        <ns0:v>69.16000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="H21">
-        <ns0:v>3.5611134686274415</ns0:v>
+        <ns0:v>-1.9146198173598084</ns0:v>
       </ns0:c>
       <ns0:c r="I21">
-        <ns0:v>52.56999969482422</ns0:v>
+        <ns0:v>71.01000213623047</ns0:v>
       </ns0:c>
       <ns0:c r="J21">
-        <ns0:v>2.339736635679346</ns0:v>
+        <ns0:v>-2.605264636623905</ns0:v>
       </ns0:c>
       <ns0:c r="K21">
-        <ns0:v>1.5186444267634416</ns0:v>
+        <ns0:v>0.6940614953545141</ns0:v>
       </ns0:c>
       <ns0:c r="L21">
-        <ns0:v>71.78624407797888</ns0:v>
+        <ns0:v>62.451797461583624</ns0:v>
       </ns0:c>
       <ns0:c r="M21">
-        <ns0:v>48.993499755859375</ns0:v>
+        <ns0:v>64.72300033569336</ns0:v>
       </ns0:c>
       <ns0:c r="N21">
-        <ns0:v>49.4689998626709</ns0:v>
+        <ns0:v>65.3934001159668</ns0:v>
       </ns0:c>
       <ns0:c r="O21">
-        <ns0:v>44.87879987716675</ns0:v>
+        <ns0:v>54.14669998168945</ns0:v>
       </ns0:c>
       <ns0:c r="P21" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q21" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </ns0:c>
       <ns0:c r="T21" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CNQ/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CNC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1702,55 +1702,55 @@
       </ns0:c>
       <ns0:c r="B22" t="inlineStr">
         <ns0:is>
-          <ns0:t>CON</ns0:t>
+          <ns0:t>CNK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Concentra Group Holdings Parent Inc</ns0:t>
+          <ns0:t>Cinemark Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Care Facilities</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
+          <ns0:t>미국과 라틴아메리카에서 영화관을 운영하는 영화 상영 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
-        <ns0:v>38.540000915527344</ns0:v>
+        <ns0:v>38.47999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="H22">
-        <ns0:v>-1.5581113322520324</ns0:v>
+        <ns0:v>-0.10384453544127759</ns0:v>
       </ns0:c>
       <ns0:c r="I22">
-        <ns0:v>39.2400016784668</ns0:v>
+        <ns0:v>39.09000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J22">
-        <ns0:v>-1.783895853713946</ns0:v>
+        <ns0:v>-1.5605029623188105</ns0:v>
       </ns0:c>
       <ns0:c r="K22">
-        <ns0:v>1.0594725566003602</ns0:v>
+        <ns0:v>1.2216275335100077</ns0:v>
       </ns0:c>
       <ns0:c r="L22">
-        <ns0:v>70.25438728409159</ns0:v>
+        <ns0:v>62.879803006802064</ns0:v>
       </ns0:c>
       <ns0:c r="M22">
-        <ns0:v>36.14250030517578</ns0:v>
+        <ns0:v>36.98350009918213</ns0:v>
       </ns0:c>
       <ns0:c r="N22">
-        <ns0:v>35.29320014953613</ns0:v>
+        <ns0:v>36.476800231933595</ns0:v>
       </ns0:c>
       <ns0:c r="O22">
-        <ns0:v>27.504850025177003</ns0:v>
+        <ns0:v>30.490500078201293</ns0:v>
       </ns0:c>
       <ns0:c r="P22" t="inlineStr">
         <ns0:is>
@@ -1769,7 +1769,7 @@
       </ns0:c>
       <ns0:c r="T22" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CON/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CNK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1781,12 +1781,12 @@
       </ns0:c>
       <ns0:c r="B23" t="inlineStr">
         <ns0:is>
-          <ns0:t>COP</ns0:t>
+          <ns0:t>CNQ</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Conoco Phillips</ns0:t>
+          <ns0:t>Canadian Natural Resources Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D23" t="inlineStr">
@@ -1801,35 +1801,35 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매하는 기업.</ns0:t>
+          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
-        <ns0:v>146.50999450683594</ns0:v>
+        <ns0:v>53.79999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="H23">
-        <ns0:v>3.3726091324280505</ns0:v>
+        <ns0:v>3.5611134686274415</ns0:v>
       </ns0:c>
       <ns0:c r="I23">
-        <ns0:v>143.1300048828125</ns0:v>
+        <ns0:v>52.56999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="J23">
-        <ns0:v>2.3614822250518364</ns0:v>
+        <ns0:v>2.339736635679346</ns0:v>
       </ns0:c>
       <ns0:c r="K23">
-        <ns0:v>1.158382986205318</ns0:v>
+        <ns0:v>1.6154839792941464</ns0:v>
       </ns0:c>
       <ns0:c r="L23">
-        <ns0:v>74.70966007110981</ns0:v>
+        <ns0:v>71.78624407797888</ns0:v>
       </ns0:c>
       <ns0:c r="M23">
-        <ns0:v>131.64449882507324</ns0:v>
+        <ns0:v>48.993499755859375</ns0:v>
       </ns0:c>
       <ns0:c r="N23">
-        <ns0:v>131.77219940185546</ns0:v>
+        <ns0:v>49.4689998626709</ns0:v>
       </ns0:c>
       <ns0:c r="O23">
-        <ns0:v>118.7269500732422</ns0:v>
+        <ns0:v>44.87879987716675</ns0:v>
       </ns0:c>
       <ns0:c r="P23" t="inlineStr">
         <ns0:is>
@@ -1848,7 +1848,7 @@
       </ns0:c>
       <ns0:c r="T23" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/COP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CNQ/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1860,59 +1860,59 @@
       </ns0:c>
       <ns0:c r="B24" t="inlineStr">
         <ns0:is>
-          <ns0:t>CVX</ns0:t>
+          <ns0:t>CON</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Chevron Corp</ns0:t>
+          <ns0:t>Concentra Group Holdings Parent Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Medical Care Facilities</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·천연가스 탐사, 개발, 생산, 운송 등을 포함한 통합 에너지 및 화학 사업을 영위.</ns0:t>
+          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
-        <ns0:v>224.99000549316406</ns0:v>
+        <ns0:v>38.540000915527344</ns0:v>
       </ns0:c>
       <ns0:c r="H24">
-        <ns0:v>2.585262620643358</ns0:v>
+        <ns0:v>-1.5581113322520324</ns0:v>
       </ns0:c>
       <ns0:c r="I24">
-        <ns0:v>223.4600067138672</ns0:v>
+        <ns0:v>39.2400016784668</ns0:v>
       </ns0:c>
       <ns0:c r="J24">
-        <ns0:v>0.6846857304788179</ns0:v>
+        <ns0:v>-1.783895853713946</ns0:v>
       </ns0:c>
       <ns0:c r="K24">
-        <ns0:v>0.9251317342181823</ns0:v>
+        <ns0:v>1.0596839567605365</ns0:v>
       </ns0:c>
       <ns0:c r="L24">
-        <ns0:v>70.77157518954888</ns0:v>
+        <ns0:v>70.25438728409159</ns0:v>
       </ns0:c>
       <ns0:c r="M24">
-        <ns0:v>209.6125</ns0:v>
+        <ns0:v>36.14250030517578</ns0:v>
       </ns0:c>
       <ns0:c r="N24">
-        <ns0:v>207.1324005126953</ns0:v>
+        <ns0:v>35.29320014953613</ns0:v>
       </ns0:c>
       <ns0:c r="O24">
-        <ns0:v>189.86540000915528</ns0:v>
+        <ns0:v>27.504850025177003</ns0:v>
       </ns0:c>
       <ns0:c r="P24" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q24" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </ns0:c>
       <ns0:c r="T24" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CVX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CON/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1939,59 +1939,59 @@
       </ns0:c>
       <ns0:c r="B25" t="inlineStr">
         <ns0:is>
-          <ns0:t>DCBO</ns0:t>
+          <ns0:t>COP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Docebo Inc</ns0:t>
+          <ns0:t>Conoco Phillips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 및 해외에서 교육용 클라우드 학습관리 플랫폼을 개발·제공하는 기업.</ns0:t>
+          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
-        <ns0:v>27.59000015258789</ns0:v>
+        <ns0:v>146.50999450683594</ns0:v>
       </ns0:c>
       <ns0:c r="H25">
-        <ns0:v>-1.8847819019480405</ns0:v>
+        <ns0:v>3.3726091324280505</ns0:v>
       </ns0:c>
       <ns0:c r="I25">
-        <ns0:v>28.719999313354492</ns0:v>
+        <ns0:v>143.1300048828125</ns0:v>
       </ns0:c>
       <ns0:c r="J25">
-        <ns0:v>-3.934537561918272</ns0:v>
+        <ns0:v>2.3614822250518364</ns0:v>
       </ns0:c>
       <ns0:c r="K25">
-        <ns0:v>1.578008510638298</ns0:v>
+        <ns0:v>1.1771936818204554</ns0:v>
       </ns0:c>
       <ns0:c r="L25">
-        <ns0:v>70.2032075494698</ns0:v>
+        <ns0:v>74.70966007110981</ns0:v>
       </ns0:c>
       <ns0:c r="M25">
-        <ns0:v>24.335500049591065</ns0:v>
+        <ns0:v>131.64449882507324</ns0:v>
       </ns0:c>
       <ns0:c r="N25">
-        <ns0:v>24.169700088500978</ns0:v>
+        <ns0:v>131.77219940185546</ns0:v>
       </ns0:c>
       <ns0:c r="O25">
-        <ns0:v>20.034625005722045</ns0:v>
+        <ns0:v>118.7269500732422</ns0:v>
       </ns0:c>
       <ns0:c r="P25" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q25" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </ns0:c>
       <ns0:c r="T25" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DCBO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/COP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2018,59 +2018,59 @@
       </ns0:c>
       <ns0:c r="B26" t="inlineStr">
         <ns0:is>
-          <ns0:t>DDI</ns0:t>
+          <ns0:t>CVX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C26" t="inlineStr">
         <ns0:is>
-          <ns0:t>DoubleDown Interactive Co Ltd ADR</ns0:t>
+          <ns0:t>Chevron Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronic Gaming &amp; Multimedia</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>한국·미국 등에서 캐주얼 게임과 모바일 앱을 개발·배급하며 소셜 카지노 게임 및 iGaming 사업 운영.</ns0:t>
+          <ns0:t>원유·천연가스 탐사, 개발, 생산, 운송 등을 포함한 통합 에너지 및 화학 사업을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
-        <ns0:v>13.800000190734863</ns0:v>
+        <ns0:v>224.99000549316406</ns0:v>
       </ns0:c>
       <ns0:c r="H26">
-        <ns0:v>0.5464466825545244</ns0:v>
+        <ns0:v>2.585262620643358</ns0:v>
       </ns0:c>
       <ns0:c r="I26">
-        <ns0:v>13.89900016784668</ns0:v>
+        <ns0:v>223.4600067138672</ns0:v>
       </ns0:c>
       <ns0:c r="J26">
-        <ns0:v>-0.7122812858211036</ns0:v>
+        <ns0:v>0.6846857304788179</ns0:v>
       </ns0:c>
       <ns0:c r="K26">
-        <ns0:v>1.1789791690643343</ns0:v>
+        <ns0:v>0.9261916622675599</ns0:v>
       </ns0:c>
       <ns0:c r="L26">
-        <ns0:v>73.0400759490071</ns0:v>
+        <ns0:v>70.77157518954888</ns0:v>
       </ns0:c>
       <ns0:c r="M26">
-        <ns0:v>13.352250003814698</ns0:v>
+        <ns0:v>209.6125</ns0:v>
       </ns0:c>
       <ns0:c r="N26">
-        <ns0:v>12.939300003051757</ns0:v>
+        <ns0:v>207.1324005126953</ns0:v>
       </ns0:c>
       <ns0:c r="O26">
-        <ns0:v>10.786599979400634</ns0:v>
+        <ns0:v>189.86540000915528</ns0:v>
       </ns0:c>
       <ns0:c r="P26" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q26" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </ns0:c>
       <ns0:c r="T26" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DDI/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CVX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2097,12 +2097,12 @@
       </ns0:c>
       <ns0:c r="B27" t="inlineStr">
         <ns0:is>
-          <ns0:t>DOCU</ns0:t>
+          <ns0:t>DCBO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C27" t="inlineStr">
         <ns0:is>
-          <ns0:t>DocuSign Inc</ns0:t>
+          <ns0:t>Docebo Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D27" t="inlineStr">
@@ -2117,35 +2117,35 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 전자서명 솔루션과 계약 전 과정의 분석·자동화를 위한 AI 계약관리 플랫폼을 제공.</ns0:t>
+          <ns0:t>캐나다·미국 및 해외에서 교육용 클라우드 학습관리 플랫폼을 개발·제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
-        <ns0:v>74.6500015258789</ns0:v>
+        <ns0:v>27.59000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H27">
-        <ns0:v>-3.702264243382425</ns0:v>
+        <ns0:v>-1.8847819019480405</ns0:v>
       </ns0:c>
       <ns0:c r="I27">
-        <ns0:v>77.5999984741211</ns0:v>
+        <ns0:v>28.719999313354492</ns0:v>
       </ns0:c>
       <ns0:c r="J27">
-        <ns0:v>-3.8015425338261855</ns0:v>
+        <ns0:v>-3.934537561918272</ns0:v>
       </ns0:c>
       <ns0:c r="K27">
-        <ns0:v>0.7495865814643663</ns0:v>
+        <ns0:v>1.5795744680851065</ns0:v>
       </ns0:c>
       <ns0:c r="L27">
-        <ns0:v>62.63853843566962</ns0:v>
+        <ns0:v>70.2032075494698</ns0:v>
       </ns0:c>
       <ns0:c r="M27">
-        <ns0:v>70.07550048828125</ns0:v>
+        <ns0:v>24.335500049591065</ns0:v>
       </ns0:c>
       <ns0:c r="N27">
-        <ns0:v>66.4962001800537</ns0:v>
+        <ns0:v>24.169700088500978</ns0:v>
       </ns0:c>
       <ns0:c r="O27">
-        <ns0:v>53.79769998550415</ns0:v>
+        <ns0:v>20.034625005722045</ns0:v>
       </ns0:c>
       <ns0:c r="P27" t="inlineStr">
         <ns0:is>
@@ -2164,7 +2164,7 @@
       </ns0:c>
       <ns0:c r="T27" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DOCU/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DCBO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2176,59 +2176,59 @@
       </ns0:c>
       <ns0:c r="B28" t="inlineStr">
         <ns0:is>
-          <ns0:t>E</ns0:t>
+          <ns0:t>DDI</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Eni Spa ADR</ns0:t>
+          <ns0:t>DoubleDown Interactive Co Ltd ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Electronic Gaming &amp; Multimedia</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 원유·천연가스 탐사·개발·채굴·제조·거래·판매를 하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>한국·미국 등에서 캐주얼 게임과 모바일 앱을 개발·배급하며 소셜 카지노 게임 및 iGaming 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
-        <ns0:v>59.099998474121094</ns0:v>
+        <ns0:v>13.800000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H28">
-        <ns0:v>2.8899719482935904</ns0:v>
+        <ns0:v>0.5464466825545244</ns0:v>
       </ns0:c>
       <ns0:c r="I28">
-        <ns0:v>58.0</ns0:v>
+        <ns0:v>13.89900016784668</ns0:v>
       </ns0:c>
       <ns0:c r="J28">
-        <ns0:v>1.8965490933122275</ns0:v>
+        <ns0:v>-0.7122812858211036</ns0:v>
       </ns0:c>
       <ns0:c r="K28">
-        <ns0:v>0.9122049585817702</ns0:v>
+        <ns0:v>1.1808033145356198</ns0:v>
       </ns0:c>
       <ns0:c r="L28">
-        <ns0:v>68.92342991041936</ns0:v>
+        <ns0:v>73.0400759490071</ns0:v>
       </ns0:c>
       <ns0:c r="M28">
-        <ns0:v>55.44049968719482</ns0:v>
+        <ns0:v>13.352250003814698</ns0:v>
       </ns0:c>
       <ns0:c r="N28">
-        <ns0:v>55.274399795532226</ns0:v>
+        <ns0:v>12.939300003051757</ns0:v>
       </ns0:c>
       <ns0:c r="O28">
-        <ns0:v>50.85870008468628</ns0:v>
+        <ns0:v>10.786599979400634</ns0:v>
       </ns0:c>
       <ns0:c r="P28" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q28" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </ns0:c>
       <ns0:c r="T28" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/E/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DDI/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2255,59 +2255,59 @@
       </ns0:c>
       <ns0:c r="B29" t="inlineStr">
         <ns0:is>
-          <ns0:t>EOG</ns0:t>
+          <ns0:t>DOCU</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C29" t="inlineStr">
         <ns0:is>
-          <ns0:t>EOG Resources Inc</ns0:t>
+          <ns0:t>DocuSign Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 전자서명 솔루션과 계약 전 과정의 분석·자동화를 위한 AI 계약관리 플랫폼을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
-        <ns0:v>158.00999450683594</ns0:v>
+        <ns0:v>74.6500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H29">
-        <ns0:v>3.5316469414835128</ns0:v>
+        <ns0:v>-3.702264243382425</ns0:v>
       </ns0:c>
       <ns0:c r="I29">
-        <ns0:v>155.0</ns0:v>
+        <ns0:v>77.5999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J29">
-        <ns0:v>1.9419319398941592</ns0:v>
+        <ns0:v>-3.8015425338261855</ns0:v>
       </ns0:c>
       <ns0:c r="K29">
-        <ns0:v>1.7366315444489964</ns0:v>
+        <ns0:v>0.771350864285301</ns0:v>
       </ns0:c>
       <ns0:c r="L29">
-        <ns0:v>70.26292002532578</ns0:v>
+        <ns0:v>62.63853843566962</ns0:v>
       </ns0:c>
       <ns0:c r="M29">
-        <ns0:v>145.22150039672852</ns0:v>
+        <ns0:v>70.07550048828125</ns0:v>
       </ns0:c>
       <ns0:c r="N29">
-        <ns0:v>145.77540069580078</ns0:v>
+        <ns0:v>66.4962001800537</ns0:v>
       </ns0:c>
       <ns0:c r="O29">
-        <ns0:v>134.32284984588622</ns0:v>
+        <ns0:v>53.79769998550415</ns0:v>
       </ns0:c>
       <ns0:c r="P29" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q29" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </ns0:c>
       <ns0:c r="T29" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/EOG/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DOCU/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2334,12 +2334,12 @@
       </ns0:c>
       <ns0:c r="B30" t="inlineStr">
         <ns0:is>
-          <ns0:t>EQNR</ns0:t>
+          <ns0:t>E</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Equinor ASA ADR</ns0:t>
+          <ns0:t>Eni Spa ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D30" t="inlineStr">
@@ -2354,35 +2354,35 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>노르웨이와 해외에서 탐사·생산, 마케팅·미드스트림·가공, 재생에너지 사업을 하는 기업.</ns0:t>
+          <ns0:t>세계 각지에서 원유·천연가스 탐사·개발·채굴·제조·거래·판매를 하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
-        <ns0:v>46.97999954223633</ns0:v>
+        <ns0:v>59.099998474121094</ns0:v>
       </ns0:c>
       <ns0:c r="H30">
-        <ns0:v>4.585933787315155</ns0:v>
+        <ns0:v>2.8899719482935904</ns0:v>
       </ns0:c>
       <ns0:c r="I30">
-        <ns0:v>45.84000015258789</ns0:v>
+        <ns0:v>58.0</ns0:v>
       </ns0:c>
       <ns0:c r="J30">
-        <ns0:v>2.486909655003733</ns0:v>
+        <ns0:v>1.8965490933122275</ns0:v>
       </ns0:c>
       <ns0:c r="K30">
-        <ns0:v>1.044384256365183</ns0:v>
+        <ns0:v>0.9122165643904774</ns0:v>
       </ns0:c>
       <ns0:c r="L30">
-        <ns0:v>67.69427757759098</ns0:v>
+        <ns0:v>68.92342991041936</ns0:v>
       </ns0:c>
       <ns0:c r="M30">
-        <ns0:v>43.077999687194826</ns0:v>
+        <ns0:v>55.44049968719482</ns0:v>
       </ns0:c>
       <ns0:c r="N30">
-        <ns0:v>42.81479995727539</ns0:v>
+        <ns0:v>55.274399795532226</ns0:v>
       </ns0:c>
       <ns0:c r="O30">
-        <ns0:v>36.42074989318848</ns0:v>
+        <ns0:v>50.85870008468628</ns0:v>
       </ns0:c>
       <ns0:c r="P30" t="inlineStr">
         <ns0:is>
@@ -2401,7 +2401,7 @@
       </ns0:c>
       <ns0:c r="T30" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/EQNR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/E/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2413,59 +2413,59 @@
       </ns0:c>
       <ns0:c r="B31" t="inlineStr">
         <ns0:is>
-          <ns0:t>ETSY</ns0:t>
+          <ns0:t>EOG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Etsy Inc</ns0:t>
+          <ns0:t>EOG Resources Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Internet Retail</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 구매자와 판매자를 연결하는 Etsy·Depop 온라인 마켓플레이스를 운영하는 기업.</ns0:t>
+          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
-        <ns0:v>85.13999938964844</ns0:v>
+        <ns0:v>158.00999450683594</ns0:v>
       </ns0:c>
       <ns0:c r="H31">
-        <ns0:v>-4.530164724940988</ns0:v>
+        <ns0:v>3.5316469414835128</ns0:v>
       </ns0:c>
       <ns0:c r="I31">
-        <ns0:v>90.12999725341797</ns0:v>
+        <ns0:v>155.0</ns0:v>
       </ns0:c>
       <ns0:c r="J31">
-        <ns0:v>-5.536445152371616</ns0:v>
+        <ns0:v>1.9419319398941592</ns0:v>
       </ns0:c>
       <ns0:c r="K31">
-        <ns0:v>1.495918650717449</ns0:v>
+        <ns0:v>1.7367308480131094</ns0:v>
       </ns0:c>
       <ns0:c r="L31">
-        <ns0:v>65.60678483302902</ns0:v>
+        <ns0:v>70.26292002532578</ns0:v>
       </ns0:c>
       <ns0:c r="M31">
-        <ns0:v>74.70599937438965</ns0:v>
+        <ns0:v>145.22150039672852</ns0:v>
       </ns0:c>
       <ns0:c r="N31">
-        <ns0:v>77.18219970703124</ns0:v>
+        <ns0:v>145.77540069580078</ns0:v>
       </ns0:c>
       <ns0:c r="O31">
-        <ns0:v>66.82935005187989</ns0:v>
+        <ns0:v>134.32284984588622</ns0:v>
       </ns0:c>
       <ns0:c r="P31" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q31" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </ns0:c>
       <ns0:c r="T31" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ETSY/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/EOG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2492,59 +2492,59 @@
       </ns0:c>
       <ns0:c r="B32" t="inlineStr">
         <ns0:is>
-          <ns0:t>EXEL</ns0:t>
+          <ns0:t>EQNR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Exelixis Inc</ns0:t>
+          <ns0:t>Equinor ASA ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 난치성 암 신약의 발굴·개발·상용화에 집중하는 항암제 기업.</ns0:t>
+          <ns0:t>노르웨이와 해외에서 탐사·생산, 마케팅·미드스트림·가공, 재생에너지 사업을 하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
-        <ns0:v>62.22999954223633</ns0:v>
+        <ns0:v>46.97999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="H32">
-        <ns0:v>-0.9549614377407201</ns0:v>
+        <ns0:v>4.585933787315155</ns0:v>
       </ns0:c>
       <ns0:c r="I32">
-        <ns0:v>63.310001373291016</ns0:v>
+        <ns0:v>45.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J32">
-        <ns0:v>-1.7058944994910674</ns0:v>
+        <ns0:v>2.486909655003733</ns0:v>
       </ns0:c>
       <ns0:c r="K32">
-        <ns0:v>1.0966668953744882</ns0:v>
+        <ns0:v>1.0444446533401641</ns0:v>
       </ns0:c>
       <ns0:c r="L32">
-        <ns0:v>67.9175725380741</ns0:v>
+        <ns0:v>67.69427757759098</ns0:v>
       </ns0:c>
       <ns0:c r="M32">
-        <ns0:v>58.992500114440915</ns0:v>
+        <ns0:v>43.077999687194826</ns0:v>
       </ns0:c>
       <ns0:c r="N32">
-        <ns0:v>56.79220001220703</ns0:v>
+        <ns0:v>42.81479995727539</ns0:v>
       </ns0:c>
       <ns0:c r="O32">
-        <ns0:v>49.84970001220703</ns0:v>
+        <ns0:v>36.42074989318848</ns0:v>
       </ns0:c>
       <ns0:c r="P32" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q32" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </ns0:c>
       <ns0:c r="T32" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/EXEL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/EQNR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2571,55 +2571,55 @@
       </ns0:c>
       <ns0:c r="B33" t="inlineStr">
         <ns0:is>
-          <ns0:t>EXPD</ns0:t>
+          <ns0:t>ETSY</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Expeditors International Of Washington Inc</ns0:t>
+          <ns0:t>Etsy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Integrated Freight &amp; Logistics</ns0:t>
+          <ns0:t>Internet Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>미주·아시아·유럽·중동·아프리카 등에서 항공·해상 화물 운송을 포함한 물류 서비스를 제공.</ns0:t>
+          <ns0:t>미국·영국 등에서 구매자와 판매자를 연결하는 Etsy·Depop 온라인 마켓플레이스를 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
-        <ns0:v>195.91000366210938</ns0:v>
+        <ns0:v>85.13999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="H33">
-        <ns0:v>-1.3743434031048052</ns0:v>
+        <ns0:v>-4.530164724940988</ns0:v>
       </ns0:c>
       <ns0:c r="I33">
-        <ns0:v>199.11000061035156</ns0:v>
+        <ns0:v>90.12999725341797</ns0:v>
       </ns0:c>
       <ns0:c r="J33">
-        <ns0:v>-1.6071502879980493</ns0:v>
+        <ns0:v>-5.536445152371616</ns0:v>
       </ns0:c>
       <ns0:c r="K33">
-        <ns0:v>1.0654444365362796</ns0:v>
+        <ns0:v>1.4959925079248784</ns0:v>
       </ns0:c>
       <ns0:c r="L33">
-        <ns0:v>58.869670277620564</ns0:v>
+        <ns0:v>65.60678483302902</ns0:v>
       </ns0:c>
       <ns0:c r="M33">
-        <ns0:v>191.17950210571288</ns0:v>
+        <ns0:v>74.70599937438965</ns0:v>
       </ns0:c>
       <ns0:c r="N33">
-        <ns0:v>189.03940124511718</ns0:v>
+        <ns0:v>77.18219970703124</ns0:v>
       </ns0:c>
       <ns0:c r="O33">
-        <ns0:v>164.87020011901856</ns0:v>
+        <ns0:v>66.82935005187989</ns0:v>
       </ns0:c>
       <ns0:c r="P33" t="inlineStr">
         <ns0:is>
@@ -2638,7 +2638,7 @@
       </ns0:c>
       <ns0:c r="T33" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/EXPD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ETSY/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2650,55 +2650,55 @@
       </ns0:c>
       <ns0:c r="B34" t="inlineStr">
         <ns0:is>
-          <ns0:t>FDBC</ns0:t>
+          <ns0:t>EXEL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Fidelity D&amp;D Bancorp Inc</ns0:t>
+          <ns0:t>Exelixis Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·소기업·기업 고객에게 은행·신탁·금융 서비스를 제공하는 은행을 보유한 지주회사.</ns0:t>
+          <ns0:t>미국에서 난치성 암 신약의 발굴·개발·상용화에 집중하는 항암제 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
-        <ns0:v>58.150001525878906</ns0:v>
+        <ns0:v>62.22999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="H34">
-        <ns0:v>0.5359636453547756</ns0:v>
+        <ns0:v>-0.9549614377407201</ns0:v>
       </ns0:c>
       <ns0:c r="I34">
-        <ns0:v>58.77000045776367</ns0:v>
+        <ns0:v>63.310001373291016</ns0:v>
       </ns0:c>
       <ns0:c r="J34">
-        <ns0:v>-1.054958187945465</ns0:v>
+        <ns0:v>-1.7058944994910674</ns0:v>
       </ns0:c>
       <ns0:c r="K34">
-        <ns0:v>1.0785961871750434</ns0:v>
+        <ns0:v>1.0966747961901435</ns0:v>
       </ns0:c>
       <ns0:c r="L34">
-        <ns0:v>62.960298013339795</ns0:v>
+        <ns0:v>67.9175725380741</ns0:v>
       </ns0:c>
       <ns0:c r="M34">
-        <ns0:v>55.612999725341794</ns0:v>
+        <ns0:v>58.992500114440915</ns0:v>
       </ns0:c>
       <ns0:c r="N34">
-        <ns0:v>54.890400085449215</ns0:v>
+        <ns0:v>56.79220001220703</ns0:v>
       </ns0:c>
       <ns0:c r="O34">
-        <ns0:v>48.73384994506836</ns0:v>
+        <ns0:v>49.84970001220703</ns0:v>
       </ns0:c>
       <ns0:c r="P34" t="inlineStr">
         <ns0:is>
@@ -2717,7 +2717,7 @@
       </ns0:c>
       <ns0:c r="T34" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FDBC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/EXEL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2729,55 +2729,55 @@
       </ns0:c>
       <ns0:c r="B35" t="inlineStr">
         <ns0:is>
-          <ns0:t>FIGS</ns0:t>
+          <ns0:t>EXPD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Figs Inc</ns0:t>
+          <ns0:t>Expeditors International Of Washington Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Manufacturing</ns0:t>
+          <ns0:t>Integrated Freight &amp; Logistics</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 의료용 의류, 신발 등 생활용품을 소비자에게 직접 판매하는 기업.</ns0:t>
+          <ns0:t>미주·아시아·유럽·중동·아프리카 등에서 항공·해상 화물 운송을 포함한 물류 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
-        <ns0:v>19.1200008392334</ns0:v>
+        <ns0:v>195.91000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="H35">
-        <ns0:v>-2.1494373419409296</ns0:v>
+        <ns0:v>-1.3743434031048052</ns0:v>
       </ns0:c>
       <ns0:c r="I35">
-        <ns0:v>19.709999084472656</ns0:v>
+        <ns0:v>199.11000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="J35">
-        <ns0:v>-2.9933955994145722</ns0:v>
+        <ns0:v>-1.6071502879980493</ns0:v>
       </ns0:c>
       <ns0:c r="K35">
-        <ns0:v>1.3264386660406775</ns0:v>
+        <ns0:v>1.0707003889421527</ns0:v>
       </ns0:c>
       <ns0:c r="L35">
-        <ns0:v>76.83132133191135</ns0:v>
+        <ns0:v>58.869670277620564</ns0:v>
       </ns0:c>
       <ns0:c r="M35">
-        <ns0:v>14.934000062942506</ns0:v>
+        <ns0:v>191.17950210571288</ns0:v>
       </ns0:c>
       <ns0:c r="N35">
-        <ns0:v>14.559600067138671</ns0:v>
+        <ns0:v>189.03940124511718</ns0:v>
       </ns0:c>
       <ns0:c r="O35">
-        <ns0:v>13.010050015449524</ns0:v>
+        <ns0:v>164.87020011901856</ns0:v>
       </ns0:c>
       <ns0:c r="P35" t="inlineStr">
         <ns0:is>
@@ -2796,7 +2796,7 @@
       </ns0:c>
       <ns0:c r="T35" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FIGS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/EXPD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2808,12 +2808,12 @@
       </ns0:c>
       <ns0:c r="B36" t="inlineStr">
         <ns0:is>
-          <ns0:t>FRHC</ns0:t>
+          <ns0:t>FDBC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Freedom Holding Corp</ns0:t>
+          <ns0:t>Fidelity D&amp;D Bancorp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D36" t="inlineStr">
@@ -2823,44 +2823,44 @@
       </ns0:c>
       <ns0:c r="E36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial Conglomerates</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>증권 중개·매매, 시장조성, 투자 리서치·자문, 소매·상업은행 및 보험 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>개인·소기업·기업 고객에게 은행·신탁·금융 서비스를 제공하는 은행을 보유한 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
-        <ns0:v>181.57000732421875</ns0:v>
+        <ns0:v>58.150001525878906</ns0:v>
       </ns0:c>
       <ns0:c r="H36">
-        <ns0:v>0.6541426567785891</ns0:v>
+        <ns0:v>0.5359636453547756</ns0:v>
       </ns0:c>
       <ns0:c r="I36">
-        <ns0:v>181.0</ns0:v>
+        <ns0:v>58.77000045776367</ns0:v>
       </ns0:c>
       <ns0:c r="J36">
-        <ns0:v>0.3149211736015234</ns0:v>
+        <ns0:v>-1.054958187945465</ns0:v>
       </ns0:c>
       <ns0:c r="K36">
-        <ns0:v>1.4886373572990041</ns0:v>
+        <ns0:v>1.074523396880416</ns0:v>
       </ns0:c>
       <ns0:c r="L36">
-        <ns0:v>63.19573236900714</ns0:v>
+        <ns0:v>62.960298013339795</ns0:v>
       </ns0:c>
       <ns0:c r="M36">
-        <ns0:v>173.06199951171874</ns0:v>
+        <ns0:v>55.612999725341794</ns0:v>
       </ns0:c>
       <ns0:c r="N36">
-        <ns0:v>166.42759979248046</ns0:v>
+        <ns0:v>54.890400085449215</ns0:v>
       </ns0:c>
       <ns0:c r="O36">
-        <ns0:v>146.55034980773925</ns0:v>
+        <ns0:v>48.73384994506836</ns0:v>
       </ns0:c>
       <ns0:c r="P36" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q36" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </ns0:c>
       <ns0:c r="T36" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FRHC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FDBC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2887,55 +2887,55 @@
       </ns0:c>
       <ns0:c r="B37" t="inlineStr">
         <ns0:is>
-          <ns0:t>FRSH</ns0:t>
+          <ns0:t>FIGS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Freshworks Inc</ns0:t>
+          <ns0:t>Figs Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Apparel Manufacturing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 고객 경험과 직원 경험을 위한 서비스형 소프트웨어를 제공한다.</ns0:t>
+          <ns0:t>미국과 해외에서 의료용 의류, 신발 등 생활용품을 소비자에게 직접 판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
-        <ns0:v>13.739999771118164</ns0:v>
+        <ns0:v>19.1200008392334</ns0:v>
       </ns0:c>
       <ns0:c r="H37">
-        <ns0:v>-3.578948974609375</ns0:v>
+        <ns0:v>-2.1494373419409296</ns0:v>
       </ns0:c>
       <ns0:c r="I37">
-        <ns0:v>14.520000457763672</ns0:v>
+        <ns0:v>19.709999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="J37">
-        <ns0:v>-5.371905386052866</ns0:v>
+        <ns0:v>-2.9933955994145722</ns0:v>
       </ns0:c>
       <ns0:c r="K37">
-        <ns0:v>0.4492968332442544</ns0:v>
+        <ns0:v>1.3270299244544983</ns0:v>
       </ns0:c>
       <ns0:c r="L37">
-        <ns0:v>57.56155034216455</ns0:v>
+        <ns0:v>76.83132133191135</ns0:v>
       </ns0:c>
       <ns0:c r="M37">
-        <ns0:v>13.22799997329712</ns0:v>
+        <ns0:v>14.934000062942506</ns0:v>
       </ns0:c>
       <ns0:c r="N37">
-        <ns0:v>12.908299942016601</ns0:v>
+        <ns0:v>14.559600067138671</ns0:v>
       </ns0:c>
       <ns0:c r="O37">
-        <ns0:v>10.267374985218048</ns0:v>
+        <ns0:v>13.010050015449524</ns0:v>
       </ns0:c>
       <ns0:c r="P37" t="inlineStr">
         <ns0:is>
@@ -2954,7 +2954,7 @@
       </ns0:c>
       <ns0:c r="T37" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FRSH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FIGS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2966,59 +2966,59 @@
       </ns0:c>
       <ns0:c r="B38" t="inlineStr">
         <ns0:is>
-          <ns0:t>HALO</ns0:t>
+          <ns0:t>FRHC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Halozyme Therapeutics Inc</ns0:t>
+          <ns0:t>Freedom Holding Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Financial Conglomerates</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>독자 효소와 기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
+          <ns0:t>증권 중개·매매, 시장조성, 투자 리서치·자문, 소매·상업은행 및 보험 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
-        <ns0:v>121.83999633789062</ns0:v>
+        <ns0:v>181.57000732421875</ns0:v>
       </ns0:c>
       <ns0:c r="H38">
-        <ns0:v>0.27157780911746254</ns0:v>
+        <ns0:v>0.6541426567785891</ns0:v>
       </ns0:c>
       <ns0:c r="I38">
-        <ns0:v>122.33000183105469</ns0:v>
+        <ns0:v>181.0</ns0:v>
       </ns0:c>
       <ns0:c r="J38">
-        <ns0:v>-0.400560357908597</ns0:v>
+        <ns0:v>0.3149211736015234</ns0:v>
       </ns0:c>
       <ns0:c r="K38">
-        <ns0:v>0.7128286765297441</ns0:v>
+        <ns0:v>1.4884624726742774</ns0:v>
       </ns0:c>
       <ns0:c r="L38">
-        <ns0:v>70.34266370873462</ns0:v>
+        <ns0:v>63.19573236900714</ns0:v>
       </ns0:c>
       <ns0:c r="M38">
-        <ns0:v>112.48699989318848</ns0:v>
+        <ns0:v>173.06199951171874</ns0:v>
       </ns0:c>
       <ns0:c r="N38">
-        <ns0:v>108.91580017089844</ns0:v>
+        <ns0:v>166.42759979248046</ns0:v>
       </ns0:c>
       <ns0:c r="O38">
-        <ns0:v>80.61185024261475</ns0:v>
+        <ns0:v>146.55034980773925</ns0:v>
       </ns0:c>
       <ns0:c r="P38" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q38" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </ns0:c>
       <ns0:c r="T38" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HALO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FRHC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3045,55 +3045,55 @@
       </ns0:c>
       <ns0:c r="B39" t="inlineStr">
         <ns0:is>
-          <ns0:t>HGTY</ns0:t>
+          <ns0:t>FRSH</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hagerty Inc</ns0:t>
+          <ns0:t>Freshworks Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험을 제공하며 보험·마켓플레이스 부문을 운영.</ns0:t>
+          <ns0:t>전 세계에 고객 경험과 직원 경험을 위한 서비스형 소프트웨어를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
-        <ns0:v>15.300000190734863</ns0:v>
+        <ns0:v>13.739999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="H39">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>-3.578948974609375</ns0:v>
       </ns0:c>
       <ns0:c r="I39">
-        <ns0:v>15.350000381469727</ns0:v>
+        <ns0:v>14.520000457763672</ns0:v>
       </ns0:c>
       <ns0:c r="J39">
-        <ns0:v>-0.32573413350023284</ns0:v>
+        <ns0:v>-5.371905386052866</ns0:v>
       </ns0:c>
       <ns0:c r="K39">
-        <ns0:v>0.8788548097498585</ns0:v>
+        <ns0:v>0.45530464991982894</ns0:v>
       </ns0:c>
       <ns0:c r="L39">
-        <ns0:v>80.02906298207856</ns0:v>
+        <ns0:v>57.56155034216455</ns0:v>
       </ns0:c>
       <ns0:c r="M39">
-        <ns0:v>14.029000043869019</ns0:v>
+        <ns0:v>13.22799997329712</ns0:v>
       </ns0:c>
       <ns0:c r="N39">
-        <ns0:v>13.602999992370606</ns0:v>
+        <ns0:v>12.908299942016601</ns0:v>
       </ns0:c>
       <ns0:c r="O39">
-        <ns0:v>11.909549989700317</ns0:v>
+        <ns0:v>10.267374985218048</ns0:v>
       </ns0:c>
       <ns0:c r="P39" t="inlineStr">
         <ns0:is>
@@ -3112,7 +3112,7 @@
       </ns0:c>
       <ns0:c r="T39" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HGTY/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FRSH/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3124,59 +3124,59 @@
       </ns0:c>
       <ns0:c r="B40" t="inlineStr">
         <ns0:is>
-          <ns0:t>HMC</ns0:t>
+          <ns0:t>HALO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Honda Motor ADR</ns0:t>
+          <ns0:t>Halozyme Therapeutics Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Auto Manufacturers</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>독자 효소와 기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
-        <ns0:v>34.279998779296875</ns0:v>
+        <ns0:v>121.83999633789062</ns0:v>
       </ns0:c>
       <ns0:c r="H40">
-        <ns0:v>0.6459113245320447</ns0:v>
+        <ns0:v>0.27157780911746254</ns0:v>
       </ns0:c>
       <ns0:c r="I40">
-        <ns0:v>34.18000030517578</ns0:v>
+        <ns0:v>122.33000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="J40">
-        <ns0:v>0.29256428680004554</ns0:v>
+        <ns0:v>-0.400560357908597</ns0:v>
       </ns0:c>
       <ns0:c r="K40">
-        <ns0:v>0.9184292039791117</ns0:v>
+        <ns0:v>0.7128735242614246</ns0:v>
       </ns0:c>
       <ns0:c r="L40">
-        <ns0:v>69.90277658988103</ns0:v>
+        <ns0:v>70.34266370873462</ns0:v>
       </ns0:c>
       <ns0:c r="M40">
-        <ns0:v>32.479500198364256</ns0:v>
+        <ns0:v>112.48699989318848</ns0:v>
       </ns0:c>
       <ns0:c r="N40">
-        <ns0:v>32.19639995574951</ns0:v>
+        <ns0:v>108.91580017089844</ns0:v>
       </ns0:c>
       <ns0:c r="O40">
-        <ns0:v>28.672250051498413</ns0:v>
+        <ns0:v>80.61185024261475</ns0:v>
       </ns0:c>
       <ns0:c r="P40" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q40" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </ns0:c>
       <ns0:c r="T40" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HMC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HALO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3203,55 +3203,55 @@
       </ns0:c>
       <ns0:c r="B41" t="inlineStr">
         <ns0:is>
-          <ns0:t>HPK</ns0:t>
+          <ns0:t>HGTY</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C41" t="inlineStr">
         <ns0:is>
-          <ns0:t>HighPeak Energy Inc</ns0:t>
+          <ns0:t>Hagerty Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>퍼미안 분지에서 원유·천연가스·천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험을 제공하며 보험·마켓플레이스 부문을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
-        <ns0:v>10.550000190734863</ns0:v>
+        <ns0:v>15.300000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H41">
-        <ns0:v>6.0301547032294955</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="I41">
-        <ns0:v>10.5649995803833</ns0:v>
+        <ns0:v>15.350000381469727</ns0:v>
       </ns0:c>
       <ns0:c r="J41">
-        <ns0:v>-0.1419724585345783</ns0:v>
+        <ns0:v>-0.32573413350023284</ns0:v>
       </ns0:c>
       <ns0:c r="K41">
-        <ns0:v>1.6906476144263831</ns0:v>
+        <ns0:v>0.8788154561330153</ns0:v>
       </ns0:c>
       <ns0:c r="L41">
-        <ns0:v>76.0101429283192</ns0:v>
+        <ns0:v>80.02906298207856</ns0:v>
       </ns0:c>
       <ns0:c r="M41">
-        <ns0:v>8.575499987602234</ns0:v>
+        <ns0:v>14.029000043869019</ns0:v>
       </ns0:c>
       <ns0:c r="N41">
-        <ns0:v>8.263000001907349</ns0:v>
+        <ns0:v>13.602999992370606</ns0:v>
       </ns0:c>
       <ns0:c r="O41">
-        <ns0:v>6.751600003242492</ns0:v>
+        <ns0:v>11.909549989700317</ns0:v>
       </ns0:c>
       <ns0:c r="P41" t="inlineStr">
         <ns0:is>
@@ -3270,7 +3270,7 @@
       </ns0:c>
       <ns0:c r="T41" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HPK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HGTY/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3282,59 +3282,59 @@
       </ns0:c>
       <ns0:c r="B42" t="inlineStr">
         <ns0:is>
-          <ns0:t>IBEX</ns0:t>
+          <ns0:t>HMC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C42" t="inlineStr">
         <ns0:is>
-          <ns0:t>IBEX Ltd</ns0:t>
+          <ns0:t>Honda Motor ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Information Technology Services</ns0:t>
+          <ns0:t>Auto Manufacturers</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
+          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
-        <ns0:v>45.64500045776367</ns0:v>
+        <ns0:v>34.279998779296875</ns0:v>
       </ns0:c>
       <ns0:c r="H42">
-        <ns0:v>-0.5772149652128022</ns0:v>
+        <ns0:v>0.6459113245320447</ns0:v>
       </ns0:c>
       <ns0:c r="I42">
-        <ns0:v>46.209999084472656</ns0:v>
+        <ns0:v>34.18000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J42">
-        <ns0:v>-1.2226761261694863</ns0:v>
+        <ns0:v>0.29256428680004554</ns0:v>
       </ns0:c>
       <ns0:c r="K42">
-        <ns0:v>0.7531847133757962</ns0:v>
+        <ns0:v>0.9184321823560948</ns0:v>
       </ns0:c>
       <ns0:c r="L42">
-        <ns0:v>68.42283062512941</ns0:v>
+        <ns0:v>69.90277658988103</ns0:v>
       </ns0:c>
       <ns0:c r="M42">
-        <ns0:v>43.81375026702881</ns0:v>
+        <ns0:v>32.479500198364256</ns0:v>
       </ns0:c>
       <ns0:c r="N42">
-        <ns0:v>40.136300048828126</ns0:v>
+        <ns0:v>32.19639995574951</ns0:v>
       </ns0:c>
       <ns0:c r="O42">
-        <ns0:v>33.80140003204346</ns0:v>
+        <ns0:v>28.672250051498413</ns0:v>
       </ns0:c>
       <ns0:c r="P42" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q42" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </ns0:c>
       <ns0:c r="T42" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IBEX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HMC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3361,55 +3361,55 @@
       </ns0:c>
       <ns0:c r="B43" t="inlineStr">
         <ns0:is>
-          <ns0:t>IBTA</ns0:t>
+          <ns0:t>HPK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Ibotta Inc</ns0:t>
+          <ns0:t>HighPeak Energy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크를 통해 소비자에게 제공.</ns0:t>
+          <ns0:t>퍼미안 분지에서 원유·천연가스·천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
-        <ns0:v>47.84000015258789</ns0:v>
+        <ns0:v>10.550000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H43">
-        <ns0:v>-2.22767248270912</ns0:v>
+        <ns0:v>6.0301547032294955</ns0:v>
       </ns0:c>
       <ns0:c r="I43">
-        <ns0:v>49.599998474121094</ns0:v>
+        <ns0:v>10.5649995803833</ns0:v>
       </ns0:c>
       <ns0:c r="J43">
-        <ns0:v>-3.5483838219299235</ns0:v>
+        <ns0:v>-0.1419724585345783</ns0:v>
       </ns0:c>
       <ns0:c r="K43">
-        <ns0:v>0.663923784795143</ns0:v>
+        <ns0:v>1.6909420987024286</ns0:v>
       </ns0:c>
       <ns0:c r="L43">
-        <ns0:v>72.93492792446125</ns0:v>
+        <ns0:v>76.0101429283192</ns0:v>
       </ns0:c>
       <ns0:c r="M43">
-        <ns0:v>42.17849960327148</ns0:v>
+        <ns0:v>8.575499987602234</ns0:v>
       </ns0:c>
       <ns0:c r="N43">
-        <ns0:v>39.94579971313477</ns0:v>
+        <ns0:v>8.263000001907349</ns0:v>
       </ns0:c>
       <ns0:c r="O43">
-        <ns0:v>31.5463498878479</ns0:v>
+        <ns0:v>6.751600003242492</ns0:v>
       </ns0:c>
       <ns0:c r="P43" t="inlineStr">
         <ns0:is>
@@ -3428,7 +3428,7 @@
       </ns0:c>
       <ns0:c r="T43" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IBTA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HPK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3440,55 +3440,55 @@
       </ns0:c>
       <ns0:c r="B44" t="inlineStr">
         <ns0:is>
-          <ns0:t>IDT</ns0:t>
+          <ns0:t>IBEX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C44" t="inlineStr">
         <ns0:is>
-          <ns0:t>IDT Corp</ns0:t>
+          <ns0:t>IBEX Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Telecom Services</ns0:t>
+          <ns0:t>Information Technology Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
-        <ns0:v>80.66999816894531</ns0:v>
+        <ns0:v>45.64500045776367</ns0:v>
       </ns0:c>
       <ns0:c r="H44">
-        <ns0:v>-1.9090463711160632</ns0:v>
+        <ns0:v>-0.5772149652128022</ns0:v>
       </ns0:c>
       <ns0:c r="I44">
-        <ns0:v>82.91000366210938</ns0:v>
+        <ns0:v>46.209999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="J44">
-        <ns0:v>-2.701731267909435</ns0:v>
+        <ns0:v>-1.2226761261694863</ns0:v>
       </ns0:c>
       <ns0:c r="K44">
-        <ns0:v>0.4626548800811535</ns0:v>
+        <ns0:v>0.7530910453353316</ns0:v>
       </ns0:c>
       <ns0:c r="L44">
-        <ns0:v>65.88092788832449</ns0:v>
+        <ns0:v>68.42283062512941</ns0:v>
       </ns0:c>
       <ns0:c r="M44">
-        <ns0:v>76.78549995422364</ns0:v>
+        <ns0:v>43.81375026702881</ns0:v>
       </ns0:c>
       <ns0:c r="N44">
-        <ns0:v>71.5802001953125</ns0:v>
+        <ns0:v>40.136300048828126</ns0:v>
       </ns0:c>
       <ns0:c r="O44">
-        <ns0:v>57.881250076293945</ns0:v>
+        <ns0:v>33.80140003204346</ns0:v>
       </ns0:c>
       <ns0:c r="P44" t="inlineStr">
         <ns0:is>
@@ -3507,7 +3507,7 @@
       </ns0:c>
       <ns0:c r="T44" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IDT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IBEX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3519,55 +3519,55 @@
       </ns0:c>
       <ns0:c r="B45" t="inlineStr">
         <ns0:is>
-          <ns0:t>IFF</ns0:t>
+          <ns0:t>IBTA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C45" t="inlineStr">
         <ns0:is>
-          <ns0:t>International Flavors &amp; Fragrances Inc</ns0:t>
+          <ns0:t>Ibotta Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Chemicals</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>식품·음료·건강 및 바이오과학·향료와 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
+          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크를 통해 소비자에게 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
-        <ns0:v>90.68000030517578</ns0:v>
+        <ns0:v>47.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H45">
-        <ns0:v>0.4319408413931747</ns0:v>
+        <ns0:v>-2.22767248270912</ns0:v>
       </ns0:c>
       <ns0:c r="I45">
-        <ns0:v>91.69000244140625</ns0:v>
+        <ns0:v>49.599998474121094</ns0:v>
       </ns0:c>
       <ns0:c r="J45">
-        <ns0:v>-1.101540090890396</ns0:v>
+        <ns0:v>-3.5483838219299235</ns0:v>
       </ns0:c>
       <ns0:c r="K45">
-        <ns0:v>1.1603940103407064</ns0:v>
+        <ns0:v>0.6640192447210661</ns0:v>
       </ns0:c>
       <ns0:c r="L45">
-        <ns0:v>73.12875478301022</ns0:v>
+        <ns0:v>72.93492792446125</ns0:v>
       </ns0:c>
       <ns0:c r="M45">
-        <ns0:v>85.54250030517578</ns0:v>
+        <ns0:v>42.17849960327148</ns0:v>
       </ns0:c>
       <ns0:c r="N45">
-        <ns0:v>85.14060012817383</ns0:v>
+        <ns0:v>39.94579971313477</ns0:v>
       </ns0:c>
       <ns0:c r="O45">
-        <ns0:v>77.35069995880127</ns0:v>
+        <ns0:v>31.5463498878479</ns0:v>
       </ns0:c>
       <ns0:c r="P45" t="inlineStr">
         <ns0:is>
@@ -3586,7 +3586,7 @@
       </ns0:c>
       <ns0:c r="T45" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IFF/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IBTA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3598,55 +3598,55 @@
       </ns0:c>
       <ns0:c r="B46" t="inlineStr">
         <ns0:is>
-          <ns0:t>JAKK</ns0:t>
+          <ns0:t>IDT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Jakks Pacific Inc</ns0:t>
+          <ns0:t>IDT Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Leisure</ns0:t>
+          <ns0:t>Telecom Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 장난감, 소비재·전자제품, 아동용 가구, 의상, 스포츠용품, 가정용 가구 등을 제작·판매.</ns0:t>
+          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46">
-        <ns0:v>28.530000686645508</ns0:v>
+        <ns0:v>80.66999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H46">
-        <ns0:v>-1.756199079901355</ns0:v>
+        <ns0:v>-1.9090463711160632</ns0:v>
       </ns0:c>
       <ns0:c r="I46">
-        <ns0:v>29.059999465942383</ns0:v>
+        <ns0:v>82.91000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="J46">
-        <ns0:v>-1.8238086339885218</ns0:v>
+        <ns0:v>-2.701731267909435</ns0:v>
       </ns0:c>
       <ns0:c r="K46">
-        <ns0:v>1.3779838131339002</ns0:v>
+        <ns0:v>0.4627683984252349</ns0:v>
       </ns0:c>
       <ns0:c r="L46">
-        <ns0:v>67.03239968839934</ns0:v>
+        <ns0:v>65.88092788832449</ns0:v>
       </ns0:c>
       <ns0:c r="M46">
-        <ns0:v>26.59950008392334</ns0:v>
+        <ns0:v>76.78549995422364</ns0:v>
       </ns0:c>
       <ns0:c r="N46">
-        <ns0:v>25.61360004425049</ns0:v>
+        <ns0:v>71.5802001953125</ns0:v>
       </ns0:c>
       <ns0:c r="O46">
-        <ns0:v>22.431999959945678</ns0:v>
+        <ns0:v>57.881250076293945</ns0:v>
       </ns0:c>
       <ns0:c r="P46" t="inlineStr">
         <ns0:is>
@@ -3665,7 +3665,7 @@
       </ns0:c>
       <ns0:c r="T46" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/JAKK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IDT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3677,52 +3677,55 @@
       </ns0:c>
       <ns0:c r="B47" t="inlineStr">
         <ns0:is>
-          <ns0:t>KCHV</ns0:t>
+          <ns0:t>IFF</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Kochav Defense Acquisition Corp</ns0:t>
+          <ns0:t>International Flavors &amp; Fragrances Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Companies</ns0:t>
+          <ns0:t>Specialty Chemicals</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 방위·항공우주 분야 기업과의 합병, 주식 교환, 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>식품·음료·건강 및 바이오과학·향료와 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
-        <ns0:v>10.5</ns0:v>
+        <ns0:v>90.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H47">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>0.4319408413931747</ns0:v>
       </ns0:c>
       <ns0:c r="I47">
-        <ns0:v>10.5</ns0:v>
+        <ns0:v>91.69000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="J47">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>-1.101540090890396</ns0:v>
+      </ns0:c>
+      <ns0:c r="K47">
+        <ns0:v>1.160399689210921</ns0:v>
       </ns0:c>
       <ns0:c r="L47">
-        <ns0:v>87.4177175029709</ns0:v>
+        <ns0:v>73.12875478301022</ns0:v>
       </ns0:c>
       <ns0:c r="M47">
-        <ns0:v>10.472749853134156</ns0:v>
+        <ns0:v>85.54250030517578</ns0:v>
       </ns0:c>
       <ns0:c r="N47">
-        <ns0:v>10.451859893798828</ns0:v>
+        <ns0:v>85.14060012817383</ns0:v>
       </ns0:c>
       <ns0:c r="O47">
-        <ns0:v>10.326589946746827</ns0:v>
+        <ns0:v>77.35069995880127</ns0:v>
       </ns0:c>
       <ns0:c r="P47" t="inlineStr">
         <ns0:is>
@@ -3741,7 +3744,7 @@
       </ns0:c>
       <ns0:c r="T47" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KCHV/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IFF/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3753,59 +3756,59 @@
       </ns0:c>
       <ns0:c r="B48" t="inlineStr">
         <ns0:is>
-          <ns0:t>KDP</ns0:t>
+          <ns0:t>JAKK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Keurig Dr Pepper Inc</ns0:t>
+          <ns0:t>Jakks Pacific Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Defensive</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Beverages - Non-Alcoholic</ns0:t>
+          <ns0:t>Leisure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Keurig Dr Pepper Inc. owns, manufactures, and distributors beverages and single serve brewing systems in the United States and internationally. The company operates through three segments: U.S. Refreshment Beverages, U.S. Coffee, and International. It manufactures and distributes branded concentrates, syrup,…</ns0:t>
+          <ns0:t>전 세계에서 장난감, 소비재·전자제품, 아동용 가구, 의상, 스포츠용품, 가정용 가구 등을 제작·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
-        <ns0:v>34.619998931884766</ns0:v>
+        <ns0:v>28.530000686645508</ns0:v>
       </ns0:c>
       <ns0:c r="H48">
-        <ns0:v>1.2872984867772441</ns0:v>
+        <ns0:v>-1.756199079901355</ns0:v>
       </ns0:c>
       <ns0:c r="I48">
-        <ns0:v>34.4900016784668</ns0:v>
+        <ns0:v>29.059999465942383</ns0:v>
       </ns0:c>
       <ns0:c r="J48">
-        <ns0:v>0.37691286486405406</ns0:v>
+        <ns0:v>-1.8238086339885218</ns0:v>
       </ns0:c>
       <ns0:c r="K48">
-        <ns0:v>1.2193251196996926</ns0:v>
+        <ns0:v>1.3779325888740908</ns0:v>
       </ns0:c>
       <ns0:c r="L48">
-        <ns0:v>69.7177549624567</ns0:v>
+        <ns0:v>67.03239968839934</ns0:v>
       </ns0:c>
       <ns0:c r="M48">
-        <ns0:v>31.676000022888182</ns0:v>
+        <ns0:v>26.59950008392334</ns0:v>
       </ns0:c>
       <ns0:c r="N48">
-        <ns0:v>31.542599983215332</ns0:v>
+        <ns0:v>25.61360004425049</ns0:v>
       </ns0:c>
       <ns0:c r="O48">
-        <ns0:v>29.635200061798095</ns0:v>
+        <ns0:v>22.431999959945678</ns0:v>
       </ns0:c>
       <ns0:c r="P48" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q48" t="inlineStr">
@@ -3820,7 +3823,7 @@
       </ns0:c>
       <ns0:c r="T48" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KDP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/JAKK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3832,59 +3835,56 @@
       </ns0:c>
       <ns0:c r="B49" t="inlineStr">
         <ns0:is>
-          <ns0:t>KGEI</ns0:t>
+          <ns0:t>KCHV</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Kolibri Global Energy Inc</ns0:t>
+          <ns0:t>Kochav Defense Acquisition Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 석유·가스 에너지 사업을 발굴·개발하며 오클라호마 캐니 셰일 유전을 개발하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 방위·항공우주 분야 기업과의 합병, 주식 교환, 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
-        <ns0:v>6.96999979019165</ns0:v>
+        <ns0:v>10.5</ns0:v>
       </ns0:c>
       <ns0:c r="H49">
-        <ns0:v>5.2870077142457506</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="I49">
-        <ns0:v>6.940000057220459</ns0:v>
+        <ns0:v>10.5</ns0:v>
       </ns0:c>
       <ns0:c r="J49">
-        <ns0:v>0.43227280581905614</ns0:v>
-      </ns0:c>
-      <ns0:c r="K49">
-        <ns0:v>1.6228292868221963</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="L49">
-        <ns0:v>66.36519484359562</ns0:v>
+        <ns0:v>87.4177175029709</ns0:v>
       </ns0:c>
       <ns0:c r="M49">
-        <ns0:v>6.4369999170303345</ns0:v>
+        <ns0:v>10.472749853134156</ns0:v>
       </ns0:c>
       <ns0:c r="N49">
-        <ns0:v>6.235799989700317</ns0:v>
+        <ns0:v>10.451859893798828</ns0:v>
       </ns0:c>
       <ns0:c r="O49">
-        <ns0:v>5.180499992370605</ns0:v>
+        <ns0:v>10.326589946746827</ns0:v>
       </ns0:c>
       <ns0:c r="P49" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q49" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </ns0:c>
       <ns0:c r="T49" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KGEI/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KCHV/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3911,55 +3911,55 @@
       </ns0:c>
       <ns0:c r="B50" t="inlineStr">
         <ns0:is>
-          <ns0:t>KRP</ns0:t>
+          <ns0:t>KDP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Kimbell Royalty Partners LP</ns0:t>
+          <ns0:t>Keurig Dr Pepper Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Beverages - Non-Alcoholic</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득하는 기업.</ns0:t>
+          <ns0:t>Keurig Dr Pepper Inc. owns, manufactures, and distributors beverages and single serve brewing systems in the United States and internationally. The company operates through three segments: U.S. Refreshment Beverages, U.S. Coffee, and International. It manufactures and distributes branded concentrates, syrup,…</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
-        <ns0:v>16.280000686645508</ns0:v>
+        <ns0:v>34.619998931884766</ns0:v>
       </ns0:c>
       <ns0:c r="H50">
-        <ns0:v>2.133005741610128</ns0:v>
+        <ns0:v>1.2872984867772441</ns0:v>
       </ns0:c>
       <ns0:c r="I50">
-        <ns0:v>15.989999771118164</ns0:v>
+        <ns0:v>34.4900016784668</ns0:v>
       </ns0:c>
       <ns0:c r="J50">
-        <ns0:v>1.81363927253555</ns0:v>
+        <ns0:v>0.37691286486405406</ns0:v>
       </ns0:c>
       <ns0:c r="K50">
-        <ns0:v>0.9434619545618463</ns0:v>
+        <ns0:v>1.2193926957237875</ns0:v>
       </ns0:c>
       <ns0:c r="L50">
-        <ns0:v>77.64578541455914</ns0:v>
+        <ns0:v>69.7177549624567</ns0:v>
       </ns0:c>
       <ns0:c r="M50">
-        <ns0:v>14.940499925613404</ns0:v>
+        <ns0:v>31.676000022888182</ns0:v>
       </ns0:c>
       <ns0:c r="N50">
-        <ns0:v>14.988599910736085</ns0:v>
+        <ns0:v>31.542599983215332</ns0:v>
       </ns0:c>
       <ns0:c r="O50">
-        <ns0:v>14.520249972343445</ns0:v>
+        <ns0:v>29.635200061798095</ns0:v>
       </ns0:c>
       <ns0:c r="P50" t="inlineStr">
         <ns0:is>
@@ -3978,7 +3978,7 @@
       </ns0:c>
       <ns0:c r="T50" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KRP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KDP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3990,59 +3990,59 @@
       </ns0:c>
       <ns0:c r="B51" t="inlineStr">
         <ns0:is>
-          <ns0:t>MA</ns0:t>
+          <ns0:t>KGEI</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Mastercard Incorporated</ns0:t>
+          <ns0:t>Kolibri Global Energy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Credit Services</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 거래 처리 및 결제 관련 제품·서비스를 소비자, 가맹점, 금융기관 등에 제공.</ns0:t>
+          <ns0:t>미국에서 석유·가스 에너지 사업을 발굴·개발하며 오클라호마 캐니 셰일 유전을 개발하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
-        <ns0:v>617.4199829101562</ns0:v>
+        <ns0:v>6.96999979019165</ns0:v>
       </ns0:c>
       <ns0:c r="H51">
-        <ns0:v>0.17847474897223492</ns0:v>
+        <ns0:v>5.2870077142457506</ns0:v>
       </ns0:c>
       <ns0:c r="I51">
-        <ns0:v>619.7999877929688</ns0:v>
+        <ns0:v>6.940000057220459</ns0:v>
       </ns0:c>
       <ns0:c r="J51">
-        <ns0:v>-0.3839956324115823</ns0:v>
+        <ns0:v>0.43227280581905614</ns0:v>
       </ns0:c>
       <ns0:c r="K51">
-        <ns0:v>1.0497212046786821</ns0:v>
+        <ns0:v>1.6238802190497295</ns0:v>
       </ns0:c>
       <ns0:c r="L51">
-        <ns0:v>75.07351050485384</ns0:v>
+        <ns0:v>66.36519484359562</ns0:v>
       </ns0:c>
       <ns0:c r="M51">
-        <ns0:v>575.2380065917969</ns0:v>
+        <ns0:v>6.4369999170303345</ns0:v>
       </ns0:c>
       <ns0:c r="N51">
-        <ns0:v>575.61419921875</ns0:v>
+        <ns0:v>6.235799989700317</ns0:v>
       </ns0:c>
       <ns0:c r="O51">
-        <ns0:v>532.995698852539</ns0:v>
+        <ns0:v>5.180499992370605</ns0:v>
       </ns0:c>
       <ns0:c r="P51" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q51" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </ns0:c>
       <ns0:c r="T51" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KGEI/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4069,59 +4069,59 @@
       </ns0:c>
       <ns0:c r="B52" t="inlineStr">
         <ns0:is>
-          <ns0:t>MANH</ns0:t>
+          <ns0:t>KOF</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Manhattan Associates Inc</ns0:t>
+          <ns0:t>Coca-Cola Femsa SAB de CV ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Beverages - Non-Alcoholic</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>공급망·재고·옴니채널 운영과 창고 관리를 위한 소프트웨어를 개발·판매·구축·유지보수.</ns0:t>
+          <ns0:t>멕시코·중남미에서 코카콜라 상표 음료를 생산·마케팅·판매·유통하는 가맹 보틀링 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
-        <ns0:v>222.1699981689453</ns0:v>
+        <ns0:v>118.94999694824219</ns0:v>
       </ns0:c>
       <ns0:c r="H52">
-        <ns0:v>-2.110507756091462</ns0:v>
+        <ns0:v>2.8356521407618462</ns0:v>
       </ns0:c>
       <ns0:c r="I52">
-        <ns0:v>228.0</ns0:v>
+        <ns0:v>118.91999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J52">
-        <ns0:v>-2.55701834695381</ns0:v>
+        <ns0:v>0.02522601728791596</ns0:v>
       </ns0:c>
       <ns0:c r="K52">
-        <ns0:v>1.1472337067471823</ns0:v>
+        <ns0:v>2.431837678564768</ns0:v>
       </ns0:c>
       <ns0:c r="L52">
-        <ns0:v>61.87107373107437</ns0:v>
+        <ns0:v>69.35394022177334</ns0:v>
       </ns0:c>
       <ns0:c r="M52">
-        <ns0:v>209.16499938964844</ns0:v>
+        <ns0:v>110.68999977111817</ns0:v>
       </ns0:c>
       <ns0:c r="N52">
-        <ns0:v>208.89600067138673</ns0:v>
+        <ns0:v>111.14300048828125</ns0:v>
       </ns0:c>
       <ns0:c r="O52">
-        <ns0:v>163.08525012969972</ns0:v>
+        <ns0:v>106.03870014190674</ns0:v>
       </ns0:c>
       <ns0:c r="P52" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q52" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </ns0:c>
       <ns0:c r="T52" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MANH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KOF/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4148,55 +4148,55 @@
       </ns0:c>
       <ns0:c r="B53" t="inlineStr">
         <ns0:is>
-          <ns0:t>MCK</ns0:t>
+          <ns0:t>KRP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Mckesson Corp</ns0:t>
+          <ns0:t>Kimbell Royalty Partners LP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Distribution</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>의약품 유통, 종양·전문진료, 처방 기술, 의료·외과용품 관련 의료 서비스를 제공.</ns0:t>
+          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
-        <ns0:v>1004.8400268554688</ns0:v>
+        <ns0:v>16.280000686645508</ns0:v>
       </ns0:c>
       <ns0:c r="H53">
-        <ns0:v>0.6208455615724473</ns0:v>
+        <ns0:v>2.133005741610128</ns0:v>
       </ns0:c>
       <ns0:c r="I53">
-        <ns0:v>1003.2100219726562</ns0:v>
+        <ns0:v>15.989999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="J53">
-        <ns0:v>0.1624789273543481</ns0:v>
+        <ns0:v>1.81363927253555</ns0:v>
       </ns0:c>
       <ns0:c r="K53">
-        <ns0:v>0.7632993113625185</ns0:v>
+        <ns0:v>0.944224065392475</ns0:v>
       </ns0:c>
       <ns0:c r="L53">
-        <ns0:v>75.7252153250921</ns0:v>
+        <ns0:v>77.64578541455914</ns0:v>
       </ns0:c>
       <ns0:c r="M53">
-        <ns0:v>914.2225036621094</ns0:v>
+        <ns0:v>14.940499925613404</ns0:v>
       </ns0:c>
       <ns0:c r="N53">
-        <ns0:v>896.4298046875</ns0:v>
+        <ns0:v>14.988599910736085</ns0:v>
       </ns0:c>
       <ns0:c r="O53">
-        <ns0:v>853.9728500366211</ns0:v>
+        <ns0:v>14.520249972343445</ns0:v>
       </ns0:c>
       <ns0:c r="P53" t="inlineStr">
         <ns0:is>
@@ -4215,7 +4215,7 @@
       </ns0:c>
       <ns0:c r="T53" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MCK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KRP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4227,55 +4227,55 @@
       </ns0:c>
       <ns0:c r="B54" t="inlineStr">
         <ns0:is>
-          <ns0:t>MD</ns0:t>
+          <ns0:t>MA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Pediatrix Medical Group Inc</ns0:t>
+          <ns0:t>Mastercard Incorporated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Care Facilities</ns0:t>
+          <ns0:t>Credit Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 신생아·모체태아·소아 세부전문 진료와 미숙아·합병증 신생아 치료를 제공하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 거래 처리 및 결제 관련 제품·서비스를 소비자, 가맹점, 금융기관 등에 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
-        <ns0:v>27.3799991607666</ns0:v>
+        <ns0:v>617.4199829101562</ns0:v>
       </ns0:c>
       <ns0:c r="H54">
-        <ns0:v>-1.368879917082555</ns0:v>
+        <ns0:v>0.17847474897223492</ns0:v>
       </ns0:c>
       <ns0:c r="I54">
-        <ns0:v>27.940000534057617</ns0:v>
+        <ns0:v>619.7999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="J54">
-        <ns0:v>-2.004299794512887</ns0:v>
+        <ns0:v>-0.3839956324115823</ns0:v>
       </ns0:c>
       <ns0:c r="K54">
-        <ns0:v>0.706490505242585</ns0:v>
+        <ns0:v>1.1020652874509154</ns0:v>
       </ns0:c>
       <ns0:c r="L54">
-        <ns0:v>60.312266804979465</ns0:v>
+        <ns0:v>75.07351050485384</ns0:v>
       </ns0:c>
       <ns0:c r="M54">
-        <ns0:v>26.29699993133545</ns0:v>
+        <ns0:v>575.2380065917969</ns0:v>
       </ns0:c>
       <ns0:c r="N54">
-        <ns0:v>26.454599952697755</ns0:v>
+        <ns0:v>575.61419921875</ns0:v>
       </ns0:c>
       <ns0:c r="O54">
-        <ns0:v>23.52894995689392</ns0:v>
+        <ns0:v>532.995698852539</ns0:v>
       </ns0:c>
       <ns0:c r="P54" t="inlineStr">
         <ns0:is>
@@ -4294,7 +4294,7 @@
       </ns0:c>
       <ns0:c r="T54" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4306,55 +4306,55 @@
       </ns0:c>
       <ns0:c r="B55" t="inlineStr">
         <ns0:is>
-          <ns0:t>MET</ns0:t>
+          <ns0:t>MANH</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C55" t="inlineStr">
         <ns0:is>
-          <ns0:t>Metlife Inc</ns0:t>
+          <ns0:t>Manhattan Associates Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D55" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E55" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Life</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 보험, 연금, 임직원 복리후생 및 자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
+          <ns0:t>공급망·재고·옴니채널 운영과 창고 관리를 위한 소프트웨어를 개발·판매·구축·유지보수.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
-        <ns0:v>100.76000213623047</ns0:v>
+        <ns0:v>222.1699981689453</ns0:v>
       </ns0:c>
       <ns0:c r="H55">
-        <ns0:v>0.48868605721446023</ns0:v>
+        <ns0:v>-2.110507756091462</ns0:v>
       </ns0:c>
       <ns0:c r="I55">
-        <ns0:v>101.44000244140625</ns0:v>
+        <ns0:v>228.0</ns0:v>
       </ns0:c>
       <ns0:c r="J55">
-        <ns0:v>-0.6703472878646255</ns0:v>
+        <ns0:v>-2.55701834695381</ns0:v>
       </ns0:c>
       <ns0:c r="K55">
-        <ns0:v>0.9963771467748044</ns0:v>
+        <ns0:v>1.1478615909831706</ns0:v>
       </ns0:c>
       <ns0:c r="L55">
-        <ns0:v>63.22530777136646</ns0:v>
+        <ns0:v>61.87107373107437</ns0:v>
       </ns0:c>
       <ns0:c r="M55">
-        <ns0:v>97.34299964904785</ns0:v>
+        <ns0:v>209.16499938964844</ns0:v>
       </ns0:c>
       <ns0:c r="N55">
-        <ns0:v>96.86980010986328</ns0:v>
+        <ns0:v>208.89600067138673</ns0:v>
       </ns0:c>
       <ns0:c r="O55">
-        <ns0:v>84.6291996383667</ns0:v>
+        <ns0:v>163.08525012969972</ns0:v>
       </ns0:c>
       <ns0:c r="P55" t="inlineStr">
         <ns0:is>
@@ -4373,7 +4373,7 @@
       </ns0:c>
       <ns0:c r="T55" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MET/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MANH/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4385,55 +4385,55 @@
       </ns0:c>
       <ns0:c r="B56" t="inlineStr">
         <ns0:is>
-          <ns0:t>MSGM</ns0:t>
+          <ns0:t>MCK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C56" t="inlineStr">
         <ns0:is>
-          <ns0:t>Motorsport Games Inc</ns0:t>
+          <ns0:t>Mckesson Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D56" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E56" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronic Gaming &amp; Multimedia</ns0:t>
+          <ns0:t>Medical Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 PC용 레이싱 게임을 개발·배급하고 게임·이스포츠 사업을 운영하는 기업.</ns0:t>
+          <ns0:t>의약품 유통, 종양·전문진료, 처방 기술, 의료·외과용품 관련 의료 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
-        <ns0:v>5.619999885559082</ns0:v>
+        <ns0:v>1004.8400268554688</ns0:v>
       </ns0:c>
       <ns0:c r="H56">
-        <ns0:v>3.119267564100481</ns0:v>
+        <ns0:v>0.6208455615724473</ns0:v>
       </ns0:c>
       <ns0:c r="I56">
-        <ns0:v>5.558000087738037</ns0:v>
+        <ns0:v>1003.2100219726562</ns0:v>
       </ns0:c>
       <ns0:c r="J56">
-        <ns0:v>1.1155055207326736</ns0:v>
+        <ns0:v>0.1624789273543481</ns0:v>
       </ns0:c>
       <ns0:c r="K56">
-        <ns0:v>1.0214685231464953</ns0:v>
+        <ns0:v>0.764018691588785</ns0:v>
       </ns0:c>
       <ns0:c r="L56">
-        <ns0:v>66.40880202397764</ns0:v>
+        <ns0:v>75.7252153250921</ns0:v>
       </ns0:c>
       <ns0:c r="M56">
-        <ns0:v>4.908500003814697</ns0:v>
+        <ns0:v>914.2225036621094</ns0:v>
       </ns0:c>
       <ns0:c r="N56">
-        <ns0:v>4.512100019454956</ns0:v>
+        <ns0:v>896.4298046875</ns0:v>
       </ns0:c>
       <ns0:c r="O56">
-        <ns0:v>4.187425005435943</ns0:v>
+        <ns0:v>853.9728500366211</ns0:v>
       </ns0:c>
       <ns0:c r="P56" t="inlineStr">
         <ns0:is>
@@ -4452,7 +4452,7 @@
       </ns0:c>
       <ns0:c r="T56" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MSGM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MCK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4464,59 +4464,59 @@
       </ns0:c>
       <ns0:c r="B57" t="inlineStr">
         <ns0:is>
-          <ns0:t>MWYN</ns0:t>
+          <ns0:t>MD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marwynn Holdings Inc</ns0:t>
+          <ns0:t>Pediatrix Medical Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
+          <ns0:t>Medical Care Facilities</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 신생아·모체태아·소아 세부전문 진료와 미숙아·합병증 신생아 치료를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
-        <ns0:v>2.2049999237060547</ns0:v>
+        <ns0:v>27.3799991607666</ns0:v>
       </ns0:c>
       <ns0:c r="H57">
-        <ns0:v>14.248703815123553</ns0:v>
+        <ns0:v>-1.368879917082555</ns0:v>
       </ns0:c>
       <ns0:c r="I57">
-        <ns0:v>1.9500000476837158</ns0:v>
+        <ns0:v>27.940000534057617</ns0:v>
       </ns0:c>
       <ns0:c r="J57">
-        <ns0:v>13.076916399322002</ns0:v>
+        <ns0:v>-2.004299794512887</ns0:v>
       </ns0:c>
       <ns0:c r="K57">
-        <ns0:v>2.706722050554683</ns0:v>
+        <ns0:v>0.7064944668938014</ns0:v>
       </ns0:c>
       <ns0:c r="L57">
-        <ns0:v>78.69118255952728</ns0:v>
+        <ns0:v>60.312266804979465</ns0:v>
       </ns0:c>
       <ns0:c r="M57">
-        <ns0:v>1.3146499931812285</ns0:v>
+        <ns0:v>26.29699993133545</ns0:v>
       </ns0:c>
       <ns0:c r="N57">
-        <ns0:v>1.1712999904155732</ns0:v>
+        <ns0:v>26.454599952697755</ns0:v>
       </ns0:c>
       <ns0:c r="O57">
-        <ns0:v>0.9160099965333939</ns0:v>
+        <ns0:v>23.52894995689392</ns0:v>
       </ns0:c>
       <ns0:c r="P57" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q57" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </ns0:c>
       <ns0:c r="T57" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MWYN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4543,55 +4543,55 @@
       </ns0:c>
       <ns0:c r="B58" t="inlineStr">
         <ns0:is>
-          <ns0:t>NHC</ns0:t>
+          <ns0:t>MET</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C58" t="inlineStr">
         <ns0:is>
-          <ns0:t>National Healthcare Corp</ns0:t>
+          <ns0:t>Metlife Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D58" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E58" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Care Facilities</ns0:t>
+          <ns0:t>Insurance - Life</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>전문 간호·생활지원·독립생활 시설, 재택돌봄·호스피스 기관 및 병원 서비스를 운영하는 기업.</ns0:t>
+          <ns0:t>전 세계에서 보험, 연금, 임직원 복리후생 및 자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
-        <ns0:v>242.82000732421875</ns0:v>
+        <ns0:v>100.76000213623047</ns0:v>
       </ns0:c>
       <ns0:c r="H58">
-        <ns0:v>-1.1037313031203588</ns0:v>
+        <ns0:v>0.48868605721446023</ns0:v>
       </ns0:c>
       <ns0:c r="I58">
-        <ns0:v>245.63999938964844</ns0:v>
+        <ns0:v>101.44000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="J58">
-        <ns0:v>-1.148018267560913</ns0:v>
+        <ns0:v>-0.6703472878646255</ns0:v>
       </ns0:c>
       <ns0:c r="K58">
-        <ns0:v>0.9015273311897106</ns0:v>
+        <ns0:v>1.006710706143522</ns0:v>
       </ns0:c>
       <ns0:c r="L58">
-        <ns0:v>65.62061068347768</ns0:v>
+        <ns0:v>63.22530777136646</ns0:v>
       </ns0:c>
       <ns0:c r="M58">
-        <ns0:v>227.84300079345704</ns0:v>
+        <ns0:v>97.34299964904785</ns0:v>
       </ns0:c>
       <ns0:c r="N58">
-        <ns0:v>225.64639923095703</ns0:v>
+        <ns0:v>96.86980010986328</ns0:v>
       </ns0:c>
       <ns0:c r="O58">
-        <ns0:v>189.39094947814942</ns0:v>
+        <ns0:v>84.6291996383667</ns0:v>
       </ns0:c>
       <ns0:c r="P58" t="inlineStr">
         <ns0:is>
@@ -4610,7 +4610,7 @@
       </ns0:c>
       <ns0:c r="T58" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NHC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MET/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4622,59 +4622,59 @@
       </ns0:c>
       <ns0:c r="B59" t="inlineStr">
         <ns0:is>
-          <ns0:t>OPK</ns0:t>
+          <ns0:t>MSGM</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C59" t="inlineStr">
         <ns0:is>
-          <ns0:t>Opko Health Inc</ns0:t>
+          <ns0:t>Motorsport Games Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D59" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E59" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Electronic Gaming &amp; Multimedia</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F59" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 등 여러 국가에서 의약품 개발과 진단 사업을 운영하는 헬스케어 기업.</ns0:t>
+          <ns0:t>미국에서 PC용 레이싱 게임을 개발·배급하고 게임·이스포츠 사업을 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G59">
-        <ns0:v>1.5299999713897705</ns0:v>
+        <ns0:v>5.619999885559082</ns0:v>
       </ns0:c>
       <ns0:c r="H59">
-        <ns0:v>-4.9689467207783</ns0:v>
+        <ns0:v>3.119267564100481</ns0:v>
       </ns0:c>
       <ns0:c r="I59">
-        <ns0:v>1.75</ns0:v>
+        <ns0:v>5.558000087738037</ns0:v>
       </ns0:c>
       <ns0:c r="J59">
-        <ns0:v>-12.571430206298828</ns0:v>
+        <ns0:v>1.1155055207326736</ns0:v>
       </ns0:c>
       <ns0:c r="K59">
-        <ns0:v>2.498779124097499</ns0:v>
+        <ns0:v>1.0210639057479471</ns0:v>
       </ns0:c>
       <ns0:c r="L59">
-        <ns0:v>51.712721345434694</ns0:v>
+        <ns0:v>66.40880202397764</ns0:v>
       </ns0:c>
       <ns0:c r="M59">
-        <ns0:v>1.5385000109672546</ns0:v>
+        <ns0:v>4.908500003814697</ns0:v>
       </ns0:c>
       <ns0:c r="N59">
-        <ns0:v>1.5164000082015991</ns0:v>
+        <ns0:v>4.512100019454956</ns0:v>
       </ns0:c>
       <ns0:c r="O59">
-        <ns0:v>1.3282000041007995</ns0:v>
+        <ns0:v>4.187425005435943</ns0:v>
       </ns0:c>
       <ns0:c r="P59" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q59" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </ns0:c>
       <ns0:c r="T59" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/OPK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MSGM/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4701,59 +4701,59 @@
       </ns0:c>
       <ns0:c r="B60" t="inlineStr">
         <ns0:is>
-          <ns0:t>OPRT</ns0:t>
+          <ns0:t>MWYN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C60" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oportun Financial Corp</ns0:t>
+          <ns0:t>Marwynn Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D60" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E60" t="inlineStr">
         <ns0:is>
-          <ns0:t>Credit Services</ns0:t>
+          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F60" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드를 제공.</ns0:t>
+          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G60">
-        <ns0:v>9.079999923706055</ns0:v>
+        <ns0:v>2.2049999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="H60">
-        <ns0:v>-1.4115104658248612</ns0:v>
+        <ns0:v>14.248703815123553</ns0:v>
       </ns0:c>
       <ns0:c r="I60">
-        <ns0:v>9.270000457763672</ns0:v>
+        <ns0:v>1.9500000476837158</ns0:v>
       </ns0:c>
       <ns0:c r="J60">
-        <ns0:v>-2.049628097898215</ns0:v>
+        <ns0:v>13.076916399322002</ns0:v>
       </ns0:c>
       <ns0:c r="K60">
-        <ns0:v>0.9445077798100774</ns0:v>
+        <ns0:v>2.71212197963629</ns0:v>
       </ns0:c>
       <ns0:c r="L60">
-        <ns0:v>63.905964903145986</ns0:v>
+        <ns0:v>78.69118255952728</ns0:v>
       </ns0:c>
       <ns0:c r="M60">
-        <ns0:v>8.558749961853028</ns0:v>
+        <ns0:v>1.3146499931812285</ns0:v>
       </ns0:c>
       <ns0:c r="N60">
-        <ns0:v>8.013299989700318</ns0:v>
+        <ns0:v>1.1712999904155732</ns0:v>
       </ns0:c>
       <ns0:c r="O60">
-        <ns0:v>6.004600012302399</ns0:v>
+        <ns0:v>0.9160099965333939</ns0:v>
       </ns0:c>
       <ns0:c r="P60" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q60" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </ns0:c>
       <ns0:c r="T60" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/OPRT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MWYN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4780,59 +4780,59 @@
       </ns0:c>
       <ns0:c r="B61" t="inlineStr">
         <ns0:is>
-          <ns0:t>OVV</ns0:t>
+          <ns0:t>NHC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Ovintiv Inc</ns0:t>
+          <ns0:t>National Healthcare Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Medical Care Facilities</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F61" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다 등 북미에서 석유·천연가스 탐사·개발·생산·판매를 하는 기업.</ns0:t>
+          <ns0:t>전문 간호·생활지원·독립생활 시설, 재택돌봄·호스피스 기관 및 병원 서비스를 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G61">
-        <ns0:v>69.33000183105469</ns0:v>
+        <ns0:v>242.82000732421875</ns0:v>
       </ns0:c>
       <ns0:c r="H61">
-        <ns0:v>4.83896069944465</ns0:v>
+        <ns0:v>-1.1037313031203588</ns0:v>
       </ns0:c>
       <ns0:c r="I61">
-        <ns0:v>67.51000213623047</ns0:v>
+        <ns0:v>245.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="J61">
-        <ns0:v>2.6958963668103353</ns0:v>
+        <ns0:v>-1.148018267560913</ns0:v>
       </ns0:c>
       <ns0:c r="K61">
-        <ns0:v>1.1154811794287436</ns0:v>
+        <ns0:v>0.9012147195426938</ns0:v>
       </ns0:c>
       <ns0:c r="L61">
-        <ns0:v>71.116600306748</ns0:v>
+        <ns0:v>65.62061068347768</ns0:v>
       </ns0:c>
       <ns0:c r="M61">
-        <ns0:v>62.04900016784668</ns0:v>
+        <ns0:v>227.84300079345704</ns0:v>
       </ns0:c>
       <ns0:c r="N61">
-        <ns0:v>63.49740013122559</ns0:v>
+        <ns0:v>225.64639923095703</ns0:v>
       </ns0:c>
       <ns0:c r="O61">
-        <ns0:v>56.038750114440916</ns0:v>
+        <ns0:v>189.39094947814942</ns0:v>
       </ns0:c>
       <ns0:c r="P61" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q61" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </ns0:c>
       <ns0:c r="T61" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/OVV/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NHC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4859,55 +4859,55 @@
       </ns0:c>
       <ns0:c r="B62" t="inlineStr">
         <ns0:is>
-          <ns0:t>PAYC</ns0:t>
+          <ns0:t>OPK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Paycom Software Inc</ns0:t>
+          <ns0:t>Opko Health Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F62" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 중소·중견기업에 채용 등 고용 전 과정을 관리하는 클라우드 인적자본관리 소프트웨어를 제공.</ns0:t>
+          <ns0:t>미국 등 여러 국가에서 의약품 개발과 진단 사업을 운영하는 헬스케어 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G62">
-        <ns0:v>251.63999938964844</ns0:v>
+        <ns0:v>1.5299999713897705</ns0:v>
       </ns0:c>
       <ns0:c r="H62">
-        <ns0:v>-0.4864142647564962</ns0:v>
+        <ns0:v>-4.9689467207783</ns0:v>
       </ns0:c>
       <ns0:c r="I62">
-        <ns0:v>252.8699951171875</ns0:v>
+        <ns0:v>1.75</ns0:v>
       </ns0:c>
       <ns0:c r="J62">
-        <ns0:v>-0.4864142647564962</ns0:v>
+        <ns0:v>-12.571430206298828</ns0:v>
       </ns0:c>
       <ns0:c r="K62">
-        <ns0:v>0.9637810403382574</ns0:v>
+        <ns0:v>2.500472459031798</ns0:v>
       </ns0:c>
       <ns0:c r="L62">
-        <ns0:v>73.6579711934978</ns0:v>
+        <ns0:v>51.712721345434694</ns0:v>
       </ns0:c>
       <ns0:c r="M62">
-        <ns0:v>228.40849914550782</ns0:v>
+        <ns0:v>1.5385000109672546</ns0:v>
       </ns0:c>
       <ns0:c r="N62">
-        <ns0:v>226.47219970703125</ns0:v>
+        <ns0:v>1.5164000082015991</ns0:v>
       </ns0:c>
       <ns0:c r="O62">
-        <ns0:v>158.4820999145508</ns0:v>
+        <ns0:v>1.3282000041007995</ns0:v>
       </ns0:c>
       <ns0:c r="P62" t="inlineStr">
         <ns0:is>
@@ -4926,7 +4926,7 @@
       </ns0:c>
       <ns0:c r="T62" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PAYC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/OPK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4938,55 +4938,55 @@
       </ns0:c>
       <ns0:c r="B63" t="inlineStr">
         <ns0:is>
-          <ns0:t>PAYS</ns0:t>
+          <ns0:t>OPRT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C63" t="inlineStr">
         <ns0:is>
-          <ns0:t>PaySign Inc</ns0:t>
+          <ns0:t>Oportun Financial Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D63" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E63" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Credit Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
+          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
-        <ns0:v>14.800000190734863</ns0:v>
+        <ns0:v>9.079999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="H63">
-        <ns0:v>-5.128206225463517</ns0:v>
+        <ns0:v>-1.4115104658248612</ns0:v>
       </ns0:c>
       <ns0:c r="I63">
-        <ns0:v>15.630000114440918</ns0:v>
+        <ns0:v>9.270000457763672</ns0:v>
       </ns0:c>
       <ns0:c r="J63">
-        <ns0:v>-5.310300176768379</ns0:v>
+        <ns0:v>-2.049628097898215</ns0:v>
       </ns0:c>
       <ns0:c r="K63">
-        <ns0:v>1.4710602304039573</ns0:v>
+        <ns0:v>0.9444764601237754</ns0:v>
       </ns0:c>
       <ns0:c r="L63">
-        <ns0:v>57.77670788456152</ns0:v>
+        <ns0:v>63.905964903145986</ns0:v>
       </ns0:c>
       <ns0:c r="M63">
-        <ns0:v>14.106999969482422</ns0:v>
+        <ns0:v>8.558749961853028</ns0:v>
       </ns0:c>
       <ns0:c r="N63">
-        <ns0:v>13.434199981689453</ns0:v>
+        <ns0:v>8.013299989700318</ns0:v>
       </ns0:c>
       <ns0:c r="O63">
-        <ns0:v>7.840600003004074</ns0:v>
+        <ns0:v>6.004600012302399</ns0:v>
       </ns0:c>
       <ns0:c r="P63" t="inlineStr">
         <ns0:is>
@@ -5005,7 +5005,7 @@
       </ns0:c>
       <ns0:c r="T63" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PAYS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/OPRT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5017,12 +5017,12 @@
       </ns0:c>
       <ns0:c r="B64" t="inlineStr">
         <ns0:is>
-          <ns0:t>PBR</ns0:t>
+          <ns0:t>OVV</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C64" t="inlineStr">
         <ns0:is>
-          <ns0:t>Petroleo Brasileiro SA Petrobras ADR</ns0:t>
+          <ns0:t>Ovintiv Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D64" t="inlineStr">
@@ -5032,40 +5032,40 @@
       </ns0:c>
       <ns0:c r="E64" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F64" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>미국·캐나다 등 북미에서 석유·천연가스 탐사·개발·생산·판매를 하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G64">
-        <ns0:v>26.0</ns0:v>
+        <ns0:v>69.33000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="H64">
-        <ns0:v>2.7668015179781458</ns0:v>
+        <ns0:v>4.83896069944465</ns0:v>
       </ns0:c>
       <ns0:c r="I64">
-        <ns0:v>25.959999084472656</ns0:v>
+        <ns0:v>67.51000213623047</ns0:v>
       </ns0:c>
       <ns0:c r="J64">
-        <ns0:v>0.15408673704950804</ns0:v>
+        <ns0:v>2.6958963668103353</ns0:v>
       </ns0:c>
       <ns0:c r="K64">
-        <ns0:v>0.98571312566959</ns0:v>
+        <ns0:v>1.1159244226380505</ns0:v>
       </ns0:c>
       <ns0:c r="L64">
-        <ns0:v>75.77519716214343</ns0:v>
+        <ns0:v>71.116600306748</ns0:v>
       </ns0:c>
       <ns0:c r="M64">
-        <ns0:v>22.930999851226808</ns0:v>
+        <ns0:v>62.04900016784668</ns0:v>
       </ns0:c>
       <ns0:c r="N64">
-        <ns0:v>20.831399993896483</ns0:v>
+        <ns0:v>63.49740013122559</ns0:v>
       </ns0:c>
       <ns0:c r="O64">
-        <ns0:v>18.53740002632141</ns0:v>
+        <ns0:v>56.038750114440916</ns0:v>
       </ns0:c>
       <ns0:c r="P64" t="inlineStr">
         <ns0:is>
@@ -5084,7 +5084,7 @@
       </ns0:c>
       <ns0:c r="T64" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PBR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/OVV/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5096,59 +5096,59 @@
       </ns0:c>
       <ns0:c r="B65" t="inlineStr">
         <ns0:is>
-          <ns0:t>PBR-A</ns0:t>
+          <ns0:t>PAYC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Petroleo Brasileiro SA Petrobras ADR</ns0:t>
+          <ns0:t>Paycom Software Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F65" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>미국 중소·중견기업에 채용 등 고용 전 과정을 관리하는 클라우드 인적자본관리 소프트웨어를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G65">
-        <ns0:v>23.299999237060547</ns0:v>
+        <ns0:v>251.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="H65">
-        <ns0:v>3.051740858392904</ns0:v>
+        <ns0:v>-0.4864142647564962</ns0:v>
       </ns0:c>
       <ns0:c r="I65">
-        <ns0:v>23.100000381469727</ns0:v>
+        <ns0:v>252.8699951171875</ns0:v>
       </ns0:c>
       <ns0:c r="J65">
-        <ns0:v>0.8657958973509627</ns0:v>
+        <ns0:v>-0.4864142647564962</ns0:v>
       </ns0:c>
       <ns0:c r="K65">
-        <ns0:v>0.859422746564921</ns0:v>
+        <ns0:v>0.9781630322146331</ns0:v>
       </ns0:c>
       <ns0:c r="L65">
-        <ns0:v>75.98905168365474</ns0:v>
+        <ns0:v>73.6579711934978</ns0:v>
       </ns0:c>
       <ns0:c r="M65">
-        <ns0:v>20.688500118255615</ns0:v>
+        <ns0:v>228.40849914550782</ns0:v>
       </ns0:c>
       <ns0:c r="N65">
-        <ns0:v>18.78000005722046</ns0:v>
+        <ns0:v>226.47219970703125</ns0:v>
       </ns0:c>
       <ns0:c r="O65">
-        <ns0:v>16.817950015068053</ns0:v>
+        <ns0:v>158.4820999145508</ns0:v>
       </ns0:c>
       <ns0:c r="P65" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q65" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </ns0:c>
       <ns0:c r="T65" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PBR-A/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PAYC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5175,12 +5175,12 @@
       </ns0:c>
       <ns0:c r="B66" t="inlineStr">
         <ns0:is>
-          <ns0:t>PCTY</ns0:t>
+          <ns0:t>PAYS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C66" t="inlineStr">
         <ns0:is>
-          <ns0:t>Paylocity Holding Corp</ns0:t>
+          <ns0:t>PaySign Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D66" t="inlineStr">
@@ -5190,40 +5190,40 @@
       </ns0:c>
       <ns0:c r="E66" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F66" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 급여·세무·인사 관리 등을 지원하는 클라우드 인적자본관리·재무·IT 소프트웨어를 제공.</ns0:t>
+          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G66">
-        <ns0:v>166.32000732421875</ns0:v>
+        <ns0:v>14.800000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H66">
-        <ns0:v>0.04210966870301647</ns0:v>
+        <ns0:v>-5.128206225463517</ns0:v>
       </ns0:c>
       <ns0:c r="I66">
-        <ns0:v>166.47500610351562</ns0:v>
+        <ns0:v>15.630000114440918</ns0:v>
       </ns0:c>
       <ns0:c r="J66">
-        <ns0:v>-0.09310633645539523</ns0:v>
+        <ns0:v>-5.310300176768379</ns0:v>
       </ns0:c>
       <ns0:c r="K66">
-        <ns0:v>0.6932671489676295</ns0:v>
+        <ns0:v>1.4724721900382405</ns0:v>
       </ns0:c>
       <ns0:c r="L66">
-        <ns0:v>76.95542866744297</ns0:v>
+        <ns0:v>57.77670788456152</ns0:v>
       </ns0:c>
       <ns0:c r="M66">
-        <ns0:v>149.68050308227538</ns0:v>
+        <ns0:v>14.106999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="N66">
-        <ns0:v>149.64280120849608</ns0:v>
+        <ns0:v>13.434199981689453</ns0:v>
       </ns0:c>
       <ns0:c r="O66">
-        <ns0:v>125.22487525939941</ns0:v>
+        <ns0:v>7.840600003004074</ns0:v>
       </ns0:c>
       <ns0:c r="P66" t="inlineStr">
         <ns0:is>
@@ -5242,7 +5242,7 @@
       </ns0:c>
       <ns0:c r="T66" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PCTY/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PAYS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5254,59 +5254,59 @@
       </ns0:c>
       <ns0:c r="B67" t="inlineStr">
         <ns0:is>
-          <ns0:t>PD</ns0:t>
+          <ns0:t>PBR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C67" t="inlineStr">
         <ns0:is>
-          <ns0:t>Pagerduty Inc</ns0:t>
+          <ns0:t>Petroleo Brasileiro SA Petrobras ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D67" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E67" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F67" t="inlineStr">
         <ns0:is>
-          <ns0:t>소프트웨어·기기의 데이터와 디지털 신호를 수집하고 AI·머신러닝을 활용하는 디지털 운영 관리 플랫폼 운영.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G67">
-        <ns0:v>16.15999984741211</ns0:v>
+        <ns0:v>26.0</ns0:v>
       </ns0:c>
       <ns0:c r="H67">
-        <ns0:v>-6.318841464277625</ns0:v>
+        <ns0:v>2.7668015179781458</ns0:v>
       </ns0:c>
       <ns0:c r="I67">
-        <ns0:v>17.299999237060547</ns0:v>
+        <ns0:v>25.959999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="J67">
-        <ns0:v>-6.5895921382834395</ns0:v>
+        <ns0:v>0.15408673704950804</ns0:v>
       </ns0:c>
       <ns0:c r="K67">
-        <ns0:v>0.9539213729233382</ns0:v>
+        <ns0:v>0.9925749760058186</ns0:v>
       </ns0:c>
       <ns0:c r="L67">
-        <ns0:v>60.303365393249344</ns0:v>
+        <ns0:v>75.77519716214343</ns0:v>
       </ns0:c>
       <ns0:c r="M67">
-        <ns0:v>15.493999910354614</ns0:v>
+        <ns0:v>22.930999851226808</ns0:v>
       </ns0:c>
       <ns0:c r="N67">
-        <ns0:v>14.01639991760254</ns0:v>
+        <ns0:v>20.831399993896483</ns0:v>
       </ns0:c>
       <ns0:c r="O67">
-        <ns0:v>9.889999990463258</ns0:v>
+        <ns0:v>18.53740002632141</ns0:v>
       </ns0:c>
       <ns0:c r="P67" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q67" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </ns0:c>
       <ns0:c r="T67" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PBR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5333,59 +5333,59 @@
       </ns0:c>
       <ns0:c r="B68" t="inlineStr">
         <ns0:is>
-          <ns0:t>PEB</ns0:t>
+          <ns0:t>PBR-A</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C68" t="inlineStr">
         <ns0:is>
-          <ns0:t>Pebblebrook Hotel Trust</ns0:t>
+          <ns0:t>Petroleo Brasileiro SA Petrobras ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D68" t="inlineStr">
         <ns0:is>
-          <ns0:t>Real Estate</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E68" t="inlineStr">
         <ns0:is>
-          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F68" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국의 도심·리조트형 라이프스타일 호텔을 보유한 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G68">
-        <ns0:v>19.489999771118164</ns0:v>
+        <ns0:v>23.299999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="H68">
-        <ns0:v>0.6714832472530574</ns0:v>
+        <ns0:v>3.051740858392904</ns0:v>
       </ns0:c>
       <ns0:c r="I68">
-        <ns0:v>19.93000030517578</ns0:v>
+        <ns0:v>23.100000381469727</ns0:v>
       </ns0:c>
       <ns0:c r="J68">
-        <ns0:v>-2.2077296905176125</ns0:v>
+        <ns0:v>0.8657958973509627</ns0:v>
       </ns0:c>
       <ns0:c r="K68">
-        <ns0:v>1.2283256248652017</ns0:v>
+        <ns0:v>0.861018472833233</ns0:v>
       </ns0:c>
       <ns0:c r="L68">
-        <ns0:v>61.906370053998664</ns0:v>
+        <ns0:v>75.98905168365474</ns0:v>
       </ns0:c>
       <ns0:c r="M68">
-        <ns0:v>18.87649984359741</ns0:v>
+        <ns0:v>20.688500118255615</ns0:v>
       </ns0:c>
       <ns0:c r="N68">
-        <ns0:v>18.41319995880127</ns0:v>
+        <ns0:v>18.78000005722046</ns0:v>
       </ns0:c>
       <ns0:c r="O68">
-        <ns0:v>15.630599975585938</ns0:v>
+        <ns0:v>16.817950015068053</ns0:v>
       </ns0:c>
       <ns0:c r="P68" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q68" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </ns0:c>
       <ns0:c r="T68" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PEB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PBR-A/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5412,55 +5412,55 @@
       </ns0:c>
       <ns0:c r="B69" t="inlineStr">
         <ns0:is>
-          <ns0:t>PK</ns0:t>
+          <ns0:t>PCTY</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C69" t="inlineStr">
         <ns0:is>
-          <ns0:t>Park Hotels &amp; Resorts Inc</ns0:t>
+          <ns0:t>Paylocity Holding Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D69" t="inlineStr">
         <ns0:is>
-          <ns0:t>Real Estate</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E69" t="inlineStr">
         <ns0:is>
-          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F69" t="inlineStr">
         <ns0:is>
-          <ns0:t>상징성과 시장 경쟁력을 갖춘 다양한 호텔·리조트를 보유한 대형 상장 숙박 부동산투자신탁.</ns0:t>
+          <ns0:t>미국에서 급여·세무·인사 관리 등을 지원하는 클라우드 인적자본관리·재무·IT 소프트웨어를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G69">
-        <ns0:v>15.90999984741211</ns0:v>
+        <ns0:v>166.32000732421875</ns0:v>
       </ns0:c>
       <ns0:c r="H69">
-        <ns0:v>1.2086487096428788</ns0:v>
+        <ns0:v>0.04210966870301647</ns0:v>
       </ns0:c>
       <ns0:c r="I69">
-        <ns0:v>16.200000762939453</ns0:v>
+        <ns0:v>166.47500610351562</ns0:v>
       </ns0:c>
       <ns0:c r="J69">
-        <ns0:v>-1.790129023887299</ns0:v>
+        <ns0:v>-0.09310633645539523</ns0:v>
       </ns0:c>
       <ns0:c r="K69">
-        <ns0:v>1.718229444750101</ns0:v>
+        <ns0:v>0.6932762015404461</ns0:v>
       </ns0:c>
       <ns0:c r="L69">
-        <ns0:v>61.0018738412593</ns0:v>
+        <ns0:v>76.95542866744297</ns0:v>
       </ns0:c>
       <ns0:c r="M69">
-        <ns0:v>15.366999959945678</ns0:v>
+        <ns0:v>149.68050308227538</ns0:v>
       </ns0:c>
       <ns0:c r="N69">
-        <ns0:v>15.322799987792969</ns0:v>
+        <ns0:v>149.64280120849608</ns0:v>
       </ns0:c>
       <ns0:c r="O69">
-        <ns0:v>12.94864999294281</ns0:v>
+        <ns0:v>125.22487525939941</ns0:v>
       </ns0:c>
       <ns0:c r="P69" t="inlineStr">
         <ns0:is>
@@ -5479,7 +5479,7 @@
       </ns0:c>
       <ns0:c r="T69" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PCTY/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5491,59 +5491,59 @@
       </ns0:c>
       <ns0:c r="B70" t="inlineStr">
         <ns0:is>
-          <ns0:t>PSO</ns0:t>
+          <ns0:t>PD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C70" t="inlineStr">
         <ns0:is>
-          <ns0:t>Pearson plc ADR</ns0:t>
+          <ns0:t>Pagerduty Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D70" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E70" t="inlineStr">
         <ns0:is>
-          <ns0:t>Publishing</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F70" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 교육 교재·평가·자격인증·온라인 학습·영어 학습 등 교육 서비스를 제공.</ns0:t>
+          <ns0:t>소프트웨어·기기의 데이터와 디지털 신호를 수집하고 AI·머신러닝을 활용하는 디지털 운영 관리 플랫폼 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G70">
-        <ns0:v>18.239999771118164</ns0:v>
+        <ns0:v>16.15999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H70">
-        <ns0:v>2.127654802801948</ns0:v>
+        <ns0:v>-6.318841464277625</ns0:v>
       </ns0:c>
       <ns0:c r="I70">
-        <ns0:v>18.020000457763672</ns0:v>
+        <ns0:v>17.299999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="J70">
-        <ns0:v>1.2208618632953971</ns0:v>
+        <ns0:v>-6.5895921382834395</ns0:v>
       </ns0:c>
       <ns0:c r="K70">
-        <ns0:v>1.754568661670602</ns0:v>
+        <ns0:v>0.9539500504668535</ns0:v>
       </ns0:c>
       <ns0:c r="L70">
-        <ns0:v>81.69764980842487</ns0:v>
+        <ns0:v>60.303365393249344</ns0:v>
       </ns0:c>
       <ns0:c r="M70">
-        <ns0:v>16.534999799728393</ns0:v>
+        <ns0:v>15.493999910354614</ns0:v>
       </ns0:c>
       <ns0:c r="N70">
-        <ns0:v>16.311599884033203</ns0:v>
+        <ns0:v>14.01639991760254</ns0:v>
       </ns0:c>
       <ns0:c r="O70">
-        <ns0:v>14.869599967002868</ns0:v>
+        <ns0:v>9.889999990463258</ns0:v>
       </ns0:c>
       <ns0:c r="P70" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q70" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </ns0:c>
       <ns0:c r="T70" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PSO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5570,59 +5570,59 @@
       </ns0:c>
       <ns0:c r="B71" t="inlineStr">
         <ns0:is>
-          <ns0:t>REPX</ns0:t>
+          <ns0:t>PEB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C71" t="inlineStr">
         <ns0:is>
-          <ns0:t>Riley Exploration Permian Inc</ns0:t>
+          <ns0:t>Pebblebrook Hotel Trust</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D71" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Real Estate</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E71" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F71" t="inlineStr">
         <ns0:is>
-          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
+          <ns0:t>미국의 도심·리조트형 라이프스타일 호텔을 보유한 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G71">
-        <ns0:v>48.68000030517578</ns0:v>
+        <ns0:v>19.489999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="H71">
-        <ns0:v>3.574468734416558</ns0:v>
+        <ns0:v>0.6714832472530574</ns0:v>
       </ns0:c>
       <ns0:c r="I71">
-        <ns0:v>48.0099983215332</ns0:v>
+        <ns0:v>19.93000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J71">
-        <ns0:v>1.3955467758099749</ns0:v>
+        <ns0:v>-2.2077296905176125</ns0:v>
       </ns0:c>
       <ns0:c r="K71">
-        <ns0:v>0.8832134812713773</ns0:v>
+        <ns0:v>1.228315167781726</ns0:v>
       </ns0:c>
       <ns0:c r="L71">
-        <ns0:v>73.13204827475457</ns0:v>
+        <ns0:v>61.906370053998664</ns0:v>
       </ns0:c>
       <ns0:c r="M71">
-        <ns0:v>43.12199954986572</ns0:v>
+        <ns0:v>18.87649984359741</ns0:v>
       </ns0:c>
       <ns0:c r="N71">
-        <ns0:v>40.97599983215332</ns0:v>
+        <ns0:v>18.41319995880127</ns0:v>
       </ns0:c>
       <ns0:c r="O71">
-        <ns0:v>34.925299882888794</ns0:v>
+        <ns0:v>15.630599975585938</ns0:v>
       </ns0:c>
       <ns0:c r="P71" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q71" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </ns0:c>
       <ns0:c r="T71" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/REPX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PEB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5649,59 +5649,59 @@
       </ns0:c>
       <ns0:c r="B72" t="inlineStr">
         <ns0:is>
-          <ns0:t>RGA</ns0:t>
+          <ns0:t>PK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C72" t="inlineStr">
         <ns0:is>
-          <ns0:t>Reinsurance Group Of America Inc</ns0:t>
+          <ns0:t>Park Hotels &amp; Resorts Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D72" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Real Estate</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E72" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Reinsurance</ns0:t>
+          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F72" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 생명·건강 및 자산집약형 재보험을 제공하며 장애·장기요양 관련 보장도 취급.</ns0:t>
+          <ns0:t>상징성과 시장 경쟁력을 갖춘 다양한 호텔·리조트를 보유한 대형 상장 숙박 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G72">
-        <ns0:v>266.75</ns0:v>
+        <ns0:v>15.90999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H72">
-        <ns0:v>1.0263563730407377</ns0:v>
+        <ns0:v>1.2086487096428788</ns0:v>
       </ns0:c>
       <ns0:c r="I72">
-        <ns0:v>265.4100036621094</ns0:v>
+        <ns0:v>16.200000762939453</ns0:v>
       </ns0:c>
       <ns0:c r="J72">
-        <ns0:v>0.5048778566751233</ns0:v>
+        <ns0:v>-1.790129023887299</ns0:v>
       </ns0:c>
       <ns0:c r="K72">
-        <ns0:v>0.9625349507697329</ns0:v>
+        <ns0:v>1.7182202298838114</ns0:v>
       </ns0:c>
       <ns0:c r="L72">
-        <ns0:v>73.40938380051415</ns0:v>
+        <ns0:v>61.0018738412593</ns0:v>
       </ns0:c>
       <ns0:c r="M72">
-        <ns0:v>252.68399963378906</ns0:v>
+        <ns0:v>15.366999959945678</ns0:v>
       </ns0:c>
       <ns0:c r="N72">
-        <ns0:v>249.18380004882812</ns0:v>
+        <ns0:v>15.322799987792969</ns0:v>
       </ns0:c>
       <ns0:c r="O72">
-        <ns0:v>221.53910026550292</ns0:v>
+        <ns0:v>12.94864999294281</ns0:v>
       </ns0:c>
       <ns0:c r="P72" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q72" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </ns0:c>
       <ns0:c r="T72" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RGA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5728,59 +5728,59 @@
       </ns0:c>
       <ns0:c r="B73" t="inlineStr">
         <ns0:is>
-          <ns0:t>SAFT</ns0:t>
+          <ns0:t>PSO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C73" t="inlineStr">
         <ns0:is>
-          <ns0:t>Safety Insurance Group Inc</ns0:t>
+          <ns0:t>Pearson plc ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D73" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E73" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
+          <ns0:t>Publishing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F73" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 매사추세츠주에서 개인용·상업용 자동차보험과 주택 소유자 보험을 제공하는 회사.</ns0:t>
+          <ns0:t>세계 각지에서 교육 교재·평가·자격인증·온라인 학습·영어 학습 등 교육 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G73">
-        <ns0:v>104.02999877929688</ns0:v>
+        <ns0:v>18.239999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="H73">
-        <ns0:v>0.028844980093145622</ns0:v>
+        <ns0:v>2.127654802801948</ns0:v>
       </ns0:c>
       <ns0:c r="I73">
-        <ns0:v>104.11000061035156</ns0:v>
+        <ns0:v>18.020000457763672</ns0:v>
       </ns0:c>
       <ns0:c r="J73">
-        <ns0:v>-0.07684356025902117</ns0:v>
+        <ns0:v>1.2208618632953971</ns0:v>
       </ns0:c>
       <ns0:c r="K73">
-        <ns0:v>0.4386733128834356</ns0:v>
+        <ns0:v>1.7814734969031243</ns0:v>
       </ns0:c>
       <ns0:c r="L73">
-        <ns0:v>72.7275005366069</ns0:v>
+        <ns0:v>81.69764980842487</ns0:v>
       </ns0:c>
       <ns0:c r="M73">
-        <ns0:v>103.77050018310547</ns0:v>
+        <ns0:v>16.534999799728393</ns0:v>
       </ns0:c>
       <ns0:c r="N73">
-        <ns0:v>103.58340026855468</ns0:v>
+        <ns0:v>16.311599884033203</ns0:v>
       </ns0:c>
       <ns0:c r="O73">
-        <ns0:v>83.26774997711182</ns0:v>
+        <ns0:v>14.869599967002868</ns0:v>
       </ns0:c>
       <ns0:c r="P73" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q73" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </ns0:c>
       <ns0:c r="T73" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SAFT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PSO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5807,59 +5807,59 @@
       </ns0:c>
       <ns0:c r="B74" t="inlineStr">
         <ns0:is>
-          <ns0:t>SG</ns0:t>
+          <ns0:t>REPX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Sweetgreen Inc</ns0:t>
+          <ns0:t>Riley Exploration Permian Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Restaurants</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F74" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 건강한 음식과 음료를 제공하는 패스트푸드 식당을 운영하며 온라인·모바일 주문을 지원.</ns0:t>
+          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G74">
-        <ns0:v>10.039999961853027</ns0:v>
+        <ns0:v>48.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H74">
-        <ns0:v>-5.283022636448742</ns0:v>
+        <ns0:v>3.574468734416558</ns0:v>
       </ns0:c>
       <ns0:c r="I74">
-        <ns0:v>10.640000343322754</ns0:v>
+        <ns0:v>48.0099983215332</ns0:v>
       </ns0:c>
       <ns0:c r="J74">
-        <ns0:v>-5.639101147644821</ns0:v>
+        <ns0:v>1.3955467758099749</ns0:v>
       </ns0:c>
       <ns0:c r="K74">
-        <ns0:v>0.7411254287061543</ns0:v>
+        <ns0:v>0.8862934846083257</ns0:v>
       </ns0:c>
       <ns0:c r="L74">
-        <ns0:v>70.64199752903355</ns0:v>
+        <ns0:v>73.13204827475457</ns0:v>
       </ns0:c>
       <ns0:c r="M74">
-        <ns0:v>9.012000060081482</ns0:v>
+        <ns0:v>43.12199954986572</ns0:v>
       </ns0:c>
       <ns0:c r="N74">
-        <ns0:v>7.53640001296997</ns0:v>
+        <ns0:v>40.97599983215332</ns0:v>
       </ns0:c>
       <ns0:c r="O74">
-        <ns0:v>7.041099991798401</ns0:v>
+        <ns0:v>34.925299882888794</ns0:v>
       </ns0:c>
       <ns0:c r="P74" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q74" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </ns0:c>
       <ns0:c r="T74" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SG/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/REPX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5886,55 +5886,55 @@
       </ns0:c>
       <ns0:c r="B75" t="inlineStr">
         <ns0:is>
-          <ns0:t>SHEL</ns0:t>
+          <ns0:t>RGA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C75" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Plc ADR</ns0:t>
+          <ns0:t>Reinsurance Group Of America Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D75" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E75" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Insurance - Reinsurance</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F75" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
+          <ns0:t>전 세계에서 생명·건강 및 자산집약형 재보험을 제공하며 장애·장기요양 관련 보장도 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G75">
-        <ns0:v>106.66000366210938</ns0:v>
+        <ns0:v>266.75</ns0:v>
       </ns0:c>
       <ns0:c r="H75">
-        <ns0:v>3.003380510570408</ns0:v>
+        <ns0:v>1.0263563730407377</ns0:v>
       </ns0:c>
       <ns0:c r="I75">
-        <ns0:v>104.69999694824219</ns0:v>
+        <ns0:v>265.4100036621094</ns0:v>
       </ns0:c>
       <ns0:c r="J75">
-        <ns0:v>1.87202174880301</ns0:v>
+        <ns0:v>0.5048778566751233</ns0:v>
       </ns0:c>
       <ns0:c r="K75">
-        <ns0:v>0.8768975462799125</ns0:v>
+        <ns0:v>0.9626285154762553</ns0:v>
       </ns0:c>
       <ns0:c r="L75">
-        <ns0:v>80.66399706670381</ns0:v>
+        <ns0:v>73.40938380051415</ns0:v>
       </ns0:c>
       <ns0:c r="M75">
-        <ns0:v>98.11150016784669</ns0:v>
+        <ns0:v>252.68399963378906</ns0:v>
       </ns0:c>
       <ns0:c r="N75">
-        <ns0:v>95.02219985961914</ns0:v>
+        <ns0:v>249.18380004882812</ns0:v>
       </ns0:c>
       <ns0:c r="O75">
-        <ns0:v>86.65434997558594</ns0:v>
+        <ns0:v>221.53910026550292</ns0:v>
       </ns0:c>
       <ns0:c r="P75" t="inlineStr">
         <ns0:is>
@@ -5953,7 +5953,7 @@
       </ns0:c>
       <ns0:c r="T75" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SHEL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/RGA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5965,59 +5965,59 @@
       </ns0:c>
       <ns0:c r="B76" t="inlineStr">
         <ns0:is>
-          <ns0:t>SHO</ns0:t>
+          <ns0:t>RNR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C76" t="inlineStr">
         <ns0:is>
-          <ns0:t>Sunstone Hotel Investors Inc</ns0:t>
+          <ns0:t>RenaissanceRe Holdings Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D76" t="inlineStr">
         <ns0:is>
-          <ns0:t>Real Estate</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E76" t="inlineStr">
         <ns0:is>
-          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
+          <ns0:t>Insurance - Reinsurance</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F76" t="inlineStr">
         <ns0:is>
-          <ns0:t>입지가 좋은 호텔·리조트 부동산을 인수·적극 운영·매각하는 숙박 부동산투자신탁.</ns0:t>
+          <ns0:t>미국과 해외에서 재산·상해·특종 보험과 재보험을 제공하며 재산 재해 초과손해 재보험을 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G76">
-        <ns0:v>11.829999923706055</ns0:v>
+        <ns0:v>351.05999755859375</ns0:v>
       </ns0:c>
       <ns0:c r="H76">
-        <ns0:v>-0.3369836751362598</ns0:v>
+        <ns0:v>2.004879655701841</ns0:v>
       </ns0:c>
       <ns0:c r="I76">
-        <ns0:v>12.069999694824219</ns0:v>
+        <ns0:v>349.25</ns0:v>
       </ns0:c>
       <ns0:c r="J76">
-        <ns0:v>-1.9883991481878804</ns0:v>
+        <ns0:v>0.5182527011005744</ns0:v>
       </ns0:c>
       <ns0:c r="K76">
-        <ns0:v>4.853884450274267</ns0:v>
+        <ns0:v>0.7500216876727268</ns0:v>
       </ns0:c>
       <ns0:c r="L76">
-        <ns0:v>67.9246020565415</ns0:v>
+        <ns0:v>73.05418397676948</ns0:v>
       </ns0:c>
       <ns0:c r="M76">
-        <ns0:v>11.337500047683715</ns0:v>
+        <ns0:v>330.0585021972656</ns0:v>
       </ns0:c>
       <ns0:c r="N76">
-        <ns0:v>11.161600017547608</ns0:v>
+        <ns0:v>327.40000122070313</ns0:v>
       </ns0:c>
       <ns0:c r="O76">
-        <ns0:v>10.388449988365174</ns0:v>
+        <ns0:v>306.6820506286621</ns0:v>
       </ns0:c>
       <ns0:c r="P76" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q76" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </ns0:c>
       <ns0:c r="T76" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SHO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/RNR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6044,55 +6044,55 @@
       </ns0:c>
       <ns0:c r="B77" t="inlineStr">
         <ns0:is>
-          <ns0:t>SIG</ns0:t>
+          <ns0:t>SAFT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C77" t="inlineStr">
         <ns0:is>
-          <ns0:t>Signet Jewelers Ltd</ns0:t>
+          <ns0:t>Safety Insurance Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D77" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E77" t="inlineStr">
         <ns0:is>
-          <ns0:t>Luxury Goods</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F77" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국·아일랜드에서 다이아몬드 주얼리 소매점을 운영.</ns0:t>
+          <ns0:t>미국 매사추세츠주에서 개인용·상업용 자동차보험과 주택 소유자 보험을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G77">
-        <ns0:v>118.48999786376953</ns0:v>
+        <ns0:v>104.02999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="H77">
-        <ns0:v>0.2792774131962661</ns0:v>
+        <ns0:v>0.028844980093145622</ns0:v>
       </ns0:c>
       <ns0:c r="I77">
-        <ns0:v>120.0</ns0:v>
+        <ns0:v>104.11000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="J77">
-        <ns0:v>-1.2583351135253884</ns0:v>
+        <ns0:v>-0.07684356025902117</ns0:v>
       </ns0:c>
       <ns0:c r="K77">
-        <ns0:v>1.301387490542545</ns0:v>
+        <ns0:v>0.4386503067484663</ns0:v>
       </ns0:c>
       <ns0:c r="L77">
-        <ns0:v>77.33558677628399</ns0:v>
+        <ns0:v>72.7275005366069</ns0:v>
       </ns0:c>
       <ns0:c r="M77">
-        <ns0:v>104.64800033569335</ns0:v>
+        <ns0:v>103.77050018310547</ns0:v>
       </ns0:c>
       <ns0:c r="N77">
-        <ns0:v>95.8136001586914</ns0:v>
+        <ns0:v>103.58340026855468</ns0:v>
       </ns0:c>
       <ns0:c r="O77">
-        <ns0:v>90.61249980926513</ns0:v>
+        <ns0:v>83.26774997711182</ns0:v>
       </ns0:c>
       <ns0:c r="P77" t="inlineStr">
         <ns0:is>
@@ -6111,7 +6111,7 @@
       </ns0:c>
       <ns0:c r="T77" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SIG/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SAFT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6123,59 +6123,59 @@
       </ns0:c>
       <ns0:c r="B78" t="inlineStr">
         <ns0:is>
-          <ns0:t>SLDE</ns0:t>
+          <ns0:t>SG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C78" t="inlineStr">
         <ns0:is>
-          <ns0:t>Slide Insurance Holdings Inc</ns0:t>
+          <ns0:t>Sweetgreen Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D78" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E78" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
+          <ns0:t>Restaurants</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F78" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 해안 지역 주택·콘도·상업용 주거시설 등의 손해보험과 재보험·보험대리 서비스를 제공.</ns0:t>
+          <ns0:t>미국에서 건강한 음식과 음료를 제공하는 패스트푸드 식당을 운영하며 온라인·모바일 주문을 지원.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G78">
-        <ns0:v>27.06999969482422</ns0:v>
+        <ns0:v>10.039999961853027</ns0:v>
       </ns0:c>
       <ns0:c r="H78">
-        <ns0:v>2.035427795712552</ns0:v>
+        <ns0:v>-5.283022636448742</ns0:v>
       </ns0:c>
       <ns0:c r="I78">
-        <ns0:v>26.75</ns0:v>
+        <ns0:v>10.640000343322754</ns0:v>
       </ns0:c>
       <ns0:c r="J78">
-        <ns0:v>1.1962605413989413</ns0:v>
+        <ns0:v>-5.639101147644821</ns0:v>
       </ns0:c>
       <ns0:c r="K78">
-        <ns0:v>1.1376881591517185</ns0:v>
+        <ns0:v>0.7417531726452036</ns0:v>
       </ns0:c>
       <ns0:c r="L78">
-        <ns0:v>71.3211289123893</ns0:v>
+        <ns0:v>70.64199752903355</ns0:v>
       </ns0:c>
       <ns0:c r="M78">
-        <ns0:v>24.300499820709227</ns0:v>
+        <ns0:v>9.012000060081482</ns0:v>
       </ns0:c>
       <ns0:c r="N78">
-        <ns0:v>23.767999877929686</ns0:v>
+        <ns0:v>7.53640001296997</ns0:v>
       </ns0:c>
       <ns0:c r="O78">
-        <ns0:v>19.680474953651427</ns0:v>
+        <ns0:v>7.041099991798401</ns0:v>
       </ns0:c>
       <ns0:c r="P78" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q78" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </ns0:c>
       <ns0:c r="T78" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SLDE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6202,55 +6202,55 @@
       </ns0:c>
       <ns0:c r="B79" t="inlineStr">
         <ns0:is>
-          <ns0:t>SSL</ns0:t>
+          <ns0:t>SHEL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C79" t="inlineStr">
         <ns0:is>
-          <ns0:t>Sasol Ltd ADR</ns0:t>
+          <ns0:t>Shell Plc ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D79" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E79" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Chemicals</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F79" t="inlineStr">
         <ns0:is>
-          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청, 연료, 나프타, 윤활유, 액화석유가스 등을 공급한다.</ns0:t>
+          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G79">
-        <ns0:v>16.34000015258789</ns0:v>
+        <ns0:v>106.66000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="H79">
-        <ns0:v>2.6381914213641</ns0:v>
+        <ns0:v>3.003380510570408</ns0:v>
       </ns0:c>
       <ns0:c r="I79">
-        <ns0:v>16.170000076293945</ns0:v>
+        <ns0:v>104.69999694824219</ns0:v>
       </ns0:c>
       <ns0:c r="J79">
-        <ns0:v>1.0513300896217936</ns0:v>
+        <ns0:v>1.87202174880301</ns0:v>
       </ns0:c>
       <ns0:c r="K79">
-        <ns0:v>1.1305368181070345</ns0:v>
+        <ns0:v>0.8739402567556783</ns0:v>
       </ns0:c>
       <ns0:c r="L79">
-        <ns0:v>78.23812960396783</ns0:v>
+        <ns0:v>80.66399706670381</ns0:v>
       </ns0:c>
       <ns0:c r="M79">
-        <ns0:v>14.551500034332275</ns0:v>
+        <ns0:v>98.11150016784669</ns0:v>
       </ns0:c>
       <ns0:c r="N79">
-        <ns0:v>13.378000030517578</ns0:v>
+        <ns0:v>95.02219985961914</ns0:v>
       </ns0:c>
       <ns0:c r="O79">
-        <ns0:v>11.383150002956391</ns0:v>
+        <ns0:v>86.65434997558594</ns0:v>
       </ns0:c>
       <ns0:c r="P79" t="inlineStr">
         <ns0:is>
@@ -6269,7 +6269,7 @@
       </ns0:c>
       <ns0:c r="T79" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SSL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SHEL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6281,59 +6281,59 @@
       </ns0:c>
       <ns0:c r="B80" t="inlineStr">
         <ns0:is>
-          <ns0:t>SU</ns0:t>
+          <ns0:t>SHO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C80" t="inlineStr">
         <ns0:is>
-          <ns0:t>Suncor Energy Inc</ns0:t>
+          <ns0:t>Sunstone Hotel Investors Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D80" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Real Estate</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E80" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>REIT - Hotel &amp; Motel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F80" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>입지가 좋은 호텔·리조트 부동산을 인수·적극 운영·매각하는 숙박 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G80">
-        <ns0:v>78.05000305175781</ns0:v>
+        <ns0:v>11.829999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="H80">
-        <ns0:v>3.186149764087909</ns0:v>
+        <ns0:v>-0.3369836751362598</ns0:v>
       </ns0:c>
       <ns0:c r="I80">
-        <ns0:v>76.7300033569336</ns0:v>
+        <ns0:v>12.069999694824219</ns0:v>
       </ns0:c>
       <ns0:c r="J80">
-        <ns0:v>1.7203175251848002</ns0:v>
+        <ns0:v>-1.9883991481878804</ns0:v>
       </ns0:c>
       <ns0:c r="K80">
-        <ns0:v>1.6024241393180865</ns0:v>
+        <ns0:v>4.853873519357659</ns0:v>
       </ns0:c>
       <ns0:c r="L80">
-        <ns0:v>76.14014525785537</ns0:v>
+        <ns0:v>67.9246020565415</ns0:v>
       </ns0:c>
       <ns0:c r="M80">
-        <ns0:v>70.41850051879882</ns0:v>
+        <ns0:v>11.337500047683715</ns0:v>
       </ns0:c>
       <ns0:c r="N80">
-        <ns0:v>68.41820022583008</ns0:v>
+        <ns0:v>11.161600017547608</ns0:v>
       </ns0:c>
       <ns0:c r="O80">
-        <ns0:v>61.85835023880005</ns0:v>
+        <ns0:v>10.388449988365174</ns0:v>
       </ns0:c>
       <ns0:c r="P80" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q80" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </ns0:c>
       <ns0:c r="T80" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SU/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SHO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6360,52 +6360,55 @@
       </ns0:c>
       <ns0:c r="B81" t="inlineStr">
         <ns0:is>
-          <ns0:t>SVCC</ns0:t>
+          <ns0:t>SIG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C81" t="inlineStr">
         <ns0:is>
-          <ns0:t>Stellar V Capital Corp</ns0:t>
+          <ns0:t>Signet Jewelers Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D81" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E81" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Companies</ns0:t>
+          <ns0:t>Luxury Goods</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F81" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 합병·주식교환·자산 인수 등 기업결합을 추진하는 기업.</ns0:t>
+          <ns0:t>미국·캐나다·영국·아일랜드에서 다이아몬드 주얼리 소매점을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G81">
-        <ns0:v>10.710000038146973</ns0:v>
+        <ns0:v>118.48999786376953</ns0:v>
       </ns0:c>
       <ns0:c r="H81">
-        <ns0:v>-0.09328571485761605</ns0:v>
+        <ns0:v>0.2792774131962661</ns0:v>
       </ns0:c>
       <ns0:c r="I81">
-        <ns0:v>10.720000267028809</ns0:v>
+        <ns0:v>120.0</ns0:v>
       </ns0:c>
       <ns0:c r="J81">
-        <ns0:v>-0.09328571485761605</ns0:v>
+        <ns0:v>-1.2583351135253884</ns0:v>
+      </ns0:c>
+      <ns0:c r="K81">
+        <ns0:v>1.3013457883793944</ns0:v>
       </ns0:c>
       <ns0:c r="L81">
-        <ns0:v>56.99581733614353</ns0:v>
+        <ns0:v>77.33558677628399</ns0:v>
       </ns0:c>
       <ns0:c r="M81">
-        <ns0:v>10.705500078201293</ns0:v>
+        <ns0:v>104.64800033569335</ns0:v>
       </ns0:c>
       <ns0:c r="N81">
-        <ns0:v>10.678299980163574</ns0:v>
+        <ns0:v>95.8136001586914</ns0:v>
       </ns0:c>
       <ns0:c r="O81">
-        <ns0:v>10.535514979362487</ns0:v>
+        <ns0:v>90.61249980926513</ns0:v>
       </ns0:c>
       <ns0:c r="P81" t="inlineStr">
         <ns0:is>
@@ -6424,7 +6427,7 @@
       </ns0:c>
       <ns0:c r="T81" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SVCC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SIG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6436,55 +6439,55 @@
       </ns0:c>
       <ns0:c r="B82" t="inlineStr">
         <ns0:is>
-          <ns0:t>TBBB</ns0:t>
+          <ns0:t>SLDE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C82" t="inlineStr">
         <ns0:is>
-          <ns0:t>BBB Foods Inc</ns0:t>
+          <ns0:t>Slide Insurance Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D82" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Defensive</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E82" t="inlineStr">
         <ns0:is>
-          <ns0:t>Discount Stores</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F82" t="inlineStr">
         <ns0:is>
-          <ns0:t>멕시코에서 식료품 소매 체인을 운영하며 식품·의류·전자제품·생활용품 등을 판매한다.</ns0:t>
+          <ns0:t>미국에서 해안 지역 주택·콘도·상업용 주거시설 등의 손해보험과 재보험·보험대리 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G82">
-        <ns0:v>57.68000030517578</ns0:v>
+        <ns0:v>27.06999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H82">
-        <ns0:v>2.9448537601763913</ns0:v>
+        <ns0:v>2.035427795712552</ns0:v>
       </ns0:c>
       <ns0:c r="I82">
-        <ns0:v>57.29999923706055</ns0:v>
+        <ns0:v>26.75</ns0:v>
       </ns0:c>
       <ns0:c r="J82">
-        <ns0:v>0.6631781381760682</ns0:v>
+        <ns0:v>1.1962605413989413</ns0:v>
       </ns0:c>
       <ns0:c r="K82">
-        <ns0:v>1.0149968107857974</ns0:v>
+        <ns0:v>1.1376896815519348</ns0:v>
       </ns0:c>
       <ns0:c r="L82">
-        <ns0:v>72.55042763894151</ns0:v>
+        <ns0:v>71.3211289123893</ns0:v>
       </ns0:c>
       <ns0:c r="M82">
-        <ns0:v>53.90900020599365</ns0:v>
+        <ns0:v>24.300499820709227</ns0:v>
       </ns0:c>
       <ns0:c r="N82">
-        <ns0:v>50.85120018005371</ns0:v>
+        <ns0:v>23.767999877929686</ns0:v>
       </ns0:c>
       <ns0:c r="O82">
-        <ns0:v>40.71095012664795</ns0:v>
+        <ns0:v>19.680474953651427</ns0:v>
       </ns0:c>
       <ns0:c r="P82" t="inlineStr">
         <ns0:is>
@@ -6503,7 +6506,7 @@
       </ns0:c>
       <ns0:c r="T82" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TBBB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SLDE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6515,59 +6518,59 @@
       </ns0:c>
       <ns0:c r="B83" t="inlineStr">
         <ns0:is>
-          <ns0:t>TEAM</ns0:t>
+          <ns0:t>SSL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C83" t="inlineStr">
         <ns0:is>
-          <ns0:t>Atlassian Corp</ns0:t>
+          <ns0:t>Sasol Ltd ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D83" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E83" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Specialty Chemicals</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F83" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 조직의 팀 연결과 생산성 향상을 돕는 협업 소프트웨어를 제공한다.</ns0:t>
+          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청, 연료, 나프타, 윤활유, 액화석유가스 등을 공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G83">
-        <ns0:v>207.82000732421875</ns0:v>
+        <ns0:v>16.34000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H83">
-        <ns0:v>-4.283340089405041</ns0:v>
+        <ns0:v>2.6381914213641</ns0:v>
       </ns0:c>
       <ns0:c r="I83">
-        <ns0:v>217.25</ns0:v>
+        <ns0:v>16.170000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="J83">
-        <ns0:v>-4.340618032580556</ns0:v>
+        <ns0:v>1.0513300896217936</ns0:v>
       </ns0:c>
       <ns0:c r="K83">
-        <ns0:v>1.0104641607896754</ns0:v>
+        <ns0:v>1.1305732484076434</ns0:v>
       </ns0:c>
       <ns0:c r="L83">
-        <ns0:v>60.84298926352619</ns0:v>
+        <ns0:v>78.23812960396783</ns0:v>
       </ns0:c>
       <ns0:c r="M83">
-        <ns0:v>195.67549896240234</ns0:v>
+        <ns0:v>14.551500034332275</ns0:v>
       </ns0:c>
       <ns0:c r="N83">
-        <ns0:v>183.98649963378907</ns0:v>
+        <ns0:v>13.378000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="O83">
-        <ns0:v>114.43982498168945</ns0:v>
+        <ns0:v>11.383150002956391</ns0:v>
       </ns0:c>
       <ns0:c r="P83" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q83" t="inlineStr">
@@ -6582,7 +6585,7 @@
       </ns0:c>
       <ns0:c r="T83" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TEAM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SSL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6594,59 +6597,59 @@
       </ns0:c>
       <ns0:c r="B84" t="inlineStr">
         <ns0:is>
-          <ns0:t>URBN</ns0:t>
+          <ns0:t>SU</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C84" t="inlineStr">
         <ns0:is>
-          <ns0:t>Urban Outfitters Inc</ns0:t>
+          <ns0:t>Suncor Energy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D84" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E84" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Retail</ns0:t>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F84" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 소매·도매·구독 사업으로 의류·신발·액세서리 등 라이프스타일 상품과 서비스 제공.</ns0:t>
+          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G84">
-        <ns0:v>86.56999969482422</ns0:v>
+        <ns0:v>78.05000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="H84">
-        <ns0:v>-0.9496588290206498</ns0:v>
+        <ns0:v>3.186149764087909</ns0:v>
       </ns0:c>
       <ns0:c r="I84">
-        <ns0:v>88.05999755859375</ns0:v>
+        <ns0:v>76.7300033569336</ns0:v>
       </ns0:c>
       <ns0:c r="J84">
-        <ns0:v>-1.6920257836461006</ns0:v>
+        <ns0:v>1.7203175251848002</ns0:v>
       </ns0:c>
       <ns0:c r="K84">
-        <ns0:v>1.158214801907309</ns0:v>
+        <ns0:v>1.6584319362405513</ns0:v>
       </ns0:c>
       <ns0:c r="L84">
-        <ns0:v>69.9439481192651</ns0:v>
+        <ns0:v>76.14014525785537</ns0:v>
       </ns0:c>
       <ns0:c r="M84">
-        <ns0:v>79.6069995880127</ns0:v>
+        <ns0:v>70.41850051879882</ns0:v>
       </ns0:c>
       <ns0:c r="N84">
-        <ns0:v>78.37879974365234</ns0:v>
+        <ns0:v>68.41820022583008</ns0:v>
       </ns0:c>
       <ns0:c r="O84">
-        <ns0:v>72.47064996719361</ns0:v>
+        <ns0:v>61.85835023880005</ns0:v>
       </ns0:c>
       <ns0:c r="P84" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q84" t="inlineStr">
@@ -6661,7 +6664,7 @@
       </ns0:c>
       <ns0:c r="T84" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/URBN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SU/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6673,12 +6676,12 @@
       </ns0:c>
       <ns0:c r="B85" t="inlineStr">
         <ns0:is>
-          <ns0:t>UVE</ns0:t>
+          <ns0:t>SVCC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C85" t="inlineStr">
         <ns0:is>
-          <ns0:t>Universal Insurance Holdings Inc</ns0:t>
+          <ns0:t>Stellar V Capital Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D85" t="inlineStr">
@@ -6688,40 +6691,37 @@
       </ns0:c>
       <ns0:c r="E85" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F85" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 주택 소유자·임차인·콘도 소유자 등을 위한 주거 보험을 제공하는 보험 지주사.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식교환·자산 인수 등 기업결합을 추진하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G85">
-        <ns0:v>47.119998931884766</ns0:v>
+        <ns0:v>10.710000038146973</ns0:v>
       </ns0:c>
       <ns0:c r="H85">
-        <ns0:v>0.5977770674311156</ns0:v>
+        <ns0:v>-0.09328571485761605</ns0:v>
       </ns0:c>
       <ns0:c r="I85">
-        <ns0:v>47.68000030517578</ns0:v>
+        <ns0:v>10.720000267028809</ns0:v>
       </ns0:c>
       <ns0:c r="J85">
-        <ns0:v>-1.1744995170023698</ns0:v>
-      </ns0:c>
-      <ns0:c r="K85">
-        <ns0:v>0.7008938803575522</ns0:v>
+        <ns0:v>-0.09328571485761605</ns0:v>
       </ns0:c>
       <ns0:c r="L85">
-        <ns0:v>66.46598264114957</ns0:v>
+        <ns0:v>56.99581733614353</ns0:v>
       </ns0:c>
       <ns0:c r="M85">
-        <ns0:v>44.33800010681152</ns0:v>
+        <ns0:v>10.705500078201293</ns0:v>
       </ns0:c>
       <ns0:c r="N85">
-        <ns0:v>43.840600128173826</ns0:v>
+        <ns0:v>10.678299980163574</ns0:v>
       </ns0:c>
       <ns0:c r="O85">
-        <ns0:v>38.06580002784729</ns0:v>
+        <ns0:v>10.535514979362487</ns0:v>
       </ns0:c>
       <ns0:c r="P85" t="inlineStr">
         <ns0:is>
@@ -6740,7 +6740,7 @@
       </ns0:c>
       <ns0:c r="T85" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/UVE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SVCC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6752,59 +6752,59 @@
       </ns0:c>
       <ns0:c r="B86" t="inlineStr">
         <ns0:is>
-          <ns0:t>V</ns0:t>
+          <ns0:t>TBBB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C86" t="inlineStr">
         <ns0:is>
-          <ns0:t>Visa Inc</ns0:t>
+          <ns0:t>BBB Foods Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D86" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E86" t="inlineStr">
         <ns0:is>
-          <ns0:t>Credit Services</ns0:t>
+          <ns0:t>Discount Stores</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F86" t="inlineStr">
         <ns0:is>
-          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공.</ns0:t>
+          <ns0:t>멕시코에서 식료품 소매 체인을 운영하며 식품·의류·전자제품·생활용품 등을 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G86">
-        <ns0:v>402.6099853515625</ns0:v>
+        <ns0:v>57.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H86">
-        <ns0:v>0.7154434900719098</ns0:v>
+        <ns0:v>2.9448537601763913</ns0:v>
       </ns0:c>
       <ns0:c r="I86">
-        <ns0:v>403.2099914550781</ns0:v>
+        <ns0:v>57.29999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="J86">
-        <ns0:v>-0.14880735007343215</ns0:v>
+        <ns0:v>0.6631781381760682</ns0:v>
       </ns0:c>
       <ns0:c r="K86">
-        <ns0:v>1.0258334250526595</ns0:v>
+        <ns0:v>1.0808309466338157</ns0:v>
       </ns0:c>
       <ns0:c r="L86">
-        <ns0:v>73.6235477463431</ns0:v>
+        <ns0:v>72.55042763894151</ns0:v>
       </ns0:c>
       <ns0:c r="M86">
-        <ns0:v>374.7225006103516</ns0:v>
+        <ns0:v>53.90900020599365</ns0:v>
       </ns0:c>
       <ns0:c r="N86">
-        <ns0:v>372.5044024658203</ns0:v>
+        <ns0:v>50.85120018005371</ns0:v>
       </ns0:c>
       <ns0:c r="O86">
-        <ns0:v>339.1856001281738</ns0:v>
+        <ns0:v>40.71095012664795</ns0:v>
       </ns0:c>
       <ns0:c r="P86" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q86" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </ns0:c>
       <ns0:c r="T86" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/V/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/TBBB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6831,55 +6831,55 @@
       </ns0:c>
       <ns0:c r="B87" t="inlineStr">
         <ns0:is>
-          <ns0:t>VABK</ns0:t>
+          <ns0:t>TEAM</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C87" t="inlineStr">
         <ns0:is>
-          <ns0:t>Virginia National Bankshares Corp</ns0:t>
+          <ns0:t>Atlassian Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D87" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E87" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F87" t="inlineStr">
         <ns0:is>
-          <ns0:t>버지니아 내 상업·개인 금융 서비스를 제공하는 은행의 지주회사로 은행 및 신탁·상속재산 서비스 운영.</ns0:t>
+          <ns0:t>전 세계 조직의 팀 연결과 생산성 향상을 돕는 협업 소프트웨어를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G87">
-        <ns0:v>50.85499954223633</ns0:v>
+        <ns0:v>207.82000732421875</ns0:v>
       </ns0:c>
       <ns0:c r="H87">
-        <ns0:v>-1.1564649404859018</ns0:v>
+        <ns0:v>-4.283340089405041</ns0:v>
       </ns0:c>
       <ns0:c r="I87">
-        <ns0:v>52.0099983215332</ns0:v>
+        <ns0:v>217.25</ns0:v>
       </ns0:c>
       <ns0:c r="J87">
-        <ns0:v>-2.220724507923477</ns0:v>
+        <ns0:v>-4.340618032580556</ns0:v>
       </ns0:c>
       <ns0:c r="K87">
-        <ns0:v>2.458705035971223</ns0:v>
+        <ns0:v>1.0107681460501645</ns0:v>
       </ns0:c>
       <ns0:c r="L87">
-        <ns0:v>64.41681021449222</ns0:v>
+        <ns0:v>60.84298926352619</ns0:v>
       </ns0:c>
       <ns0:c r="M87">
-        <ns0:v>48.62125015258789</ns0:v>
+        <ns0:v>195.67549896240234</ns0:v>
       </ns0:c>
       <ns0:c r="N87">
-        <ns0:v>47.70550003051758</ns0:v>
+        <ns0:v>183.98649963378907</ns0:v>
       </ns0:c>
       <ns0:c r="O87">
-        <ns0:v>43.369475021362305</ns0:v>
+        <ns0:v>114.43982498168945</ns0:v>
       </ns0:c>
       <ns0:c r="P87" t="inlineStr">
         <ns0:is>
@@ -6898,7 +6898,7 @@
       </ns0:c>
       <ns0:c r="T87" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VABK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/TEAM/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6910,55 +6910,55 @@
       </ns0:c>
       <ns0:c r="B88" t="inlineStr">
         <ns0:is>
-          <ns0:t>VEEV</ns0:t>
+          <ns0:t>URBN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C88" t="inlineStr">
         <ns0:is>
-          <ns0:t>Veeva Systems Inc</ns0:t>
+          <ns0:t>Urban Outfitters Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D88" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E88" t="inlineStr">
         <ns0:is>
-          <ns0:t>Health Information Services</ns0:t>
+          <ns0:t>Apparel Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F88" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어를 제공하며 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소매·도매·구독 사업으로 의류·신발·액세서리 등 라이프스타일 상품과 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G88">
-        <ns0:v>310.3599853515625</ns0:v>
+        <ns0:v>86.56999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H88">
-        <ns0:v>-0.8529576839748421</ns0:v>
+        <ns0:v>-0.9496588290206498</ns0:v>
       </ns0:c>
       <ns0:c r="I88">
-        <ns0:v>315.0199890136719</ns0:v>
+        <ns0:v>88.05999755859375</ns0:v>
       </ns0:c>
       <ns0:c r="J88">
-        <ns0:v>-1.4792723714770806</ns0:v>
+        <ns0:v>-1.6920257836461006</ns0:v>
       </ns0:c>
       <ns0:c r="K88">
-        <ns0:v>1.0263071250811995</ns0:v>
+        <ns0:v>1.1582535244244527</ns0:v>
       </ns0:c>
       <ns0:c r="L88">
-        <ns0:v>71.19253007250407</ns0:v>
+        <ns0:v>69.9439481192651</ns0:v>
       </ns0:c>
       <ns0:c r="M88">
-        <ns0:v>284.81849975585936</ns0:v>
+        <ns0:v>79.6069995880127</ns0:v>
       </ns0:c>
       <ns0:c r="N88">
-        <ns0:v>268.81559997558594</ns0:v>
+        <ns0:v>78.37879974365234</ns0:v>
       </ns0:c>
       <ns0:c r="O88">
-        <ns0:v>204.86990043640137</ns0:v>
+        <ns0:v>72.47064996719361</ns0:v>
       </ns0:c>
       <ns0:c r="P88" t="inlineStr">
         <ns0:is>
@@ -6977,7 +6977,7 @@
       </ns0:c>
       <ns0:c r="T88" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VEEV/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/URBN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6989,55 +6989,55 @@
       </ns0:c>
       <ns0:c r="B89" t="inlineStr">
         <ns0:is>
-          <ns0:t>VNCE</ns0:t>
+          <ns0:t>UVE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C89" t="inlineStr">
         <ns0:is>
-          <ns0:t>Vince Holding Corp</ns0:t>
+          <ns0:t>Universal Insurance Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D89" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E89" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Manufacturing</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F89" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 도매·소비자 직접판매 사업을 운영하며 캐시미어 스웨터·실크 블라우스 등 여성복을 판매한다.</ns0:t>
+          <ns0:t>미국에서 주택 소유자·임차인·콘도 소유자 등을 위한 주거 보험을 제공하는 보험 지주사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G89">
-        <ns0:v>12.859999656677246</ns0:v>
+        <ns0:v>47.119998931884766</ns0:v>
       </ns0:c>
       <ns0:c r="H89">
-        <ns0:v>-3.52588349376477</ns0:v>
+        <ns0:v>0.5977770674311156</ns0:v>
       </ns0:c>
       <ns0:c r="I89">
-        <ns0:v>13.449999809265137</ns0:v>
+        <ns0:v>47.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J89">
-        <ns0:v>-4.3866182970609735</ns0:v>
+        <ns0:v>-1.1744995170023698</ns0:v>
       </ns0:c>
       <ns0:c r="K89">
-        <ns0:v>0.970879102754412</ns0:v>
+        <ns0:v>0.7095016171339802</ns0:v>
       </ns0:c>
       <ns0:c r="L89">
-        <ns0:v>63.50809697096953</ns0:v>
+        <ns0:v>66.46598264114957</ns0:v>
       </ns0:c>
       <ns0:c r="M89">
-        <ns0:v>11.268499946594238</ns0:v>
+        <ns0:v>44.33800010681152</ns0:v>
       </ns0:c>
       <ns0:c r="N89">
-        <ns0:v>8.560799980163575</ns0:v>
+        <ns0:v>43.840600128173826</ns0:v>
       </ns0:c>
       <ns0:c r="O89">
-        <ns0:v>5.2583999979496</ns0:v>
+        <ns0:v>38.06580002784729</ns0:v>
       </ns0:c>
       <ns0:c r="P89" t="inlineStr">
         <ns0:is>
@@ -7056,7 +7056,7 @@
       </ns0:c>
       <ns0:c r="T89" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VNCE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/UVE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7068,55 +7068,55 @@
       </ns0:c>
       <ns0:c r="B90" t="inlineStr">
         <ns0:is>
-          <ns0:t>VRA</ns0:t>
+          <ns0:t>V</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C90" t="inlineStr">
         <ns0:is>
-          <ns0:t>Vera Bradley Inc</ns0:t>
+          <ns0:t>Visa Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D90" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E90" t="inlineStr">
         <ns0:is>
-          <ns0:t>Footwear &amp; Accessories</ns0:t>
+          <ns0:t>Credit Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F90" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 여성용 핸드백, 여행 가방·용품, 패션·홈 액세서리와 선물용품을 디자인·제조한다.</ns0:t>
+          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G90">
-        <ns0:v>5.849999904632568</ns0:v>
+        <ns0:v>402.6099853515625</ns0:v>
       </ns0:c>
       <ns0:c r="H90">
-        <ns0:v>-2.3372265748761722</ns0:v>
+        <ns0:v>0.7154434900719098</ns0:v>
       </ns0:c>
       <ns0:c r="I90">
-        <ns0:v>6.019999980926514</ns0:v>
+        <ns0:v>403.2099914550781</ns0:v>
       </ns0:c>
       <ns0:c r="J90">
-        <ns0:v>-2.8239215420691965</ns0:v>
+        <ns0:v>-0.14880735007343215</ns0:v>
       </ns0:c>
       <ns0:c r="K90">
-        <ns0:v>1.0869582580184118</ns0:v>
+        <ns0:v>1.0292806042089682</ns0:v>
       </ns0:c>
       <ns0:c r="L90">
-        <ns0:v>74.30454937769449</ns0:v>
+        <ns0:v>73.6235477463431</ns0:v>
       </ns0:c>
       <ns0:c r="M90">
-        <ns0:v>4.886500000953674</ns0:v>
+        <ns0:v>374.7225006103516</ns0:v>
       </ns0:c>
       <ns0:c r="N90">
-        <ns0:v>3.972000002861023</ns0:v>
+        <ns0:v>372.5044024658203</ns0:v>
       </ns0:c>
       <ns0:c r="O90">
-        <ns0:v>3.501800004243851</ns0:v>
+        <ns0:v>339.1856001281738</ns0:v>
       </ns0:c>
       <ns0:c r="P90" t="inlineStr">
         <ns0:is>
@@ -7135,7 +7135,7 @@
       </ns0:c>
       <ns0:c r="T90" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VRA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/V/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7147,59 +7147,59 @@
       </ns0:c>
       <ns0:c r="B91" t="inlineStr">
         <ns0:is>
-          <ns0:t>VTRS</ns0:t>
+          <ns0:t>VABK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C91" t="inlineStr">
         <ns0:is>
-          <ns0:t>Viatris Inc</ns0:t>
+          <ns0:t>Virginia National Bankshares Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D91" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E91" t="inlineStr">
         <ns0:is>
-          <ns0:t>Drug Manufacturers - Specialty &amp; Generic</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F91" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미·유럽·아시아 등 세계 여러 지역에서 자회사와 함께 헬스케어 사업을 운영한다.</ns0:t>
+          <ns0:t>버지니아 내 상업·개인 금융 서비스를 제공하는 은행의 지주회사로 은행 및 신탁·상속재산 서비스 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G91">
-        <ns0:v>18.655000686645508</ns0:v>
+        <ns0:v>50.86000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="H91">
-        <ns0:v>2.3874939060627653</ns0:v>
+        <ns0:v>-1.146744691620838</ns0:v>
       </ns0:c>
       <ns0:c r="I91">
-        <ns0:v>18.43000030517578</ns0:v>
+        <ns0:v>52.0099983215332</ns0:v>
       </ns0:c>
       <ns0:c r="J91">
-        <ns0:v>1.2208376437548907</ns0:v>
+        <ns0:v>-2.21110891808185</ns0:v>
       </ns0:c>
       <ns0:c r="K91">
-        <ns0:v>0.9970656661763756</ns0:v>
+        <ns0:v>2.4556354916067145</ns0:v>
       </ns0:c>
       <ns0:c r="L91">
-        <ns0:v>69.12686266591909</ns0:v>
+        <ns0:v>64.45555644674292</ns0:v>
       </ns0:c>
       <ns0:c r="M91">
-        <ns0:v>17.632750225067138</ns0:v>
+        <ns0:v>48.621500205993655</ns0:v>
       </ns0:c>
       <ns0:c r="N91">
-        <ns0:v>16.97810012817383</ns0:v>
+        <ns0:v>47.705600051879884</ns0:v>
       </ns0:c>
       <ns0:c r="O91">
-        <ns0:v>15.599425029754638</ns0:v>
+        <ns0:v>43.36950002670288</ns0:v>
       </ns0:c>
       <ns0:c r="P91" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q91" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </ns0:c>
       <ns0:c r="T91" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VTRS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VABK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7226,55 +7226,55 @@
       </ns0:c>
       <ns0:c r="B92" t="inlineStr">
         <ns0:is>
-          <ns0:t>WPP</ns0:t>
+          <ns0:t>VEEV</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C92" t="inlineStr">
         <ns0:is>
-          <ns0:t>WPP Plc ADR</ns0:t>
+          <ns0:t>Veeva Systems Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D92" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E92" t="inlineStr">
         <ns0:is>
-          <ns0:t>Advertising Agencies</ns0:t>
+          <ns0:t>Health Information Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F92" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 커뮤니케이션·경험·커머스·기술 서비스를 제공하는 크리에이티브 전환 기업.</ns0:t>
+          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어를 제공하며 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G92">
-        <ns0:v>27.280000686645508</ns0:v>
+        <ns0:v>310.3599853515625</ns0:v>
       </ns0:c>
       <ns0:c r="H92">
-        <ns0:v>0.44182930746530236</ns0:v>
+        <ns0:v>-0.8529576839748421</ns0:v>
       </ns0:c>
       <ns0:c r="I92">
-        <ns0:v>27.780000686645508</ns0:v>
+        <ns0:v>315.0199890136719</ns0:v>
       </ns0:c>
       <ns0:c r="J92">
-        <ns0:v>-1.7998559670315717</ns0:v>
+        <ns0:v>-1.4792723714770806</ns0:v>
       </ns0:c>
       <ns0:c r="K92">
-        <ns0:v>3.4675143471468126</ns0:v>
+        <ns0:v>1.0263605164727274</ns0:v>
       </ns0:c>
       <ns0:c r="L92">
-        <ns0:v>63.9461053517599</ns0:v>
+        <ns0:v>71.19253007250407</ns0:v>
       </ns0:c>
       <ns0:c r="M92">
-        <ns0:v>25.494499969482423</ns0:v>
+        <ns0:v>284.81849975585936</ns0:v>
       </ns0:c>
       <ns0:c r="N92">
-        <ns0:v>25.771200065612792</ns0:v>
+        <ns0:v>268.81559997558594</ns0:v>
       </ns0:c>
       <ns0:c r="O92">
-        <ns0:v>20.29899998664856</ns0:v>
+        <ns0:v>204.86990043640137</ns0:v>
       </ns0:c>
       <ns0:c r="P92" t="inlineStr">
         <ns0:is>
@@ -7293,7 +7293,7 @@
       </ns0:c>
       <ns0:c r="T92" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/WPP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VEEV/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7305,12 +7305,12 @@
       </ns0:c>
       <ns0:c r="B93" t="inlineStr">
         <ns0:is>
-          <ns0:t>WSM</ns0:t>
+          <ns0:t>VNCE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C93" t="inlineStr">
         <ns0:is>
-          <ns0:t>Williams-Sonoma Inc</ns0:t>
+          <ns0:t>Vince Holding Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D93" t="inlineStr">
@@ -7320,40 +7320,40 @@
       </ns0:c>
       <ns0:c r="E93" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Retail</ns0:t>
+          <ns0:t>Apparel Manufacturing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F93" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 온·오프라인으로 조리·식사·접객용품과 가구 등 가정용 제품을 판매.</ns0:t>
+          <ns0:t>미국과 해외에서 도매·소비자 직접판매 사업을 운영하며 캐시미어 스웨터·실크 블라우스 등 여성복을 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G93">
-        <ns0:v>250.16000366210938</ns0:v>
+        <ns0:v>12.859999656677246</ns0:v>
       </ns0:c>
       <ns0:c r="H93">
-        <ns0:v>-0.7419732278874713</ns0:v>
+        <ns0:v>-3.52588349376477</ns0:v>
       </ns0:c>
       <ns0:c r="I93">
-        <ns0:v>254.88999938964844</ns0:v>
+        <ns0:v>13.449999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="J93">
-        <ns0:v>-1.85570078813031</ns0:v>
+        <ns0:v>-4.3866182970609735</ns0:v>
       </ns0:c>
       <ns0:c r="K93">
-        <ns0:v>1.5409097687021502</ns0:v>
+        <ns0:v>0.9722359667931167</ns0:v>
       </ns0:c>
       <ns0:c r="L93">
-        <ns0:v>66.22834076108995</ns0:v>
+        <ns0:v>63.50809697096953</ns0:v>
       </ns0:c>
       <ns0:c r="M93">
-        <ns0:v>236.42800064086913</ns0:v>
+        <ns0:v>11.268499946594238</ns0:v>
       </ns0:c>
       <ns0:c r="N93">
-        <ns0:v>234.6311996459961</ns0:v>
+        <ns0:v>8.560799980163575</ns0:v>
       </ns0:c>
       <ns0:c r="O93">
-        <ns0:v>211.59334999084473</ns0:v>
+        <ns0:v>5.2583999979496</ns0:v>
       </ns0:c>
       <ns0:c r="P93" t="inlineStr">
         <ns0:is>
@@ -7372,7 +7372,7 @@
       </ns0:c>
       <ns0:c r="T93" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/WSM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VNCE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7384,55 +7384,55 @@
       </ns0:c>
       <ns0:c r="B94" t="inlineStr">
         <ns0:is>
-          <ns0:t>WST</ns0:t>
+          <ns0:t>VRA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C94" t="inlineStr">
         <ns0:is>
-          <ns0:t>West Pharmaceutical Services Inc</ns0:t>
+          <ns0:t>Vera Bradley Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D94" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E94" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
+          <ns0:t>Footwear &amp; Accessories</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F94" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 주사제와 헬스케어 제품의 보관·투여 시스템을 설계·제조·판매.</ns0:t>
+          <ns0:t>미국에서 여성용 핸드백, 여행 가방·용품, 패션·홈 액세서리와 선물용품을 디자인·제조한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G94">
-        <ns0:v>384.0199890136719</ns0:v>
+        <ns0:v>5.849999904632568</ns0:v>
       </ns0:c>
       <ns0:c r="H94">
-        <ns0:v>0.2610829796573011</ns0:v>
+        <ns0:v>-2.3372265748761722</ns0:v>
       </ns0:c>
       <ns0:c r="I94">
-        <ns0:v>386.0</ns0:v>
+        <ns0:v>6.019999980926514</ns0:v>
       </ns0:c>
       <ns0:c r="J94">
-        <ns0:v>-0.5129562140746446</ns0:v>
+        <ns0:v>-2.8239215420691965</ns0:v>
       </ns0:c>
       <ns0:c r="K94">
-        <ns0:v>0.8793157129710064</ns0:v>
+        <ns0:v>1.1021900878557316</ns0:v>
       </ns0:c>
       <ns0:c r="L94">
-        <ns0:v>65.56343407533834</ns0:v>
+        <ns0:v>74.30454937769449</ns0:v>
       </ns0:c>
       <ns0:c r="M94">
-        <ns0:v>371.60350189208987</ns0:v>
+        <ns0:v>4.886500000953674</ns0:v>
       </ns0:c>
       <ns0:c r="N94">
-        <ns0:v>358.1402020263672</ns0:v>
+        <ns0:v>3.972000002861023</ns0:v>
       </ns0:c>
       <ns0:c r="O94">
-        <ns0:v>307.28840072631834</ns0:v>
+        <ns0:v>3.501800004243851</ns0:v>
       </ns0:c>
       <ns0:c r="P94" t="inlineStr">
         <ns0:is>
@@ -7451,7 +7451,7 @@
       </ns0:c>
       <ns0:c r="T94" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/WST/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VRA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7463,55 +7463,55 @@
       </ns0:c>
       <ns0:c r="B95" t="inlineStr">
         <ns0:is>
-          <ns0:t>XOM</ns0:t>
+          <ns0:t>VTRS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C95" t="inlineStr">
         <ns0:is>
-          <ns0:t>ExxonMobil Holdings Corp</ns0:t>
+          <ns0:t>Viatris Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D95" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E95" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+          <ns0:t>Drug Manufacturers - Specialty &amp; Generic</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F95" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업을 운영한다.</ns0:t>
+          <ns0:t>북미·유럽·아시아 등 세계 여러 지역에서 자회사와 함께 헬스케어 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G95">
-        <ns0:v>178.97999572753906</ns0:v>
+        <ns0:v>18.65999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H95">
-        <ns0:v>2.4616459995730144</ns0:v>
+        <ns0:v>2.4149316720067926</ns0:v>
       </ns0:c>
       <ns0:c r="I95">
-        <ns0:v>178.69000244140625</ns0:v>
+        <ns0:v>18.43000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J95">
-        <ns0:v>0.16228847846588845</ns0:v>
+        <ns0:v>1.247962769548816</ns0:v>
       </ns0:c>
       <ns0:c r="K95">
-        <ns0:v>1.0164476904399438</ns0:v>
+        <ns0:v>0.9976629105922992</ns0:v>
       </ns0:c>
       <ns0:c r="L95">
-        <ns0:v>72.9509082610167</ns0:v>
+        <ns0:v>69.17328759155848</ns0:v>
       </ns0:c>
       <ns0:c r="M95">
-        <ns0:v>166.11449966430663</ns0:v>
+        <ns0:v>17.63300018310547</ns0:v>
       </ns0:c>
       <ns0:c r="N95">
-        <ns0:v>163.68860046386717</ns0:v>
+        <ns0:v>16.97820011138916</ns0:v>
       </ns0:c>
       <ns0:c r="O95">
-        <ns0:v>151.71649990081787</ns0:v>
+        <ns0:v>15.599450025558472</ns0:v>
       </ns0:c>
       <ns0:c r="P95" t="inlineStr">
         <ns0:is>
@@ -7530,7 +7530,7 @@
       </ns0:c>
       <ns0:c r="T95" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/XOM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VTRS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7542,79 +7542,395 @@
       </ns0:c>
       <ns0:c r="B96" t="inlineStr">
         <ns0:is>
+          <ns0:t>WPP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WPP Plc ADR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Advertising Agencies</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전 세계에서 커뮤니케이션·경험·커머스·기술 서비스를 제공하는 크리에이티브 전환 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G96">
+        <ns0:v>27.280000686645508</ns0:v>
+      </ns0:c>
+      <ns0:c r="H96">
+        <ns0:v>0.44182930746530236</ns0:v>
+      </ns0:c>
+      <ns0:c r="I96">
+        <ns0:v>27.780000686645508</ns0:v>
+      </ns0:c>
+      <ns0:c r="J96">
+        <ns0:v>-1.7998559670315717</ns0:v>
+      </ns0:c>
+      <ns0:c r="K96">
+        <ns0:v>3.4674462852104506</ns0:v>
+      </ns0:c>
+      <ns0:c r="L96">
+        <ns0:v>63.9461053517599</ns0:v>
+      </ns0:c>
+      <ns0:c r="M96">
+        <ns0:v>25.494499969482423</ns0:v>
+      </ns0:c>
+      <ns0:c r="N96">
+        <ns0:v>25.771200065612792</ns0:v>
+      </ns0:c>
+      <ns0:c r="O96">
+        <ns0:v>20.29899998664856</ns0:v>
+      </ns0:c>
+      <ns0:c r="P96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R96" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/WPP/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="97">
+      <ns0:c r="A97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-16</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WSM</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Williams-Sonoma Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Specialty Retail</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국과 해외에서 온·오프라인으로 조리·식사·접객용품과 가구 등 가정용 제품을 판매.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G97">
+        <ns0:v>250.16000366210938</ns0:v>
+      </ns0:c>
+      <ns0:c r="H97">
+        <ns0:v>-0.7419732278874713</ns0:v>
+      </ns0:c>
+      <ns0:c r="I97">
+        <ns0:v>254.88999938964844</ns0:v>
+      </ns0:c>
+      <ns0:c r="J97">
+        <ns0:v>-1.85570078813031</ns0:v>
+      </ns0:c>
+      <ns0:c r="K97">
+        <ns0:v>1.5409063603713375</ns0:v>
+      </ns0:c>
+      <ns0:c r="L97">
+        <ns0:v>66.22834076108995</ns0:v>
+      </ns0:c>
+      <ns0:c r="M97">
+        <ns0:v>236.42800064086913</ns0:v>
+      </ns0:c>
+      <ns0:c r="N97">
+        <ns0:v>234.6311996459961</ns0:v>
+      </ns0:c>
+      <ns0:c r="O97">
+        <ns0:v>211.59334999084473</ns0:v>
+      </ns0:c>
+      <ns0:c r="P97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R97" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/WSM/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="98">
+      <ns0:c r="A98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-16</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WST</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>West Pharmaceutical Services Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전 세계에서 주사제와 헬스케어 제품의 보관·투여 시스템을 설계·제조·판매.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G98">
+        <ns0:v>384.0199890136719</ns0:v>
+      </ns0:c>
+      <ns0:c r="H98">
+        <ns0:v>0.2610829796573011</ns0:v>
+      </ns0:c>
+      <ns0:c r="I98">
+        <ns0:v>386.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="J98">
+        <ns0:v>-0.5129562140746446</ns0:v>
+      </ns0:c>
+      <ns0:c r="K98">
+        <ns0:v>0.8793552770777606</ns0:v>
+      </ns0:c>
+      <ns0:c r="L98">
+        <ns0:v>65.56343407533834</ns0:v>
+      </ns0:c>
+      <ns0:c r="M98">
+        <ns0:v>371.60350189208987</ns0:v>
+      </ns0:c>
+      <ns0:c r="N98">
+        <ns0:v>358.1402020263672</ns0:v>
+      </ns0:c>
+      <ns0:c r="O98">
+        <ns0:v>307.28840072631834</ns0:v>
+      </ns0:c>
+      <ns0:c r="P98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R98" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/WST/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="99">
+      <ns0:c r="A99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-16</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>XOM</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ExxonMobil Holdings Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Energy</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Oil &amp; Gas Integrated</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업을 운영한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G99">
+        <ns0:v>178.97999572753906</ns0:v>
+      </ns0:c>
+      <ns0:c r="H99">
+        <ns0:v>2.4616459995730144</ns0:v>
+      </ns0:c>
+      <ns0:c r="I99">
+        <ns0:v>178.69000244140625</ns0:v>
+      </ns0:c>
+      <ns0:c r="J99">
+        <ns0:v>0.16228847846588845</ns0:v>
+      </ns0:c>
+      <ns0:c r="K99">
+        <ns0:v>1.0173472337309464</ns0:v>
+      </ns0:c>
+      <ns0:c r="L99">
+        <ns0:v>72.9509082610167</ns0:v>
+      </ns0:c>
+      <ns0:c r="M99">
+        <ns0:v>166.11449966430663</ns0:v>
+      </ns0:c>
+      <ns0:c r="N99">
+        <ns0:v>163.68860046386717</ns0:v>
+      </ns0:c>
+      <ns0:c r="O99">
+        <ns0:v>151.71649990081787</ns0:v>
+      </ns0:c>
+      <ns0:c r="P99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R99" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/XOM/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="100">
+      <ns0:c r="A100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-16</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B100" t="inlineStr">
+        <ns0:is>
           <ns0:t>ZETA</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C96" t="inlineStr">
+      <ns0:c r="C100" t="inlineStr">
         <ns0:is>
           <ns0:t>Zeta Global Holdings Corp</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D96" t="inlineStr">
+      <ns0:c r="D100" t="inlineStr">
         <ns0:is>
           <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E96" t="inlineStr">
+      <ns0:c r="E100" t="inlineStr">
         <ns0:is>
           <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F96" t="inlineStr">
+      <ns0:c r="F100" t="inlineStr">
         <ns0:is>
           <ns0:t>미국과 해외 기업에 소비자 인텔리전스와 마케팅 자동화 소프트웨어를 제공하는 옴니채널 데이터 기반 플랫폼 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G96">
+      <ns0:c r="G100">
         <ns0:v>31.809999465942383</ns0:v>
       </ns0:c>
-      <ns0:c r="H96">
+      <ns0:c r="H100">
         <ns0:v>-5.186288556442342</ns0:v>
       </ns0:c>
-      <ns0:c r="I96">
+      <ns0:c r="I100">
         <ns0:v>34.91999816894531</ns0:v>
       </ns0:c>
-      <ns0:c r="J96">
+      <ns0:c r="J100">
         <ns0:v>-8.906067772273484</ns0:v>
       </ns0:c>
-      <ns0:c r="K96">
-        <ns0:v>1.5766332225042488</ns0:v>
-      </ns0:c>
-      <ns0:c r="L96">
+      <ns0:c r="K100">
+        <ns0:v>1.5801572779529924</ns0:v>
+      </ns0:c>
+      <ns0:c r="L100">
         <ns0:v>51.1492184176021</ns0:v>
       </ns0:c>
-      <ns0:c r="M96">
+      <ns0:c r="M100">
         <ns0:v>31.763500022888184</ns0:v>
       </ns0:c>
-      <ns0:c r="N96">
+      <ns0:c r="N100">
         <ns0:v>30.527600021362304</ns0:v>
       </ns0:c>
-      <ns0:c r="O96">
+      <ns0:c r="O100">
         <ns0:v>21.973449993133546</ns0:v>
       </ns0:c>
-      <ns0:c r="P96" t="inlineStr">
+      <ns0:c r="P100" t="inlineStr">
         <ns0:is>
           <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="Q96" t="inlineStr">
-        <ns0:is>
-          <ns0:t>재료 수집 실패</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="R96" t="inlineStr">
-        <ns0:is>
-          <ns0:t/>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="T96" t="inlineStr">
+      <ns0:c r="Q100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R100" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T100" t="inlineStr">
         <ns0:is>
           <ns0:t>https://finance.yahoo.com/quote/ZETA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:T96"/>
+  <ns0:autoFilter ref="A1:T100"/>
   <ns0:hyperlinks>
     <ns0:hyperlink ref="T2" ns1:id="rId1"/>
     <ns0:hyperlink ref="T3" ns1:id="rId2"/>
@@ -7711,6 +8027,10 @@
     <ns0:hyperlink ref="T94" ns1:id="rId93"/>
     <ns0:hyperlink ref="T95" ns1:id="rId94"/>
     <ns0:hyperlink ref="T96" ns1:id="rId95"/>
+    <ns0:hyperlink ref="T97" ns1:id="rId96"/>
+    <ns0:hyperlink ref="T98" ns1:id="rId97"/>
+    <ns0:hyperlink ref="T99" ns1:id="rId98"/>
+    <ns0:hyperlink ref="T100" ns1:id="rId99"/>
   </ns0:hyperlinks>
 </ns0:worksheet>
 </file>
@@ -7758,11 +8078,11 @@
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3">
-        <ns0:v>16</ns0:v>
+        <ns0:v>17</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="4">
@@ -7773,11 +8093,11 @@
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C4">
-        <ns0:v>15</ns0:v>
+        <ns0:v>16</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="5">
@@ -7788,7 +8108,7 @@
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5">
@@ -7807,7 +8127,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6">
-        <ns0:v>14</ns0:v>
+        <ns0:v>15</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="7">
@@ -7848,11 +8168,11 @@
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9">
-        <ns0:v>2</ns0:v>
+        <ns0:v>3</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10">
@@ -7863,7 +8183,7 @@
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Defensive</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C10">
@@ -7927,7 +8247,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2">
-        <ns0:v>95</ns0:v>
+        <ns0:v>99</ns0:v>
       </ns0:c>
       <ns0:c r="D2" t="inlineStr">
         <ns0:is>

--- a/technicals/exports/2026-10-16.xlsx
+++ b/technicals/exports/2026-10-16.xlsx
@@ -221,7 +221,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 클라우드 기반 인적자본관리 플랫폼과 인사 업무 아웃소싱 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>전 세계에 클라우드 기반 인적자본관리 플랫폼과 인사 업무 아웃소싱을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -300,7 +300,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재산·상해보험을 제공하는 보험 지주회사로, 재산 및 운송보험 상품 등을 취급한다.</ns0:t>
+          <ns0:t>미국에서 재산·상해보험과 운송보험 등을 제공하는 보험 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -458,7 +458,7 @@
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 병원과 의료시설에 기술 기반 의료인력 솔루션 및 인력 공급 서비스를 제공.</ns0:t>
+          <ns0:t>미국 병원·의료시설에 기술 기반 의료인력 솔루션과 인력 공급 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
@@ -537,7 +537,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 사격 스포츠 액세서리, 칼 등 야외활동 제품과 용품을 제공하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 사격 스포츠 액세서리·칼 등 야외활동 제품과 용품을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
@@ -616,7 +616,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·이집트·북해에서 천연가스, 원유 및 천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
+          <ns0:t>미국·이집트·북해에서 천연가스·원유·천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
@@ -695,7 +695,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 내 고급 객실 중심 호텔 포트폴리오를 보유한 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>미국 내 고급 객실 중심 호텔을 보유한 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -774,7 +774,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
+          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리·음성 AI 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
@@ -932,7 +932,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 의료기관·연구기관 등에 의료용품, 의료기기, 실험실 장비 및 진단 제품을 개발·제조·판매.</ns0:t>
+          <ns0:t>전 세계 의료·연구기관 등에 의료용품·의료기기·실험실 장비·진단 제품을 개발·제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1011,7 +1011,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 규모의 조직이 장소와 기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
+          <ns0:t>다양한 규모의 조직이 장소·기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
@@ -1090,7 +1090,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 석유·가스 사업을 운영하며 가스·저탄소 에너지, 석유 생산 및 고객·제품 부문을 영위.</ns0:t>
+          <ns0:t>전 세계에서 가스·저탄소 에너지, 석유 생산, 고객·제품 부문 등 석유·가스 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1327,7 +1327,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다에서 식당을 운영·라이선스하고, 치즈케이크 등 제과 제품을 생산·공급하는 기업.</ns0:t>
+          <ns0:t>미국·캐나다에서 식당 운영·라이선스 사업과 치즈케이크 등 제과 제품 생산·공급을 하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1485,7 +1485,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>대만과 해외에서 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>대만과 해외 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1564,7 +1564,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>고급 장기체류 호텔과 프리미엄 브랜드의 선택형 서비스 호텔에 주로 투자하는 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>고급 장기체류 호텔과 프리미엄 브랜드 선택형 서비스 호텔에 주로 투자하는 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1643,7 +1643,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 보험 보장이 부족한 가정과 기업에 프로그램·서비스를 제공하는 관리형 의료 기업.</ns0:t>
+          <ns0:t>미국 내 보험 보장이 부족한 가정·기업에 프로그램과 서비스를 제공하는 관리형 의료 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1801,7 +1801,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
@@ -1880,7 +1880,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
+          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소를 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -1959,7 +1959,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매하는 기업.</ns0:t>
+          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2038,7 +2038,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·천연가스 탐사, 개발, 생산, 운송 등을 포함한 통합 에너지 및 화학 사업을 영위.</ns0:t>
+          <ns0:t>원유·천연가스 탐사·개발·생산·운송 등을 포함한 통합 에너지·화학 사업 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2196,7 +2196,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>한국·미국 등에서 캐주얼 게임과 모바일 앱을 개발·배급하며 소셜 카지노 게임 및 iGaming 사업 운영.</ns0:t>
+          <ns0:t>한국·미국 등에서 캐주얼 게임·모바일 앱을 개발·배급하고 소셜 카지노와 iGaming 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2433,7 +2433,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2512,7 +2512,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>노르웨이와 해외에서 탐사·생산, 마케팅·미드스트림·가공, 재생에너지 사업을 하는 기업.</ns0:t>
+          <ns0:t>노르웨이와 해외에서 탐사·생산, 마케팅·미드스트림·가공 및 재생에너지 사업을 하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2591,7 +2591,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 구매자와 판매자를 연결하는 Etsy·Depop 온라인 마켓플레이스를 운영하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 구매자와 판매자를 연결하는 Etsy·Depop 온라인 마켓플레이스 운영기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2828,7 +2828,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·소기업·기업 고객에게 은행·신탁·금융 서비스를 제공하는 은행을 보유한 지주회사.</ns0:t>
+          <ns0:t>개인·소기업·기업에 은행·신탁·금융 서비스를 제공하는 은행을 보유한 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -2907,7 +2907,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 의료용 의류, 신발 등 생활용품을 소비자에게 직접 판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 의료용 의류·신발 등 생활용품을 소비자에게 직접 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
@@ -2986,7 +2986,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>증권 중개·매매, 시장조성, 투자 리서치·자문, 소매·상업은행 및 보험 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>증권 중개·매매·시장조성·투자 리서치·자문과 소매·상업은행 및 보험 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3065,7 +3065,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 고객 경험과 직원 경험을 위한 서비스형 소프트웨어를 제공한다.</ns0:t>
+          <ns0:t>전 세계에 고객·직원 경험을 위한 서비스형 소프트웨어를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3144,7 +3144,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>독자 효소와 기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
+          <ns0:t>독자 효소·기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3223,7 +3223,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험을 제공하며 보험·마켓플레이스 부문을 운영.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험과 마켓플레이스 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3302,7 +3302,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3460,7 +3460,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
+          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3539,7 +3539,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크를 통해 소비자에게 제공.</ns0:t>
+          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크로 소비자에게 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3618,7 +3618,7 @@
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46">
@@ -3697,7 +3697,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>식품·음료·건강 및 바이오과학·향료와 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
+          <ns0:t>식품·음료·건강·바이오과학·향료 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3776,7 +3776,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 장난감, 소비재·전자제품, 아동용 가구, 의상, 스포츠용품, 가정용 가구 등을 제작·판매.</ns0:t>
+          <ns0:t>전 세계에서 장난감, 소비재·전자제품, 아동·가정용 가구, 의상, 스포츠용품을 제작·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
@@ -3855,7 +3855,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 방위·항공우주 분야 기업과의 합병, 주식 교환, 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 방위·항공우주 기업과 합병·주식 교환·인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
@@ -4010,7 +4010,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 석유·가스 에너지 사업을 발굴·개발하며 오클라호마 캐니 셰일 유전을 개발하는 기업.</ns0:t>
+          <ns0:t>미국에서 석유·가스 사업을 발굴·개발하고 오클라호마 캐니 셰일 유전을 개발하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
@@ -4168,7 +4168,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득하는 기업.</ns0:t>
+          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
@@ -4247,7 +4247,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 거래 처리 및 결제 관련 제품·서비스를 소비자, 가맹점, 금융기관 등에 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소비자·가맹점·금융기관 등에 거래 처리와 결제 제품·서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
@@ -4326,7 +4326,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>공급망·재고·옴니채널 운영과 창고 관리를 위한 소프트웨어를 개발·판매·구축·유지보수.</ns0:t>
+          <ns0:t>공급망·재고·옴니채널 운영·창고 관리 소프트웨어를 개발·판매·구축·유지보수하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
@@ -4405,7 +4405,7 @@
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>의약품 유통, 종양·전문진료, 처방 기술, 의료·외과용품 관련 의료 서비스를 제공.</ns0:t>
+          <ns0:t>의약품 유통·종양 및 전문진료·처방 기술·의료 및 외과용품 관련 의료 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
@@ -4484,7 +4484,7 @@
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 신생아·모체태아·소아 세부전문 진료와 미숙아·합병증 신생아 치료를 제공하는 기업.</ns0:t>
+          <ns0:t>미국에서 신생아·모체태아·소아 전문 진료와 미숙아·합병증 신생아 치료를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
@@ -4563,7 +4563,7 @@
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 보험, 연금, 임직원 복리후생 및 자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
+          <ns0:t>전 세계에서 보험·연금·임직원 복리후생·자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
@@ -4721,7 +4721,7 @@
       </ns0:c>
       <ns0:c r="F60" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G60">
@@ -4800,7 +4800,7 @@
       </ns0:c>
       <ns0:c r="F61" t="inlineStr">
         <ns0:is>
-          <ns0:t>전문 간호·생활지원·독립생활 시설, 재택돌봄·호스피스 기관 및 병원 서비스를 운영하는 기업.</ns0:t>
+          <ns0:t>전문 간호·생활지원·독립생활 시설과 재택돌봄·호스피스 기관 및 병원 서비스를 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G61">
@@ -4958,7 +4958,7 @@
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드를 제공.</ns0:t>
+          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
@@ -5116,7 +5116,7 @@
       </ns0:c>
       <ns0:c r="F65" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 중소·중견기업에 채용 등 고용 전 과정을 관리하는 클라우드 인적자본관리 소프트웨어를 제공.</ns0:t>
+          <ns0:t>미국 중소·중견기업에 채용 등 고용 전 과정을 관리하는 클라우드 인적자본관리 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G65">
@@ -5195,7 +5195,7 @@
       </ns0:c>
       <ns0:c r="F66" t="inlineStr">
         <ns0:is>
-          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
+          <ns0:t>선불카드, 환자 비용 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G66">
@@ -5274,7 +5274,7 @@
       </ns0:c>
       <ns0:c r="F67" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G67">
@@ -5353,7 +5353,7 @@
       </ns0:c>
       <ns0:c r="F68" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G68">
@@ -5432,7 +5432,7 @@
       </ns0:c>
       <ns0:c r="F69" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 급여·세무·인사 관리 등을 지원하는 클라우드 인적자본관리·재무·IT 소프트웨어를 제공.</ns0:t>
+          <ns0:t>미국에서 급여·세무·인사 관리를 지원하는 클라우드 인적자본관리·재무·IT 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G69">
@@ -5590,7 +5590,7 @@
       </ns0:c>
       <ns0:c r="F71" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국의 도심·리조트형 라이프스타일 호텔을 보유한 상장 부동산투자신탁.</ns0:t>
+          <ns0:t>미국 도심·리조트형 라이프스타일 호텔을 보유한 상장 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G71">
@@ -5748,7 +5748,7 @@
       </ns0:c>
       <ns0:c r="F73" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 교육 교재·평가·자격인증·온라인 학습·영어 학습 등 교육 서비스를 제공.</ns0:t>
+          <ns0:t>세계 각지에서 교육 교재·평가·자격인증·온라인 학습·영어 학습 등 교육 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G73">
@@ -5827,7 +5827,7 @@
       </ns0:c>
       <ns0:c r="F74" t="inlineStr">
         <ns0:is>
-          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
+          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G74">
@@ -5906,7 +5906,7 @@
       </ns0:c>
       <ns0:c r="F75" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 생명·건강 및 자산집약형 재보험을 제공하며 장애·장기요양 관련 보장도 취급.</ns0:t>
+          <ns0:t>전 세계에서 생명·건강·자산집약형 재보험을 제공하고 장애·장기요양 관련 보장도 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G75">
@@ -5985,7 +5985,7 @@
       </ns0:c>
       <ns0:c r="F76" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 재산·상해·특종 보험과 재보험을 제공하며 재산 재해 초과손해 재보험을 취급.</ns0:t>
+          <ns0:t>미국과 해외에서 재산·상해·특종 보험 및 재보험을 제공하고 재산 재해 초과손해 재보험 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G76">
@@ -6143,7 +6143,7 @@
       </ns0:c>
       <ns0:c r="F78" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 건강한 음식과 음료를 제공하는 패스트푸드 식당을 운영하며 온라인·모바일 주문을 지원.</ns0:t>
+          <ns0:t>미국에서 건강한 음식·음료를 제공하는 패스트푸드 식당을 운영하고 온라인·모바일 주문 지원.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G78">
@@ -6222,7 +6222,7 @@
       </ns0:c>
       <ns0:c r="F79" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
+          <ns0:t>전 세계에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G79">
@@ -6301,7 +6301,7 @@
       </ns0:c>
       <ns0:c r="F80" t="inlineStr">
         <ns0:is>
-          <ns0:t>입지가 좋은 호텔·리조트 부동산을 인수·적극 운영·매각하는 숙박 부동산투자신탁.</ns0:t>
+          <ns0:t>입지가 좋은 호텔·리조트 부동산을 인수·운영·매각하는 숙박 부동산투자신탁.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G80">
@@ -6380,7 +6380,7 @@
       </ns0:c>
       <ns0:c r="F81" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국·아일랜드에서 다이아몬드 주얼리 소매점을 운영.</ns0:t>
+          <ns0:t>미국·캐나다·영국·아일랜드에서 다이아몬드 주얼리 소매점을 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G81">
@@ -6459,7 +6459,7 @@
       </ns0:c>
       <ns0:c r="F82" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 해안 지역 주택·콘도·상업용 주거시설 등의 손해보험과 재보험·보험대리 서비스를 제공.</ns0:t>
+          <ns0:t>미국 해안 지역 주택·콘도·상업용 주거시설의 손해보험과 재보험·보험대리 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G82">
@@ -6538,7 +6538,7 @@
       </ns0:c>
       <ns0:c r="F83" t="inlineStr">
         <ns0:is>
-          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청, 연료, 나프타, 윤활유, 액화석유가스 등을 공급한다.</ns0:t>
+          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청·연료·나프타·윤활유·액화석유가스를 공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G83">
@@ -6617,7 +6617,7 @@
       </ns0:c>
       <ns0:c r="F84" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 운영하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G84">
@@ -6930,7 +6930,7 @@
       </ns0:c>
       <ns0:c r="F88" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 소매·도매·구독 사업으로 의류·신발·액세서리 등 라이프스타일 상품과 서비스 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소매·도매·구독 사업을 통해 의류·신발·액세서리 등 라이프스타일 상품·서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G88">
@@ -7088,7 +7088,7 @@
       </ns0:c>
       <ns0:c r="F90" t="inlineStr">
         <ns0:is>
-          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공.</ns0:t>
+          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G90">
@@ -7167,7 +7167,7 @@
       </ns0:c>
       <ns0:c r="F91" t="inlineStr">
         <ns0:is>
-          <ns0:t>버지니아 내 상업·개인 금융 서비스를 제공하는 은행의 지주회사로 은행 및 신탁·상속재산 서비스 운영.</ns0:t>
+          <ns0:t>버지니아에서 상업·개인 금융과 신탁·상속재산 서비스를 운영하는 은행 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G91">
@@ -7246,7 +7246,7 @@
       </ns0:c>
       <ns0:c r="F92" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어를 제공하며 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
+          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어와 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G92">
@@ -7325,7 +7325,7 @@
       </ns0:c>
       <ns0:c r="F93" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 도매·소비자 직접판매 사업을 운영하며 캐시미어 스웨터·실크 블라우스 등 여성복을 판매한다.</ns0:t>
+          <ns0:t>미국과 해외에서 도매·소비자 직접판매로 캐시미어 스웨터·실크 블라우스 등 여성복을 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G93">
@@ -7641,7 +7641,7 @@
       </ns0:c>
       <ns0:c r="F97" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 온·오프라인으로 조리·식사·접객용품과 가구 등 가정용 제품을 판매.</ns0:t>
+          <ns0:t>미국과 해외 온·오프라인에서 조리·식사·접객용품과 가구 등 가정용 제품 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G97">
@@ -7799,7 +7799,7 @@
       </ns0:c>
       <ns0:c r="F99" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업을 운영한다.</ns0:t>
+          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G99">
@@ -7878,7 +7878,7 @@
       </ns0:c>
       <ns0:c r="F100" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외 기업에 소비자 인텔리전스와 마케팅 자동화 소프트웨어를 제공하는 옴니채널 데이터 기반 플랫폼 운영.</ns0:t>
+          <ns0:t>미국과 해외 기업에 소비자 인텔리전스·마케팅 자동화 소프트웨어를 제공하는 옴니채널 데이터 기반 플랫폼 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G100">
